--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="89">
   <si>
     <t>Name</t>
   </si>
@@ -100,6 +100,114 @@
     <t>GANNA Filippo</t>
   </si>
   <si>
+    <t>PEDERSEN Rasmus</t>
+  </si>
+  <si>
+    <t>MORO Manlio</t>
+  </si>
+  <si>
+    <t>BLEDDYN Oliver</t>
+  </si>
+  <si>
+    <t>ANGSUTHASAWIT Jai</t>
+  </si>
+  <si>
+    <t>AWANG Mohd Azizulhasni</t>
+  </si>
+  <si>
+    <t>CARLIN Jack</t>
+  </si>
+  <si>
+    <t>CECHMAN Martin</t>
+  </si>
+  <si>
+    <t>CORNISH Thomas</t>
+  </si>
+  <si>
+    <t>DAKIN Sam</t>
+  </si>
+  <si>
+    <t>DODYK Ryan</t>
+  </si>
+  <si>
+    <t>DORNBACH Maximilian</t>
+  </si>
+  <si>
+    <t>GLAETZER Matthew</t>
+  </si>
+  <si>
+    <t>HELAL Ryan</t>
+  </si>
+  <si>
+    <t>HOOGLAND Jeffrey</t>
+  </si>
+  <si>
+    <t>LAVREYSEN Harrie</t>
+  </si>
+  <si>
+    <t>LENDEL Vasilijus</t>
+  </si>
+  <si>
+    <t>MARTINEZ CHORRO</t>
+  </si>
+  <si>
+    <t>MOHD ZONIS Muhammad Fadhil</t>
+  </si>
+  <si>
+    <t>ORTEGA FONTALVO Cristian David</t>
+  </si>
+  <si>
+    <t>OTA Kaiya</t>
+  </si>
+  <si>
+    <t>PAUL Nicholas</t>
+  </si>
+  <si>
+    <t>PREDOMO Mattia</t>
+  </si>
+  <si>
+    <t>QUINTERO CHAVARRO Kevin Santiago</t>
+  </si>
+  <si>
+    <t>RICHARDSON Matthew</t>
+  </si>
+  <si>
+    <t>RUDYK Mateusz</t>
+  </si>
+  <si>
+    <t>SAHROM Muhammad Shah Firdaus</t>
+  </si>
+  <si>
+    <t>SARNECKI Rafal</t>
+  </si>
+  <si>
+    <t>SZALONTAY Sandor</t>
+  </si>
+  <si>
+    <t>TERASAKI Kohei</t>
+  </si>
+  <si>
+    <t>TJON EN FA Jair</t>
+  </si>
+  <si>
+    <t>TRUMAN Joseph</t>
+  </si>
+  <si>
+    <t>van LOON Tijmen</t>
+  </si>
+  <si>
+    <t>VIGIER Sebastien</t>
+  </si>
+  <si>
+    <t>WAMMES Nick</t>
+  </si>
+  <si>
+    <t>WEINRICH Willy Leonhard</t>
+  </si>
+  <si>
+    <t>YAKOVLEV Mikhail</t>
+  </si>
+  <si>
     <t>NZL</t>
   </si>
   <si>
@@ -115,7 +223,61 @@
     <t>ITA</t>
   </si>
   <si>
+    <t>THA</t>
+  </si>
+  <si>
+    <t>MAS</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>GER</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>NED</t>
+  </si>
+  <si>
+    <t>LTU</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>TTO</t>
+  </si>
+  <si>
+    <t>POL</t>
+  </si>
+  <si>
+    <t>HUN</t>
+  </si>
+  <si>
+    <t>SUR</t>
+  </si>
+  <si>
+    <t>ISR</t>
+  </si>
+  <si>
     <t>Team Pursuit</t>
+  </si>
+  <si>
+    <t>Sprint Qual</t>
+  </si>
+  <si>
+    <t>Null</t>
   </si>
   <si>
     <t>WCH</t>
@@ -480,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -514,16 +676,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2">
         <v>45141</v>
@@ -540,16 +702,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F3" s="2">
         <v>45141</v>
@@ -566,16 +728,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2">
         <v>45141</v>
@@ -592,16 +754,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2">
         <v>45141</v>
@@ -618,16 +780,16 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F6" s="2">
         <v>45141</v>
@@ -644,16 +806,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F7" s="2">
         <v>45141</v>
@@ -670,16 +832,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2">
         <v>45141</v>
@@ -696,16 +858,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2">
         <v>45141</v>
@@ -722,16 +884,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F10" s="2">
         <v>45141</v>
@@ -748,16 +910,16 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2">
         <v>45141</v>
@@ -774,16 +936,16 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2">
         <v>45141</v>
@@ -800,16 +962,16 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F13" s="2">
         <v>45141</v>
@@ -826,16 +988,16 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F14" s="2">
         <v>45141</v>
@@ -852,16 +1014,16 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F15" s="2">
         <v>45141</v>
@@ -878,16 +1040,16 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F16" s="2">
         <v>45141</v>
@@ -904,16 +1066,16 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F17" s="2">
         <v>45141</v>
@@ -930,16 +1092,16 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F18" s="2">
         <v>45141</v>
@@ -956,16 +1118,16 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2">
         <v>45141</v>
@@ -982,16 +1144,16 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F20" s="2">
         <v>45141</v>
@@ -1008,16 +1170,16 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2">
         <v>45141</v>
@@ -1027,6 +1189,1280 @@
       </c>
       <c r="H21">
         <v>121.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G22">
+        <v>128.01</v>
+      </c>
+      <c r="H22">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G23">
+        <v>127.42</v>
+      </c>
+      <c r="H23">
+        <v>127.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G24">
+        <v>127.42</v>
+      </c>
+      <c r="H24">
+        <v>127.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G25">
+        <v>129.34</v>
+      </c>
+      <c r="H25">
+        <v>129.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G26">
+        <v>127.75</v>
+      </c>
+      <c r="H26">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G27">
+        <v>127.74</v>
+      </c>
+      <c r="H27">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G28">
+        <v>127.74</v>
+      </c>
+      <c r="H28">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G29">
+        <v>127.79</v>
+      </c>
+      <c r="H29">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G30">
+        <v>121.63</v>
+      </c>
+      <c r="H30">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G31">
+        <v>121.4</v>
+      </c>
+      <c r="H31">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G32">
+        <v>123.6</v>
+      </c>
+      <c r="H32">
+        <v>123.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G33">
+        <v>121.29</v>
+      </c>
+      <c r="H33">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G34">
+        <v>120.74</v>
+      </c>
+      <c r="H34">
+        <v>120.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G35">
+        <v>122.5</v>
+      </c>
+      <c r="H35">
+        <v>122.54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G36">
+        <v>124.75</v>
+      </c>
+      <c r="H36">
+        <v>124.62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G37">
+        <v>123.96</v>
+      </c>
+      <c r="H37">
+        <v>123.88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G38">
+        <v>135.25</v>
+      </c>
+      <c r="H38">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" t="s">
+        <v>87</v>
+      </c>
+      <c r="E39" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G39">
+        <v>132.49</v>
+      </c>
+      <c r="H39">
+        <v>132.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" t="s">
+        <v>88</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G40">
+        <v>133.4</v>
+      </c>
+      <c r="H40">
+        <v>133.31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G41">
+        <v>130.8</v>
+      </c>
+      <c r="H41">
+        <v>130.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" t="s">
+        <v>88</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G42">
+        <v>128.87</v>
+      </c>
+      <c r="H42">
+        <v>128.77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G43">
+        <v>134.36</v>
+      </c>
+      <c r="H43">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G44">
+        <v>129.68</v>
+      </c>
+      <c r="H44">
+        <v>129.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G45">
+        <v>129.32</v>
+      </c>
+      <c r="H45">
+        <v>129.21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G46">
+        <v>136.58</v>
+      </c>
+      <c r="H46">
+        <v>136.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G47">
+        <v>133.89</v>
+      </c>
+      <c r="H47">
+        <v>133.31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G48">
+        <v>135.24</v>
+      </c>
+      <c r="H48">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G49">
+        <v>134.28</v>
+      </c>
+      <c r="H49">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G50">
+        <v>139.73</v>
+      </c>
+      <c r="H50">
+        <v>139.91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G51">
+        <v>130.91</v>
+      </c>
+      <c r="H51">
+        <v>130.85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" t="s">
+        <v>86</v>
+      </c>
+      <c r="D52" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G52">
+        <v>135.26</v>
+      </c>
+      <c r="H52">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G53">
+        <v>131.73</v>
+      </c>
+      <c r="H53">
+        <v>131.63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G54">
+        <v>139.29</v>
+      </c>
+      <c r="H54">
+        <v>139.15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G55">
+        <v>140.76</v>
+      </c>
+      <c r="H55">
+        <v>140.79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" t="s">
+        <v>88</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G56">
+        <v>119.48</v>
+      </c>
+      <c r="H56">
+        <v>119.57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" t="s">
+        <v>87</v>
+      </c>
+      <c r="E57" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G57">
+        <v>131.78</v>
+      </c>
+      <c r="H57">
+        <v>131.63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E58" t="s">
+        <v>88</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G58">
+        <v>134.33</v>
+      </c>
+      <c r="H58">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" t="s">
+        <v>87</v>
+      </c>
+      <c r="E59" t="s">
+        <v>88</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G59">
+        <v>138.93</v>
+      </c>
+      <c r="H59">
+        <v>138.86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>87</v>
+      </c>
+      <c r="E60" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G60">
+        <v>142.39</v>
+      </c>
+      <c r="H60">
+        <v>142.36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G61">
+        <v>137.91</v>
+      </c>
+      <c r="H61">
+        <v>137.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" t="s">
+        <v>87</v>
+      </c>
+      <c r="E62" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G62">
+        <v>132.57</v>
+      </c>
+      <c r="H62">
+        <v>132.55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" t="s">
+        <v>88</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G63">
+        <v>128.46</v>
+      </c>
+      <c r="H63">
+        <v>128.25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" t="s">
+        <v>86</v>
+      </c>
+      <c r="D64" t="s">
+        <v>87</v>
+      </c>
+      <c r="E64" t="s">
+        <v>88</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G64">
+        <v>133.41</v>
+      </c>
+      <c r="H64">
+        <v>133.31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" t="s">
+        <v>86</v>
+      </c>
+      <c r="D65" t="s">
+        <v>87</v>
+      </c>
+      <c r="E65" t="s">
+        <v>88</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G65">
+        <v>126.68</v>
+      </c>
+      <c r="H65">
+        <v>126.69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" t="s">
+        <v>86</v>
+      </c>
+      <c r="D66" t="s">
+        <v>87</v>
+      </c>
+      <c r="E66" t="s">
+        <v>88</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G66">
+        <v>130.86</v>
+      </c>
+      <c r="H66">
+        <v>130.85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" t="s">
+        <v>86</v>
+      </c>
+      <c r="D67" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" t="s">
+        <v>88</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G67">
+        <v>140.13</v>
+      </c>
+      <c r="H67">
+        <v>139.91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>86</v>
+      </c>
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G68">
+        <v>137.49</v>
+      </c>
+      <c r="H68">
+        <v>137.45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" t="s">
+        <v>87</v>
+      </c>
+      <c r="E69" t="s">
+        <v>88</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G69">
+        <v>120.58</v>
+      </c>
+      <c r="H69">
+        <v>120.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" t="s">
+        <v>86</v>
+      </c>
+      <c r="D70" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" t="s">
+        <v>88</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45143</v>
+      </c>
+      <c r="G70">
+        <v>138.85</v>
+      </c>
+      <c r="H70">
+        <v>138.86</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Gear_Calculator\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A782E-54C9-4E01-B47A-89FC81E6E8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$110</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="108">
   <si>
     <t>Name</t>
   </si>
@@ -208,6 +217,42 @@
     <t>YAKOVLEV Mikhail</t>
   </si>
   <si>
+    <t>TURNBULL Hamish</t>
+  </si>
+  <si>
+    <t>NAKANO Shinji</t>
+  </si>
+  <si>
+    <t>SAHROM Muhammad Ridwan</t>
+  </si>
+  <si>
+    <t>QUINTERO CHAVARRO Kevin S</t>
+  </si>
+  <si>
+    <t>ESOW Esow</t>
+  </si>
+  <si>
+    <t>van LOOK Tijmen</t>
+  </si>
+  <si>
+    <t>BROWNE Kwesi</t>
+  </si>
+  <si>
+    <t>RAMIREZ MORALES Santiago</t>
+  </si>
+  <si>
+    <t>HEDGCOCK James</t>
+  </si>
+  <si>
+    <t>PONOMARYOV Sergey</t>
+  </si>
+  <si>
+    <t>JURCZYK Marc</t>
+  </si>
+  <si>
+    <t>SPIES Jean</t>
+  </si>
+  <si>
     <t>NZL</t>
   </si>
   <si>
@@ -271,26 +316,47 @@
     <t>ISR</t>
   </si>
   <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
     <t>Team Pursuit</t>
   </si>
   <si>
     <t>Sprint Qual</t>
   </si>
   <si>
+    <t>Keirin</t>
+  </si>
+  <si>
     <t>Null</t>
   </si>
   <si>
     <t>WCH</t>
+  </si>
+  <si>
+    <t>WCH 7-12 Final</t>
+  </si>
+  <si>
+    <t>WCH Gold Final</t>
+  </si>
+  <si>
+    <t>WCH R1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,13 +420,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -398,7 +472,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -432,6 +506,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -466,9 +541,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -641,11 +717,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,21 +752,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2">
         <v>45141</v>
@@ -697,21 +778,21 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F3" s="2">
         <v>45141</v>
@@ -723,21 +804,21 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F4" s="2">
         <v>45141</v>
@@ -749,21 +830,21 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F5" s="2">
         <v>45141</v>
@@ -775,47 +856,47 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F6" s="2">
         <v>45141</v>
       </c>
       <c r="G6">
-        <v>128.17</v>
+        <v>128.16999999999999</v>
       </c>
       <c r="H6">
         <v>128.25</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F7" s="2">
         <v>45141</v>
@@ -827,21 +908,21 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F8" s="2">
         <v>45141</v>
@@ -853,21 +934,21 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F9" s="2">
         <v>45141</v>
@@ -879,21 +960,21 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F10" s="2">
         <v>45141</v>
@@ -905,21 +986,21 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F11" s="2">
         <v>45141</v>
@@ -931,21 +1012,21 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F12" s="2">
         <v>45141</v>
@@ -957,21 +1038,21 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F13" s="2">
         <v>45141</v>
@@ -983,21 +1064,21 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F14" s="2">
         <v>45141</v>
@@ -1009,21 +1090,21 @@
         <v>123.19</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F15" s="2">
         <v>45141</v>
@@ -1035,21 +1116,21 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F16" s="2">
         <v>45141</v>
@@ -1061,21 +1142,21 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F17" s="2">
         <v>45141</v>
@@ -1087,21 +1168,21 @@
         <v>125.18</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F18" s="2">
         <v>45141</v>
@@ -1113,21 +1194,21 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F19" s="2">
         <v>45141</v>
@@ -1139,21 +1220,21 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F20" s="2">
         <v>45141</v>
@@ -1165,21 +1246,21 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F21" s="2">
         <v>45141</v>
@@ -1191,21 +1272,21 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F22" s="2">
         <v>45142</v>
@@ -1217,21 +1298,21 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F23" s="2">
         <v>45142</v>
@@ -1243,21 +1324,21 @@
         <v>127.29</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F24" s="2">
         <v>45142</v>
@@ -1269,21 +1350,21 @@
         <v>127.29</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F25" s="2">
         <v>45142</v>
@@ -1295,21 +1376,21 @@
         <v>129.21</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F26" s="2">
         <v>45143</v>
@@ -1321,21 +1402,21 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2">
         <v>45143</v>
@@ -1347,21 +1428,21 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F28" s="2">
         <v>45143</v>
@@ -1373,21 +1454,21 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2">
         <v>45143</v>
@@ -1399,21 +1480,21 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F30" s="2">
         <v>45143</v>
@@ -1425,21 +1506,21 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2">
         <v>45143</v>
@@ -1451,21 +1532,21 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F32" s="2">
         <v>45143</v>
@@ -1477,21 +1558,21 @@
         <v>123.75</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F33" s="2">
         <v>45143</v>
@@ -1503,21 +1584,21 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F34" s="2">
         <v>45142</v>
@@ -1529,21 +1610,21 @@
         <v>120.71</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F35" s="2">
         <v>45142</v>
@@ -1555,21 +1636,21 @@
         <v>122.54</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F36" s="2">
         <v>45142</v>
@@ -1581,21 +1662,21 @@
         <v>124.62</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F37" s="2">
         <v>45142</v>
@@ -1607,21 +1688,21 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E38" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F38" s="2">
         <v>45143</v>
@@ -1633,21 +1714,21 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F39" s="2">
         <v>45143</v>
@@ -1656,24 +1737,24 @@
         <v>132.49</v>
       </c>
       <c r="H39">
-        <v>132.55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>132.55000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F40" s="2">
         <v>45143</v>
@@ -1685,47 +1766,47 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F41" s="2">
         <v>45143</v>
       </c>
       <c r="G41">
-        <v>130.8</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="H41">
         <v>130.85</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F42" s="2">
         <v>45143</v>
@@ -1734,50 +1815,50 @@
         <v>128.87</v>
       </c>
       <c r="H42">
-        <v>128.77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>128.77000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F43" s="2">
         <v>45143</v>
       </c>
       <c r="G43">
-        <v>134.36</v>
+        <v>134.36000000000001</v>
       </c>
       <c r="H43">
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F44" s="2">
         <v>45143</v>
@@ -1789,21 +1870,21 @@
         <v>129.6</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E45" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F45" s="2">
         <v>45143</v>
@@ -1815,73 +1896,73 @@
         <v>129.21</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F46" s="2">
         <v>45143</v>
       </c>
       <c r="G46">
-        <v>136.58</v>
+        <v>136.58000000000001</v>
       </c>
       <c r="H46">
-        <v>136.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>136.80000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F47" s="2">
         <v>45143</v>
       </c>
       <c r="G47">
-        <v>133.89</v>
+        <v>133.88999999999999</v>
       </c>
       <c r="H47">
         <v>133.31</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E48" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F48" s="2">
         <v>45143</v>
@@ -1893,21 +1974,21 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F49" s="2">
         <v>45143</v>
@@ -1919,47 +2000,47 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F50" s="2">
         <v>45143</v>
       </c>
       <c r="G50">
-        <v>139.73</v>
+        <v>139.72999999999999</v>
       </c>
       <c r="H50">
         <v>139.91</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E51" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F51" s="2">
         <v>45143</v>
@@ -1971,21 +2052,21 @@
         <v>130.85</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E52" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F52" s="2">
         <v>45143</v>
@@ -1997,47 +2078,47 @@
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E53" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F53" s="2">
         <v>45143</v>
       </c>
       <c r="G53">
-        <v>131.73</v>
+        <v>131.72999999999999</v>
       </c>
       <c r="H53">
         <v>131.63</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E54" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F54" s="2">
         <v>45143</v>
@@ -2049,21 +2130,21 @@
         <v>139.15</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E55" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F55" s="2">
         <v>45143</v>
@@ -2075,21 +2156,21 @@
         <v>140.79</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E56" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F56" s="2">
         <v>45143</v>
@@ -2101,21 +2182,21 @@
         <v>119.57</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D57" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F57" s="2">
         <v>45143</v>
@@ -2127,47 +2208,47 @@
         <v>131.63</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E58" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F58" s="2">
         <v>45143</v>
       </c>
       <c r="G58">
-        <v>134.33</v>
+        <v>134.33000000000001</v>
       </c>
       <c r="H58">
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F59" s="2">
         <v>45143</v>
@@ -2176,50 +2257,50 @@
         <v>138.93</v>
       </c>
       <c r="H59">
-        <v>138.86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>138.86000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E60" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F60" s="2">
         <v>45143</v>
       </c>
       <c r="G60">
-        <v>142.39</v>
+        <v>142.38999999999999</v>
       </c>
       <c r="H60">
-        <v>142.36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>142.36000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F61" s="2">
         <v>45143</v>
@@ -2228,24 +2309,24 @@
         <v>137.91</v>
       </c>
       <c r="H61">
-        <v>137.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>137.69999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D62" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F62" s="2">
         <v>45143</v>
@@ -2254,24 +2335,24 @@
         <v>132.57</v>
       </c>
       <c r="H62">
-        <v>132.55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>132.55000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E63" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F63" s="2">
         <v>45143</v>
@@ -2283,21 +2364,21 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E64" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F64" s="2">
         <v>45143</v>
@@ -2309,21 +2390,21 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D65" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E65" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F65" s="2">
         <v>45143</v>
@@ -2335,47 +2416,47 @@
         <v>126.69</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E66" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F66" s="2">
         <v>45143</v>
       </c>
       <c r="G66">
-        <v>130.86</v>
+        <v>130.86000000000001</v>
       </c>
       <c r="H66">
         <v>130.85</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D67" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E67" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F67" s="2">
         <v>45143</v>
@@ -2387,21 +2468,21 @@
         <v>139.91</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>61</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D68" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F68" s="2">
         <v>45143</v>
@@ -2410,24 +2491,24 @@
         <v>137.49</v>
       </c>
       <c r="H68">
-        <v>137.45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>137.44999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>62</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E69" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F69" s="2">
         <v>45143</v>
@@ -2439,21 +2520,21 @@
         <v>120.6</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>63</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E70" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F70" s="2">
         <v>45143</v>
@@ -2462,10 +2543,1055 @@
         <v>138.85</v>
       </c>
       <c r="H70">
-        <v>138.86</v>
+        <v>138.86000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" t="s">
+        <v>105</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G71">
+        <v>120.98</v>
+      </c>
+      <c r="H71">
+        <v>120.71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" t="s">
+        <v>105</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G72">
+        <v>134.69</v>
+      </c>
+      <c r="H72">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>47</v>
+      </c>
+      <c r="B73" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" t="s">
+        <v>103</v>
+      </c>
+      <c r="E73" t="s">
+        <v>105</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G73">
+        <v>134.06</v>
+      </c>
+      <c r="H73">
+        <v>133.31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" t="s">
+        <v>102</v>
+      </c>
+      <c r="D74" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" t="s">
+        <v>105</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G74">
+        <v>129.27000000000001</v>
+      </c>
+      <c r="H74">
+        <v>129.21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" t="s">
+        <v>102</v>
+      </c>
+      <c r="D75" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G75">
+        <v>123.65</v>
+      </c>
+      <c r="H75">
+        <v>123.75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" t="s">
+        <v>103</v>
+      </c>
+      <c r="E76" t="s">
+        <v>105</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G76">
+        <v>117.92</v>
+      </c>
+      <c r="H76">
+        <v>117.82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" t="s">
+        <v>102</v>
+      </c>
+      <c r="D77" t="s">
+        <v>103</v>
+      </c>
+      <c r="E77" t="s">
+        <v>106</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G77">
+        <v>119.49</v>
+      </c>
+      <c r="H77">
+        <v>119.57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" t="s">
+        <v>103</v>
+      </c>
+      <c r="E78" t="s">
+        <v>106</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G78">
+        <v>126.69</v>
+      </c>
+      <c r="H78">
+        <v>126.69</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" t="s">
+        <v>103</v>
+      </c>
+      <c r="E79" t="s">
+        <v>106</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G79">
+        <v>134.6</v>
+      </c>
+      <c r="H79">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>33</v>
+      </c>
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" t="s">
+        <v>103</v>
+      </c>
+      <c r="E80" t="s">
+        <v>106</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G80">
+        <v>125.9</v>
+      </c>
+      <c r="H80">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" t="s">
+        <v>102</v>
+      </c>
+      <c r="D81" t="s">
+        <v>103</v>
+      </c>
+      <c r="E81" t="s">
+        <v>106</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G81">
+        <v>127.8</v>
+      </c>
+      <c r="H81">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" t="s">
+        <v>87</v>
+      </c>
+      <c r="C82" t="s">
+        <v>102</v>
+      </c>
+      <c r="D82" t="s">
+        <v>103</v>
+      </c>
+      <c r="E82" t="s">
+        <v>106</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45147</v>
+      </c>
+      <c r="G82">
+        <v>121.06</v>
+      </c>
+      <c r="H82">
+        <v>120.71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" t="s">
+        <v>78</v>
+      </c>
+      <c r="C83" t="s">
+        <v>102</v>
+      </c>
+      <c r="D83" t="s">
+        <v>103</v>
+      </c>
+      <c r="E83" t="s">
+        <v>107</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G83">
+        <v>124.31</v>
+      </c>
+      <c r="H83">
+        <v>124.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84" t="s">
+        <v>107</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G84">
+        <v>134.76</v>
+      </c>
+      <c r="H84">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" t="s">
+        <v>102</v>
+      </c>
+      <c r="D85" t="s">
+        <v>103</v>
+      </c>
+      <c r="E85" t="s">
+        <v>107</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G85">
+        <v>133.96</v>
+      </c>
+      <c r="H85">
+        <v>133.31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>66</v>
+      </c>
+      <c r="B86" t="s">
+        <v>82</v>
+      </c>
+      <c r="C86" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" t="s">
+        <v>107</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G86">
+        <v>128.38</v>
+      </c>
+      <c r="H86">
+        <v>128.25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>47</v>
+      </c>
+      <c r="B87" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" t="s">
+        <v>102</v>
+      </c>
+      <c r="D87" t="s">
+        <v>103</v>
+      </c>
+      <c r="E87" t="s">
+        <v>107</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G87">
+        <v>133.83000000000001</v>
+      </c>
+      <c r="H87">
+        <v>133.31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" t="s">
+        <v>90</v>
+      </c>
+      <c r="C88" t="s">
+        <v>102</v>
+      </c>
+      <c r="D88" t="s">
+        <v>103</v>
+      </c>
+      <c r="E88" t="s">
+        <v>107</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G88">
+        <v>127.72</v>
+      </c>
+      <c r="H88">
+        <v>127.64</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89" t="s">
+        <v>102</v>
+      </c>
+      <c r="D89" t="s">
+        <v>103</v>
+      </c>
+      <c r="E89" t="s">
+        <v>107</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G89">
+        <v>131.66</v>
+      </c>
+      <c r="H89">
+        <v>131.63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" t="s">
+        <v>102</v>
+      </c>
+      <c r="D90" t="s">
+        <v>103</v>
+      </c>
+      <c r="E90" t="s">
+        <v>107</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G90">
+        <v>125.98</v>
+      </c>
+      <c r="H90">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>48</v>
+      </c>
+      <c r="B91" t="s">
+        <v>92</v>
+      </c>
+      <c r="C91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91" t="s">
+        <v>103</v>
+      </c>
+      <c r="E91" t="s">
+        <v>107</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G91">
+        <v>127.01</v>
+      </c>
+      <c r="H91">
+        <v>127.06</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B92" t="s">
+        <v>78</v>
+      </c>
+      <c r="C92" t="s">
+        <v>102</v>
+      </c>
+      <c r="D92" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" t="s">
+        <v>107</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G92">
+        <v>124.3</v>
+      </c>
+      <c r="H92">
+        <v>124.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" t="s">
+        <v>102</v>
+      </c>
+      <c r="D93" t="s">
+        <v>103</v>
+      </c>
+      <c r="E93" t="s">
+        <v>107</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G93">
+        <v>121.47</v>
+      </c>
+      <c r="H93">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" t="s">
+        <v>102</v>
+      </c>
+      <c r="D94" t="s">
+        <v>103</v>
+      </c>
+      <c r="E94" t="s">
+        <v>107</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G94">
+        <v>129.1</v>
+      </c>
+      <c r="H94">
+        <v>129.21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>69</v>
+      </c>
+      <c r="B95" t="s">
+        <v>87</v>
+      </c>
+      <c r="C95" t="s">
+        <v>102</v>
+      </c>
+      <c r="D95" t="s">
+        <v>103</v>
+      </c>
+      <c r="E95" t="s">
+        <v>107</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G95">
+        <v>120.33</v>
+      </c>
+      <c r="H95">
+        <v>120.27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>38</v>
+      </c>
+      <c r="B96" t="s">
+        <v>85</v>
+      </c>
+      <c r="C96" t="s">
+        <v>102</v>
+      </c>
+      <c r="D96" t="s">
+        <v>103</v>
+      </c>
+      <c r="E96" t="s">
+        <v>107</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G96">
+        <v>122.05</v>
+      </c>
+      <c r="H96">
+        <v>122.29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97" t="s">
+        <v>102</v>
+      </c>
+      <c r="D97" t="s">
+        <v>103</v>
+      </c>
+      <c r="E97" t="s">
+        <v>107</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G97">
+        <v>131.25</v>
+      </c>
+      <c r="H97">
+        <v>131.13999999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>35</v>
+      </c>
+      <c r="B98" t="s">
+        <v>79</v>
+      </c>
+      <c r="C98" t="s">
+        <v>102</v>
+      </c>
+      <c r="D98" t="s">
+        <v>103</v>
+      </c>
+      <c r="E98" t="s">
+        <v>107</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G98">
+        <v>117.35</v>
+      </c>
+      <c r="H98">
+        <v>117.53</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>57</v>
+      </c>
+      <c r="B99" t="s">
+        <v>95</v>
+      </c>
+      <c r="C99" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" t="s">
+        <v>103</v>
+      </c>
+      <c r="E99" t="s">
+        <v>107</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G99">
+        <v>124.06</v>
+      </c>
+      <c r="H99">
+        <v>124.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>71</v>
+      </c>
+      <c r="B100" t="s">
+        <v>90</v>
+      </c>
+      <c r="C100" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" t="s">
+        <v>103</v>
+      </c>
+      <c r="E100" t="s">
+        <v>107</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G100">
+        <v>128.22</v>
+      </c>
+      <c r="H100">
+        <v>128.25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>72</v>
+      </c>
+      <c r="B101" t="s">
+        <v>84</v>
+      </c>
+      <c r="C101" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" t="s">
+        <v>103</v>
+      </c>
+      <c r="E101" t="s">
+        <v>107</v>
+      </c>
+      <c r="F101" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G101">
+        <v>123.36</v>
+      </c>
+      <c r="H101">
+        <v>123.43</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>39</v>
+      </c>
+      <c r="B102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" t="s">
+        <v>102</v>
+      </c>
+      <c r="D102" t="s">
+        <v>103</v>
+      </c>
+      <c r="E102" t="s">
+        <v>107</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G102">
+        <v>116.92</v>
+      </c>
+      <c r="H102">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>41</v>
+      </c>
+      <c r="B103" t="s">
+        <v>87</v>
+      </c>
+      <c r="C103" t="s">
+        <v>102</v>
+      </c>
+      <c r="D103" t="s">
+        <v>103</v>
+      </c>
+      <c r="E103" t="s">
+        <v>107</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G103">
+        <v>118.85</v>
+      </c>
+      <c r="H103">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>53</v>
+      </c>
+      <c r="B104" t="s">
+        <v>82</v>
+      </c>
+      <c r="C104" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" t="s">
+        <v>103</v>
+      </c>
+      <c r="E104" t="s">
+        <v>107</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G104">
+        <v>130.74</v>
+      </c>
+      <c r="H104">
+        <v>130.85</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" t="s">
+        <v>87</v>
+      </c>
+      <c r="C105" t="s">
+        <v>102</v>
+      </c>
+      <c r="D105" t="s">
+        <v>103</v>
+      </c>
+      <c r="E105" t="s">
+        <v>107</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G105">
+        <v>119.15</v>
+      </c>
+      <c r="H105">
+        <v>119.12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106" t="s">
+        <v>98</v>
+      </c>
+      <c r="C106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D106" t="s">
+        <v>103</v>
+      </c>
+      <c r="E106" t="s">
+        <v>107</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G106">
+        <v>138.37</v>
+      </c>
+      <c r="H106">
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" t="s">
+        <v>76</v>
+      </c>
+      <c r="C107" t="s">
+        <v>102</v>
+      </c>
+      <c r="D107" t="s">
+        <v>103</v>
+      </c>
+      <c r="E107" t="s">
+        <v>107</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G107">
+        <v>122.74</v>
+      </c>
+      <c r="H107">
+        <v>122.73</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>60</v>
+      </c>
+      <c r="B108" t="s">
+        <v>86</v>
+      </c>
+      <c r="C108" t="s">
+        <v>102</v>
+      </c>
+      <c r="D108" t="s">
+        <v>103</v>
+      </c>
+      <c r="E108" t="s">
+        <v>107</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G108">
+        <v>123.91</v>
+      </c>
+      <c r="H108">
+        <v>123.88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>74</v>
+      </c>
+      <c r="B109" t="s">
+        <v>85</v>
+      </c>
+      <c r="C109" t="s">
+        <v>102</v>
+      </c>
+      <c r="D109" t="s">
+        <v>103</v>
+      </c>
+      <c r="E109" t="s">
+        <v>107</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G109">
+        <v>125.74</v>
+      </c>
+      <c r="H109">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>75</v>
+      </c>
+      <c r="B110" t="s">
+        <v>99</v>
+      </c>
+      <c r="C110" t="s">
+        <v>102</v>
+      </c>
+      <c r="D110" t="s">
+        <v>103</v>
+      </c>
+      <c r="E110" t="s">
+        <v>107</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45146</v>
+      </c>
+      <c r="G110">
+        <v>125.79</v>
+      </c>
+      <c r="H110">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H110" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H110">
+      <sortCondition ref="E1:E110"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -8,22 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Gear_Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A782E-54C9-4E01-B47A-89FC81E6E8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036F32A1-5462-4667-9BA5-25E904701878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$110</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="138">
   <si>
     <t>Name</t>
   </si>
@@ -223,12 +233,12 @@
     <t>NAKANO Shinji</t>
   </si>
   <si>
+    <t>QUINTERO CHAVARRO Kevin S</t>
+  </si>
+  <si>
     <t>SAHROM Muhammad Ridwan</t>
   </si>
   <si>
-    <t>QUINTERO CHAVARRO Kevin S</t>
-  </si>
-  <si>
     <t>ESOW Esow</t>
   </si>
   <si>
@@ -253,6 +263,90 @@
     <t>SPIES Jean</t>
   </si>
   <si>
+    <t>MORAN Chloe</t>
+  </si>
+  <si>
+    <t>EDWARDS Sophie</t>
+  </si>
+  <si>
+    <t>PLOUFFE Maeve</t>
+  </si>
+  <si>
+    <t>BAKER Georgia</t>
+  </si>
+  <si>
+    <t>FORTIN Valentine</t>
+  </si>
+  <si>
+    <t>BERTEAU Victoire</t>
+  </si>
+  <si>
+    <t>le NET Marie</t>
+  </si>
+  <si>
+    <t>BORRAS Marion</t>
+  </si>
+  <si>
+    <t>MORRIS Anna</t>
+  </si>
+  <si>
+    <t>ARCHIBALD Katie</t>
+  </si>
+  <si>
+    <t>BARKER Elinor</t>
+  </si>
+  <si>
+    <t>KNIGHT Josie</t>
+  </si>
+  <si>
+    <t>BRAUSSE Franziska</t>
+  </si>
+  <si>
+    <t>KLEIN Lisa</t>
+  </si>
+  <si>
+    <t>SUSSEMILCH Laura</t>
+  </si>
+  <si>
+    <t>KROGER Mieke</t>
+  </si>
+  <si>
+    <t>FIDANZA Martina</t>
+  </si>
+  <si>
+    <t>PATERNOSTER Le.</t>
+  </si>
+  <si>
+    <t>BALSAMO Elisa</t>
+  </si>
+  <si>
+    <t>GUAZZINI Vittoria</t>
+  </si>
+  <si>
+    <t>SHEARMAN Emily</t>
+  </si>
+  <si>
+    <t>DRUMMOND Micky</t>
+  </si>
+  <si>
+    <t>WOLLASTON Ally</t>
+  </si>
+  <si>
+    <t>BOTHA Bryony</t>
+  </si>
+  <si>
+    <t>CUMMINS Olivia</t>
+  </si>
+  <si>
+    <t>VALENTA Jennifer</t>
+  </si>
+  <si>
+    <t>WILLIAMS Lily</t>
+  </si>
+  <si>
+    <t>DYGERT Chloe</t>
+  </si>
+  <si>
     <t>NZL</t>
   </si>
   <si>
@@ -325,6 +419,9 @@
     <t>RSA</t>
   </si>
   <si>
+    <t>USA</t>
+  </si>
+  <si>
     <t>Team Pursuit</t>
   </si>
   <si>
@@ -347,6 +444,9 @@
   </si>
   <si>
     <t>WCH R1</t>
+  </si>
+  <si>
+    <t>WCH WTP Q</t>
   </si>
 </sst>
 </file>
@@ -718,12 +818,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -757,16 +862,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F2" s="2">
         <v>45141</v>
@@ -783,16 +888,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F3" s="2">
         <v>45141</v>
@@ -809,16 +914,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F4" s="2">
         <v>45141</v>
@@ -835,16 +940,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F5" s="2">
         <v>45141</v>
@@ -861,16 +966,16 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F6" s="2">
         <v>45141</v>
@@ -887,16 +992,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F7" s="2">
         <v>45141</v>
@@ -913,16 +1018,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F8" s="2">
         <v>45141</v>
@@ -939,16 +1044,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F9" s="2">
         <v>45141</v>
@@ -965,16 +1070,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F10" s="2">
         <v>45141</v>
@@ -991,16 +1096,16 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F11" s="2">
         <v>45141</v>
@@ -1017,16 +1122,16 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F12" s="2">
         <v>45141</v>
@@ -1043,16 +1148,16 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F13" s="2">
         <v>45141</v>
@@ -1069,16 +1174,16 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F14" s="2">
         <v>45141</v>
@@ -1095,16 +1200,16 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F15" s="2">
         <v>45141</v>
@@ -1121,16 +1226,16 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F16" s="2">
         <v>45141</v>
@@ -1147,16 +1252,16 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F17" s="2">
         <v>45141</v>
@@ -1173,16 +1278,16 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F18" s="2">
         <v>45141</v>
@@ -1199,16 +1304,16 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F19" s="2">
         <v>45141</v>
@@ -1225,16 +1330,16 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F20" s="2">
         <v>45141</v>
@@ -1251,16 +1356,16 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F21" s="2">
         <v>45141</v>
@@ -1277,16 +1382,16 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F22" s="2">
         <v>45142</v>
@@ -1303,16 +1408,16 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F23" s="2">
         <v>45142</v>
@@ -1329,16 +1434,16 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D24">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F24" s="2">
         <v>45142</v>
@@ -1355,16 +1460,16 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F25" s="2">
         <v>45142</v>
@@ -1381,16 +1486,16 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2">
         <v>45143</v>
@@ -1407,16 +1512,16 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F27" s="2">
         <v>45143</v>
@@ -1433,16 +1538,16 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F28" s="2">
         <v>45143</v>
@@ -1459,16 +1564,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F29" s="2">
         <v>45143</v>
@@ -1485,16 +1590,16 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F30" s="2">
         <v>45143</v>
@@ -1511,16 +1616,16 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F31" s="2">
         <v>45143</v>
@@ -1537,16 +1642,16 @@
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D32">
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F32" s="2">
         <v>45143</v>
@@ -1563,16 +1668,16 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F33" s="2">
         <v>45143</v>
@@ -1589,16 +1694,16 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F34" s="2">
         <v>45142</v>
@@ -1615,16 +1720,16 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F35" s="2">
         <v>45142</v>
@@ -1641,16 +1746,16 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F36" s="2">
         <v>45142</v>
@@ -1667,16 +1772,16 @@
         <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F37" s="2">
         <v>45142</v>
@@ -1693,16 +1798,16 @@
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F38" s="2">
         <v>45143</v>
@@ -1719,16 +1824,16 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F39" s="2">
         <v>45143</v>
@@ -1745,16 +1850,16 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2">
         <v>45143</v>
@@ -1771,16 +1876,16 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F41" s="2">
         <v>45143</v>
@@ -1797,16 +1902,16 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F42" s="2">
         <v>45143</v>
@@ -1823,16 +1928,16 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E43" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F43" s="2">
         <v>45143</v>
@@ -1849,16 +1954,16 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2">
         <v>45143</v>
@@ -1875,16 +1980,16 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F45" s="2">
         <v>45143</v>
@@ -1901,16 +2006,16 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E46" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F46" s="2">
         <v>45143</v>
@@ -1927,16 +2032,16 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F47" s="2">
         <v>45143</v>
@@ -1953,16 +2058,16 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E48" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F48" s="2">
         <v>45143</v>
@@ -1979,16 +2084,16 @@
         <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E49" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F49" s="2">
         <v>45143</v>
@@ -2005,16 +2110,16 @@
         <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F50" s="2">
         <v>45143</v>
@@ -2031,16 +2136,16 @@
         <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D51" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E51" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F51" s="2">
         <v>45143</v>
@@ -2057,16 +2162,16 @@
         <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E52" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F52" s="2">
         <v>45143</v>
@@ -2083,16 +2188,16 @@
         <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F53" s="2">
         <v>45143</v>
@@ -2109,16 +2214,16 @@
         <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E54" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F54" s="2">
         <v>45143</v>
@@ -2135,16 +2240,16 @@
         <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E55" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F55" s="2">
         <v>45143</v>
@@ -2161,16 +2266,16 @@
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E56" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F56" s="2">
         <v>45143</v>
@@ -2187,16 +2292,16 @@
         <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F57" s="2">
         <v>45143</v>
@@ -2213,16 +2318,16 @@
         <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F58" s="2">
         <v>45143</v>
@@ -2239,16 +2344,16 @@
         <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F59" s="2">
         <v>45143</v>
@@ -2265,16 +2370,16 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F60" s="2">
         <v>45143</v>
@@ -2291,16 +2396,16 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D61" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F61" s="2">
         <v>45143</v>
@@ -2317,16 +2422,16 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E62" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F62" s="2">
         <v>45143</v>
@@ -2343,16 +2448,16 @@
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D63" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F63" s="2">
         <v>45143</v>
@@ -2369,16 +2474,16 @@
         <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F64" s="2">
         <v>45143</v>
@@ -2395,16 +2500,16 @@
         <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D65" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E65" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F65" s="2">
         <v>45143</v>
@@ -2421,16 +2526,16 @@
         <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F66" s="2">
         <v>45143</v>
@@ -2447,16 +2552,16 @@
         <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C67" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D67" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F67" s="2">
         <v>45143</v>
@@ -2473,16 +2578,16 @@
         <v>61</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D68" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E68" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F68" s="2">
         <v>45143</v>
@@ -2499,16 +2604,16 @@
         <v>62</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D69" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F69" s="2">
         <v>45143</v>
@@ -2525,16 +2630,16 @@
         <v>63</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D70" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F70" s="2">
         <v>45143</v>
@@ -2551,16 +2656,16 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E71" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="F71" s="2">
         <v>45147</v>
@@ -2577,16 +2682,16 @@
         <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D72" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E72" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="F72" s="2">
         <v>45147</v>
@@ -2603,16 +2708,16 @@
         <v>47</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E73" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="F73" s="2">
         <v>45147</v>
@@ -2629,16 +2734,16 @@
         <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C74" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D74" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E74" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="F74" s="2">
         <v>45147</v>
@@ -2655,16 +2760,16 @@
         <v>64</v>
       </c>
       <c r="B75" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C75" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D75" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E75" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="F75" s="2">
         <v>45147</v>
@@ -2681,16 +2786,16 @@
         <v>35</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D76" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E76" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="F76" s="2">
         <v>45147</v>
@@ -2707,16 +2812,16 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D77" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E77" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F77" s="2">
         <v>45147</v>
@@ -2733,16 +2838,16 @@
         <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C78" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E78" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F78" s="2">
         <v>45147</v>
@@ -2759,16 +2864,16 @@
         <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C79" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D79" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E79" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F79" s="2">
         <v>45147</v>
@@ -2785,16 +2890,16 @@
         <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D80" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E80" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F80" s="2">
         <v>45147</v>
@@ -2808,19 +2913,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C81" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D81" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E81" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F81" s="2">
         <v>45147</v>
@@ -2837,16 +2942,16 @@
         <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F82" s="2">
         <v>45147</v>
@@ -2863,16 +2968,16 @@
         <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E83" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F83" s="2">
         <v>45146</v>
@@ -2889,16 +2994,16 @@
         <v>63</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D84" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E84" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F84" s="2">
         <v>45146</v>
@@ -2915,16 +3020,16 @@
         <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C85" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D85" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E85" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F85" s="2">
         <v>45146</v>
@@ -2938,19 +3043,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E86" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F86" s="2">
         <v>45146</v>
@@ -2967,16 +3072,16 @@
         <v>47</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E87" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F87" s="2">
         <v>45146</v>
@@ -2990,19 +3095,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E88" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F88" s="2">
         <v>45146</v>
@@ -3019,16 +3124,16 @@
         <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E89" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F89" s="2">
         <v>45146</v>
@@ -3045,16 +3150,16 @@
         <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E90" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F90" s="2">
         <v>45146</v>
@@ -3071,16 +3176,16 @@
         <v>48</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E91" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F91" s="2">
         <v>45146</v>
@@ -3097,16 +3202,16 @@
         <v>64</v>
       </c>
       <c r="B92" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C92" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E92" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F92" s="2">
         <v>45146</v>
@@ -3123,16 +3228,16 @@
         <v>68</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E93" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F93" s="2">
         <v>45146</v>
@@ -3149,16 +3254,16 @@
         <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C94" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E94" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F94" s="2">
         <v>45146</v>
@@ -3175,16 +3280,16 @@
         <v>69</v>
       </c>
       <c r="B95" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C95" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E95" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F95" s="2">
         <v>45146</v>
@@ -3201,16 +3306,16 @@
         <v>38</v>
       </c>
       <c r="B96" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C96" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E96" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F96" s="2">
         <v>45146</v>
@@ -3227,16 +3332,16 @@
         <v>70</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E97" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F97" s="2">
         <v>45146</v>
@@ -3253,16 +3358,16 @@
         <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D98" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E98" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F98" s="2">
         <v>45146</v>
@@ -3279,16 +3384,16 @@
         <v>57</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D99" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E99" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F99" s="2">
         <v>45146</v>
@@ -3305,16 +3410,16 @@
         <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D100" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E100" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F100" s="2">
         <v>45146</v>
@@ -3331,16 +3436,16 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D101" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E101" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F101" s="2">
         <v>45146</v>
@@ -3357,16 +3462,16 @@
         <v>39</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D102" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E102" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F102" s="2">
         <v>45146</v>
@@ -3383,16 +3488,16 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D103" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E103" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F103" s="2">
         <v>45146</v>
@@ -3409,16 +3514,16 @@
         <v>53</v>
       </c>
       <c r="B104" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D104" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E104" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F104" s="2">
         <v>45146</v>
@@ -3435,16 +3540,16 @@
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C105" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D105" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F105" s="2">
         <v>45146</v>
@@ -3461,16 +3566,16 @@
         <v>73</v>
       </c>
       <c r="B106" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C106" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D106" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E106" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F106" s="2">
         <v>45146</v>
@@ -3487,16 +3592,16 @@
         <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D107" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E107" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F107" s="2">
         <v>45146</v>
@@ -3513,16 +3618,16 @@
         <v>60</v>
       </c>
       <c r="B108" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D108" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E108" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F108" s="2">
         <v>45146</v>
@@ -3539,16 +3644,16 @@
         <v>74</v>
       </c>
       <c r="B109" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D109" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E109" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F109" s="2">
         <v>45146</v>
@@ -3565,16 +3670,16 @@
         <v>75</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="C110" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D110" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E110" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F110" s="2">
         <v>45146</v>
@@ -3586,12 +3691,735 @@
         <v>126</v>
       </c>
     </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>76</v>
+      </c>
+      <c r="B111" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" t="s">
+        <v>129</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111" t="s">
+        <v>137</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G111">
+        <v>113.29</v>
+      </c>
+      <c r="H111">
+        <v>113.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>77</v>
+      </c>
+      <c r="B112" t="s">
+        <v>107</v>
+      </c>
+      <c r="C112" t="s">
+        <v>129</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+      <c r="E112" t="s">
+        <v>137</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G112">
+        <v>112.57</v>
+      </c>
+      <c r="H112">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" t="s">
+        <v>129</v>
+      </c>
+      <c r="D113">
+        <v>3</v>
+      </c>
+      <c r="E113" t="s">
+        <v>137</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G113">
+        <v>111.39</v>
+      </c>
+      <c r="H113">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>79</v>
+      </c>
+      <c r="B114" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" t="s">
+        <v>129</v>
+      </c>
+      <c r="D114">
+        <v>4</v>
+      </c>
+      <c r="E114" t="s">
+        <v>137</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G114">
+        <v>113.14</v>
+      </c>
+      <c r="H114">
+        <v>113.06</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>80</v>
+      </c>
+      <c r="B115" t="s">
+        <v>114</v>
+      </c>
+      <c r="C115" t="s">
+        <v>129</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115" t="s">
+        <v>137</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G115">
+        <v>126.35</v>
+      </c>
+      <c r="H115">
+        <v>126.56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>81</v>
+      </c>
+      <c r="B116" t="s">
+        <v>114</v>
+      </c>
+      <c r="C116" t="s">
+        <v>129</v>
+      </c>
+      <c r="D116">
+        <v>2</v>
+      </c>
+      <c r="E116" t="s">
+        <v>137</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G116">
+        <v>128.83000000000001</v>
+      </c>
+      <c r="H116">
+        <v>128.77000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>82</v>
+      </c>
+      <c r="B117" t="s">
+        <v>114</v>
+      </c>
+      <c r="C117" t="s">
+        <v>129</v>
+      </c>
+      <c r="D117">
+        <v>3</v>
+      </c>
+      <c r="E117" t="s">
+        <v>137</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G117">
+        <v>124.79</v>
+      </c>
+      <c r="H117">
+        <v>124.88</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>83</v>
+      </c>
+      <c r="B118" t="s">
+        <v>114</v>
+      </c>
+      <c r="C118" t="s">
+        <v>129</v>
+      </c>
+      <c r="D118">
+        <v>4</v>
+      </c>
+      <c r="E118" t="s">
+        <v>137</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G118">
+        <v>129.38999999999999</v>
+      </c>
+      <c r="H118">
+        <v>129.21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>84</v>
+      </c>
+      <c r="B119" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119" t="s">
+        <v>129</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>137</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G119">
+        <v>110.19</v>
+      </c>
+      <c r="H119">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>85</v>
+      </c>
+      <c r="B120" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" t="s">
+        <v>129</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120" t="s">
+        <v>137</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G120">
+        <v>110.3</v>
+      </c>
+      <c r="H120">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>86</v>
+      </c>
+      <c r="B121" t="s">
+        <v>106</v>
+      </c>
+      <c r="C121" t="s">
+        <v>129</v>
+      </c>
+      <c r="D121">
+        <v>3</v>
+      </c>
+      <c r="E121" t="s">
+        <v>137</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G121">
+        <v>110.27</v>
+      </c>
+      <c r="H121">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>87</v>
+      </c>
+      <c r="B122" t="s">
+        <v>106</v>
+      </c>
+      <c r="C122" t="s">
+        <v>129</v>
+      </c>
+      <c r="D122">
+        <v>4</v>
+      </c>
+      <c r="E122" t="s">
+        <v>137</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G122">
+        <v>110.59</v>
+      </c>
+      <c r="H122">
+        <v>110.45</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>88</v>
+      </c>
+      <c r="B123" t="s">
+        <v>113</v>
+      </c>
+      <c r="C123" t="s">
+        <v>129</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123" t="s">
+        <v>137</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G123">
+        <v>111.69</v>
+      </c>
+      <c r="H123">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>89</v>
+      </c>
+      <c r="B124" t="s">
+        <v>113</v>
+      </c>
+      <c r="C124" t="s">
+        <v>129</v>
+      </c>
+      <c r="D124">
+        <v>2</v>
+      </c>
+      <c r="E124" t="s">
+        <v>137</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G124">
+        <v>112.86</v>
+      </c>
+      <c r="H124">
+        <v>112.91</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>90</v>
+      </c>
+      <c r="B125" t="s">
+        <v>113</v>
+      </c>
+      <c r="C125" t="s">
+        <v>129</v>
+      </c>
+      <c r="D125">
+        <v>3</v>
+      </c>
+      <c r="E125" t="s">
+        <v>137</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G125">
+        <v>111.11</v>
+      </c>
+      <c r="H125">
+        <v>111.18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>91</v>
+      </c>
+      <c r="B126" t="s">
+        <v>113</v>
+      </c>
+      <c r="C126" t="s">
+        <v>129</v>
+      </c>
+      <c r="D126">
+        <v>4</v>
+      </c>
+      <c r="E126" t="s">
+        <v>137</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G126">
+        <v>119.42</v>
+      </c>
+      <c r="H126">
+        <v>119.57</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>92</v>
+      </c>
+      <c r="B127" t="s">
+        <v>108</v>
+      </c>
+      <c r="C127" t="s">
+        <v>129</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127" t="s">
+        <v>137</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G127">
+        <v>111.61</v>
+      </c>
+      <c r="H127">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>93</v>
+      </c>
+      <c r="B128" t="s">
+        <v>108</v>
+      </c>
+      <c r="C128" t="s">
+        <v>129</v>
+      </c>
+      <c r="D128">
+        <v>2</v>
+      </c>
+      <c r="E128" t="s">
+        <v>137</v>
+      </c>
+      <c r="F128" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G128">
+        <v>112.21</v>
+      </c>
+      <c r="H128">
+        <v>112.26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>94</v>
+      </c>
+      <c r="B129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C129" t="s">
+        <v>129</v>
+      </c>
+      <c r="D129">
+        <v>3</v>
+      </c>
+      <c r="E129" t="s">
+        <v>137</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G129">
+        <v>111.92</v>
+      </c>
+      <c r="H129">
+        <v>111.86</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>95</v>
+      </c>
+      <c r="B130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C130" t="s">
+        <v>129</v>
+      </c>
+      <c r="D130">
+        <v>4</v>
+      </c>
+      <c r="E130" t="s">
+        <v>137</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G130">
+        <v>112.25</v>
+      </c>
+      <c r="H130">
+        <v>112.26</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>96</v>
+      </c>
+      <c r="B131" t="s">
+        <v>104</v>
+      </c>
+      <c r="C131" t="s">
+        <v>129</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131" t="s">
+        <v>137</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G131">
+        <v>113.15</v>
+      </c>
+      <c r="H131">
+        <v>113.06</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>97</v>
+      </c>
+      <c r="B132" t="s">
+        <v>104</v>
+      </c>
+      <c r="C132" t="s">
+        <v>129</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+      <c r="E132" t="s">
+        <v>137</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G132">
+        <v>111.44</v>
+      </c>
+      <c r="H132">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>98</v>
+      </c>
+      <c r="B133" t="s">
+        <v>104</v>
+      </c>
+      <c r="C133" t="s">
+        <v>129</v>
+      </c>
+      <c r="D133">
+        <v>3</v>
+      </c>
+      <c r="E133" t="s">
+        <v>137</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G133">
+        <v>113.25</v>
+      </c>
+      <c r="H133">
+        <v>113.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>99</v>
+      </c>
+      <c r="B134" t="s">
+        <v>104</v>
+      </c>
+      <c r="C134" t="s">
+        <v>129</v>
+      </c>
+      <c r="D134">
+        <v>4</v>
+      </c>
+      <c r="E134" t="s">
+        <v>137</v>
+      </c>
+      <c r="F134" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G134">
+        <v>113.16</v>
+      </c>
+      <c r="H134">
+        <v>113.06</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>100</v>
+      </c>
+      <c r="B135" t="s">
+        <v>128</v>
+      </c>
+      <c r="C135" t="s">
+        <v>129</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135" t="s">
+        <v>137</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G135">
+        <v>111.95</v>
+      </c>
+      <c r="H135">
+        <v>111.86</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>101</v>
+      </c>
+      <c r="B136" t="s">
+        <v>128</v>
+      </c>
+      <c r="C136" t="s">
+        <v>129</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+      <c r="E136" t="s">
+        <v>137</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G136">
+        <v>111.39</v>
+      </c>
+      <c r="H136">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>102</v>
+      </c>
+      <c r="B137" t="s">
+        <v>128</v>
+      </c>
+      <c r="C137" t="s">
+        <v>129</v>
+      </c>
+      <c r="D137">
+        <v>3</v>
+      </c>
+      <c r="E137" t="s">
+        <v>137</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G137">
+        <v>111.39</v>
+      </c>
+      <c r="H137">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>103</v>
+      </c>
+      <c r="B138" t="s">
+        <v>128</v>
+      </c>
+      <c r="C138" t="s">
+        <v>129</v>
+      </c>
+      <c r="D138">
+        <v>4</v>
+      </c>
+      <c r="E138" t="s">
+        <v>137</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45142</v>
+      </c>
+      <c r="G138">
+        <v>111.91</v>
+      </c>
+      <c r="H138">
+        <v>111.86</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H110" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H110">
-      <sortCondition ref="E1:E110"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Gear_Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036F32A1-5462-4667-9BA5-25E904701878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAADA45-4C21-4783-B5AE-15F2190EBF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="142">
   <si>
     <t>Name</t>
   </si>
@@ -437,16 +437,28 @@
     <t>WCH</t>
   </si>
   <si>
-    <t>WCH 7-12 Final</t>
-  </si>
-  <si>
-    <t>WCH Gold Final</t>
-  </si>
-  <si>
-    <t>WCH R1</t>
-  </si>
-  <si>
-    <t>WCH WTP Q</t>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>B Final</t>
+  </si>
+  <si>
+    <t>A Final</t>
   </si>
 </sst>
 </file>
@@ -456,7 +468,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,6 +480,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -818,20 +836,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -839,25 +859,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -865,25 +891,31 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D2">
+        <v>135</v>
+      </c>
+      <c r="D2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="F2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="2">
         <v>45141</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>120.73</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>120.46</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -891,25 +923,31 @@
         <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="F3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="2">
         <v>45141</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>120.49</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>120.46</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -917,25 +955,31 @@
         <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4">
+        <v>135</v>
+      </c>
+      <c r="D4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="F4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="2">
         <v>45141</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>120.49</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>120.46</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -943,25 +987,31 @@
         <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5">
+        <v>135</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="F5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="2">
         <v>45141</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>120.47</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>120.46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -969,25 +1019,31 @@
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6">
+        <v>135</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="F6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="2">
         <v>45141</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>128.16999999999999</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>128.25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -995,25 +1051,31 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D7">
+        <v>135</v>
+      </c>
+      <c r="D7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="F7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="2">
         <v>45141</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>127.78</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>128.25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1021,25 +1083,31 @@
         <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8">
+        <v>135</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="F8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" t="s">
+        <v>138</v>
+      </c>
+      <c r="H8" s="2">
         <v>45141</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>127.78</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>128.25</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1047,25 +1115,31 @@
         <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9">
+        <v>135</v>
+      </c>
+      <c r="D9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="F9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9" s="2">
         <v>45141</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>128.18</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>128.25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1073,25 +1147,31 @@
         <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10">
+        <v>135</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="F10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="2">
         <v>45141</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>121.69</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>121.5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1099,25 +1179,31 @@
         <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11">
+        <v>135</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="E11" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="F11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" s="2">
         <v>45141</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>122.19</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>122.29</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1125,25 +1211,31 @@
         <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12">
+        <v>135</v>
+      </c>
+      <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="E12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="F12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="2">
         <v>45141</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>122.27</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>122.29</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1151,25 +1243,31 @@
         <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13">
+        <v>135</v>
+      </c>
+      <c r="D13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13">
         <v>4</v>
       </c>
-      <c r="E13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="F13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" s="2">
         <v>45141</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>121.9</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>122.29</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1177,25 +1275,31 @@
         <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14">
+        <v>135</v>
+      </c>
+      <c r="D14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="E14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="F14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="2">
         <v>45141</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>123.25</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>123.19</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1203,25 +1307,31 @@
         <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15">
+        <v>135</v>
+      </c>
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="E15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="F15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="2">
         <v>45141</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>123.98</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>123.88</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1229,25 +1339,31 @@
         <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16">
+        <v>135</v>
+      </c>
+      <c r="D16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="F16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="2">
         <v>45141</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>125.87</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1255,25 +1371,31 @@
         <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17">
+        <v>135</v>
+      </c>
+      <c r="D17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17">
         <v>4</v>
       </c>
-      <c r="E17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="F17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="2">
         <v>45141</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>125.13</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>125.18</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1281,25 +1403,31 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18">
+        <v>135</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="F18" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="2">
         <v>45141</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>121.68</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>121.5</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1307,25 +1435,31 @@
         <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19">
+        <v>135</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19">
         <v>2</v>
       </c>
-      <c r="E19" t="s">
-        <v>133</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="F19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="2">
         <v>45141</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>122.3</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>122.29</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1333,25 +1467,31 @@
         <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20">
+        <v>135</v>
+      </c>
+      <c r="D20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20">
         <v>3</v>
       </c>
-      <c r="E20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="F20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="2">
         <v>45141</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>123.83</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>123.88</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1359,25 +1499,31 @@
         <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21">
+        <v>135</v>
+      </c>
+      <c r="D21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21">
         <v>4</v>
       </c>
-      <c r="E21" t="s">
-        <v>133</v>
-      </c>
-      <c r="F21" s="2">
+      <c r="F21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" s="2">
         <v>45141</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>121.47</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>121.5</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1385,25 +1531,31 @@
         <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22">
+        <v>135</v>
+      </c>
+      <c r="D22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22">
         <v>1</v>
       </c>
-      <c r="E22" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="2">
+      <c r="F22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="2">
         <v>45142</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>128.01</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>127.8</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1411,25 +1563,31 @@
         <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23">
+        <v>135</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="E23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="F23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="2">
         <v>45142</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>127.42</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>127.29</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1437,25 +1595,31 @@
         <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24">
+        <v>135</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24">
         <v>3</v>
       </c>
-      <c r="E24" t="s">
-        <v>133</v>
-      </c>
-      <c r="F24" s="2">
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="2">
         <v>45142</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>127.42</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>127.29</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1463,25 +1627,31 @@
         <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25">
+        <v>135</v>
+      </c>
+      <c r="D25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25">
         <v>4</v>
       </c>
-      <c r="E25" t="s">
-        <v>133</v>
-      </c>
-      <c r="F25" s="2">
+      <c r="F25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="2">
         <v>45142</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>129.34</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>129.21</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -1489,25 +1659,31 @@
         <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26">
+        <v>135</v>
+      </c>
+      <c r="D26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="E26" t="s">
-        <v>133</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="F26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" s="2">
         <v>45143</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>127.75</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>127.8</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1515,25 +1691,31 @@
         <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27">
+        <v>135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27">
         <v>2</v>
       </c>
-      <c r="E27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="2">
+      <c r="F27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27" s="2">
         <v>45143</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>127.74</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>127.8</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1541,25 +1723,31 @@
         <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28">
+        <v>135</v>
+      </c>
+      <c r="D28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28">
         <v>3</v>
       </c>
-      <c r="E28" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" s="2">
+      <c r="F28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28" s="2">
         <v>45143</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>127.74</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>127.8</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1567,25 +1755,31 @@
         <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29">
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29">
         <v>4</v>
       </c>
-      <c r="E29" t="s">
-        <v>133</v>
-      </c>
-      <c r="F29" s="2">
+      <c r="F29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="2">
         <v>45143</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>127.79</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>127.8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -1593,25 +1787,31 @@
         <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30">
+        <v>135</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30">
         <v>1</v>
       </c>
-      <c r="E30" t="s">
-        <v>133</v>
-      </c>
-      <c r="F30" s="2">
+      <c r="F30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" s="2">
         <v>45143</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>121.63</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>121.5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1619,25 +1819,31 @@
         <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31">
+        <v>135</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31">
         <v>2</v>
       </c>
-      <c r="E31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F31" s="2">
+      <c r="F31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" s="2">
         <v>45143</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>121.4</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>121.5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1645,25 +1851,31 @@
         <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32">
+        <v>135</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32">
         <v>3</v>
       </c>
-      <c r="E32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F32" s="2">
+      <c r="F32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="2">
         <v>45143</v>
       </c>
-      <c r="G32">
+      <c r="I32">
         <v>123.6</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>123.75</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -1671,25 +1883,31 @@
         <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33">
+        <v>135</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33">
         <v>4</v>
       </c>
-      <c r="E33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F33" s="2">
+      <c r="F33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" t="s">
+        <v>139</v>
+      </c>
+      <c r="H33" s="2">
         <v>45143</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>121.29</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>121.5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -1697,25 +1915,31 @@
         <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34">
+        <v>135</v>
+      </c>
+      <c r="D34" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34">
         <v>1</v>
       </c>
-      <c r="E34" t="s">
-        <v>133</v>
-      </c>
-      <c r="F34" s="2">
+      <c r="F34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34" s="2">
         <v>45142</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>120.74</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>120.71</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -1723,25 +1947,31 @@
         <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="E35" t="s">
-        <v>133</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="F35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35" s="2">
         <v>45142</v>
       </c>
-      <c r="G35">
+      <c r="I35">
         <v>122.5</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>122.54</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -1749,25 +1979,31 @@
         <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36">
+        <v>135</v>
+      </c>
+      <c r="D36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36">
         <v>3</v>
       </c>
-      <c r="E36" t="s">
-        <v>133</v>
-      </c>
-      <c r="F36" s="2">
+      <c r="F36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G36" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36" s="2">
         <v>45142</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>124.75</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>124.62</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -1775,25 +2011,31 @@
         <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37">
+        <v>135</v>
+      </c>
+      <c r="D37" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37">
         <v>4</v>
       </c>
-      <c r="E37" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="2">
+      <c r="F37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" t="s">
+        <v>139</v>
+      </c>
+      <c r="H37" s="2">
         <v>45142</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>123.96</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>123.88</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -1801,25 +2043,31 @@
         <v>109</v>
       </c>
       <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="s">
         <v>130</v>
       </c>
-      <c r="D38" t="s">
-        <v>132</v>
-      </c>
       <c r="E38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F38" s="2">
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" s="2">
         <v>45143</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>135.25</v>
       </c>
-      <c r="H38">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -1827,25 +2075,31 @@
         <v>110</v>
       </c>
       <c r="C39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" t="s">
         <v>130</v>
       </c>
-      <c r="D39" t="s">
-        <v>132</v>
-      </c>
       <c r="E39" t="s">
-        <v>133</v>
-      </c>
-      <c r="F39" s="2">
+        <v>132</v>
+      </c>
+      <c r="F39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G39" t="s">
+        <v>138</v>
+      </c>
+      <c r="H39" s="2">
         <v>45143</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>132.49</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>132.55000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -1853,25 +2107,31 @@
         <v>106</v>
       </c>
       <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" t="s">
         <v>130</v>
       </c>
-      <c r="D40" t="s">
-        <v>132</v>
-      </c>
       <c r="E40" t="s">
-        <v>133</v>
-      </c>
-      <c r="F40" s="2">
+        <v>132</v>
+      </c>
+      <c r="F40" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H40" s="2">
         <v>45143</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>133.4</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>133.31</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -1879,25 +2139,31 @@
         <v>111</v>
       </c>
       <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="s">
         <v>130</v>
       </c>
-      <c r="D41" t="s">
-        <v>132</v>
-      </c>
       <c r="E41" t="s">
-        <v>133</v>
-      </c>
-      <c r="F41" s="2">
+        <v>132</v>
+      </c>
+      <c r="F41" t="s">
+        <v>133</v>
+      </c>
+      <c r="G41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="2">
         <v>45143</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>130.80000000000001</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>130.85</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -1905,25 +2171,31 @@
         <v>107</v>
       </c>
       <c r="C42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" t="s">
         <v>130</v>
       </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
       <c r="E42" t="s">
-        <v>133</v>
-      </c>
-      <c r="F42" s="2">
+        <v>132</v>
+      </c>
+      <c r="F42" t="s">
+        <v>133</v>
+      </c>
+      <c r="G42" t="s">
+        <v>138</v>
+      </c>
+      <c r="H42" s="2">
         <v>45143</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>128.87</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>128.77000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -1931,25 +2203,31 @@
         <v>104</v>
       </c>
       <c r="C43" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" t="s">
         <v>130</v>
       </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
       <c r="E43" t="s">
-        <v>133</v>
-      </c>
-      <c r="F43" s="2">
+        <v>132</v>
+      </c>
+      <c r="F43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43" t="s">
+        <v>138</v>
+      </c>
+      <c r="H43" s="2">
         <v>45143</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>134.36000000000001</v>
       </c>
-      <c r="H43">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -1957,25 +2235,31 @@
         <v>112</v>
       </c>
       <c r="C44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" t="s">
         <v>130</v>
       </c>
-      <c r="D44" t="s">
-        <v>132</v>
-      </c>
       <c r="E44" t="s">
-        <v>133</v>
-      </c>
-      <c r="F44" s="2">
+        <v>132</v>
+      </c>
+      <c r="F44" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H44" s="2">
         <v>45143</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>129.68</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>129.6</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -1983,25 +2267,31 @@
         <v>113</v>
       </c>
       <c r="C45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" t="s">
         <v>130</v>
       </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
       <c r="E45" t="s">
-        <v>133</v>
-      </c>
-      <c r="F45" s="2">
+        <v>132</v>
+      </c>
+      <c r="F45" t="s">
+        <v>133</v>
+      </c>
+      <c r="G45" t="s">
+        <v>138</v>
+      </c>
+      <c r="H45" s="2">
         <v>45143</v>
       </c>
-      <c r="G45">
+      <c r="I45">
         <v>129.32</v>
       </c>
-      <c r="H45">
+      <c r="J45">
         <v>129.21</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -2009,25 +2299,31 @@
         <v>107</v>
       </c>
       <c r="C46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" t="s">
         <v>130</v>
       </c>
-      <c r="D46" t="s">
-        <v>132</v>
-      </c>
       <c r="E46" t="s">
-        <v>133</v>
-      </c>
-      <c r="F46" s="2">
+        <v>132</v>
+      </c>
+      <c r="F46" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" s="2">
         <v>45143</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>136.58000000000001</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>136.80000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -2035,25 +2331,31 @@
         <v>114</v>
       </c>
       <c r="C47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" t="s">
         <v>130</v>
       </c>
-      <c r="D47" t="s">
-        <v>132</v>
-      </c>
       <c r="E47" t="s">
-        <v>133</v>
-      </c>
-      <c r="F47" s="2">
+        <v>132</v>
+      </c>
+      <c r="F47" t="s">
+        <v>133</v>
+      </c>
+      <c r="G47" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="2">
         <v>45143</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>133.88999999999999</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>133.31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -2061,25 +2363,31 @@
         <v>115</v>
       </c>
       <c r="C48" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" t="s">
         <v>130</v>
       </c>
-      <c r="D48" t="s">
-        <v>132</v>
-      </c>
       <c r="E48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F48" s="2">
+        <v>132</v>
+      </c>
+      <c r="F48" t="s">
+        <v>133</v>
+      </c>
+      <c r="G48" t="s">
+        <v>138</v>
+      </c>
+      <c r="H48" s="2">
         <v>45143</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>135.24</v>
       </c>
-      <c r="H48">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J48">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -2087,25 +2395,31 @@
         <v>115</v>
       </c>
       <c r="C49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" t="s">
         <v>130</v>
       </c>
-      <c r="D49" t="s">
-        <v>132</v>
-      </c>
       <c r="E49" t="s">
-        <v>133</v>
-      </c>
-      <c r="F49" s="2">
+        <v>132</v>
+      </c>
+      <c r="F49" t="s">
+        <v>133</v>
+      </c>
+      <c r="G49" t="s">
+        <v>138</v>
+      </c>
+      <c r="H49" s="2">
         <v>45143</v>
       </c>
-      <c r="G49">
+      <c r="I49">
         <v>134.28</v>
       </c>
-      <c r="H49">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J49">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>43</v>
       </c>
@@ -2113,25 +2427,31 @@
         <v>116</v>
       </c>
       <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
         <v>130</v>
       </c>
-      <c r="D50" t="s">
-        <v>132</v>
-      </c>
       <c r="E50" t="s">
-        <v>133</v>
-      </c>
-      <c r="F50" s="2">
+        <v>132</v>
+      </c>
+      <c r="F50" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H50" s="2">
         <v>45143</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>139.72999999999999</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>139.91</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -2139,25 +2459,31 @@
         <v>117</v>
       </c>
       <c r="C51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" t="s">
         <v>130</v>
       </c>
-      <c r="D51" t="s">
-        <v>132</v>
-      </c>
       <c r="E51" t="s">
-        <v>133</v>
-      </c>
-      <c r="F51" s="2">
+        <v>132</v>
+      </c>
+      <c r="F51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G51" t="s">
+        <v>138</v>
+      </c>
+      <c r="H51" s="2">
         <v>45143</v>
       </c>
-      <c r="G51">
+      <c r="I51">
         <v>130.91</v>
       </c>
-      <c r="H51">
+      <c r="J51">
         <v>130.85</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -2165,25 +2491,31 @@
         <v>110</v>
       </c>
       <c r="C52" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" t="s">
         <v>130</v>
       </c>
-      <c r="D52" t="s">
-        <v>132</v>
-      </c>
       <c r="E52" t="s">
-        <v>133</v>
-      </c>
-      <c r="F52" s="2">
+        <v>132</v>
+      </c>
+      <c r="F52" t="s">
+        <v>133</v>
+      </c>
+      <c r="G52" t="s">
+        <v>138</v>
+      </c>
+      <c r="H52" s="2">
         <v>45143</v>
       </c>
-      <c r="G52">
+      <c r="I52">
         <v>135.26</v>
       </c>
-      <c r="H52">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J52">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -2191,25 +2523,31 @@
         <v>118</v>
       </c>
       <c r="C53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" t="s">
         <v>130</v>
       </c>
-      <c r="D53" t="s">
-        <v>132</v>
-      </c>
       <c r="E53" t="s">
-        <v>133</v>
-      </c>
-      <c r="F53" s="2">
+        <v>132</v>
+      </c>
+      <c r="F53" t="s">
+        <v>133</v>
+      </c>
+      <c r="G53" t="s">
+        <v>138</v>
+      </c>
+      <c r="H53" s="2">
         <v>45143</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>131.72999999999999</v>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>131.63</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -2217,25 +2555,31 @@
         <v>119</v>
       </c>
       <c r="C54" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" t="s">
         <v>130</v>
       </c>
-      <c r="D54" t="s">
-        <v>132</v>
-      </c>
       <c r="E54" t="s">
-        <v>133</v>
-      </c>
-      <c r="F54" s="2">
+        <v>132</v>
+      </c>
+      <c r="F54" t="s">
+        <v>133</v>
+      </c>
+      <c r="G54" t="s">
+        <v>138</v>
+      </c>
+      <c r="H54" s="2">
         <v>45143</v>
       </c>
-      <c r="G54">
+      <c r="I54">
         <v>139.29</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>139.15</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>48</v>
       </c>
@@ -2243,25 +2587,31 @@
         <v>120</v>
       </c>
       <c r="C55" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" t="s">
         <v>130</v>
       </c>
-      <c r="D55" t="s">
-        <v>132</v>
-      </c>
       <c r="E55" t="s">
-        <v>133</v>
-      </c>
-      <c r="F55" s="2">
+        <v>132</v>
+      </c>
+      <c r="F55" t="s">
+        <v>133</v>
+      </c>
+      <c r="G55" t="s">
+        <v>138</v>
+      </c>
+      <c r="H55" s="2">
         <v>45143</v>
       </c>
-      <c r="G55">
+      <c r="I55">
         <v>140.76</v>
       </c>
-      <c r="H55">
+      <c r="J55">
         <v>140.79</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -2269,25 +2619,31 @@
         <v>108</v>
       </c>
       <c r="C56" t="s">
+        <v>135</v>
+      </c>
+      <c r="D56" t="s">
         <v>130</v>
       </c>
-      <c r="D56" t="s">
-        <v>132</v>
-      </c>
       <c r="E56" t="s">
-        <v>133</v>
-      </c>
-      <c r="F56" s="2">
+        <v>132</v>
+      </c>
+      <c r="F56" t="s">
+        <v>133</v>
+      </c>
+      <c r="G56" t="s">
+        <v>138</v>
+      </c>
+      <c r="H56" s="2">
         <v>45143</v>
       </c>
-      <c r="G56">
+      <c r="I56">
         <v>119.48</v>
       </c>
-      <c r="H56">
+      <c r="J56">
         <v>119.57</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -2295,25 +2651,31 @@
         <v>118</v>
       </c>
       <c r="C57" t="s">
+        <v>135</v>
+      </c>
+      <c r="D57" t="s">
         <v>130</v>
       </c>
-      <c r="D57" t="s">
-        <v>132</v>
-      </c>
       <c r="E57" t="s">
-        <v>133</v>
-      </c>
-      <c r="F57" s="2">
+        <v>132</v>
+      </c>
+      <c r="F57" t="s">
+        <v>133</v>
+      </c>
+      <c r="G57" t="s">
+        <v>138</v>
+      </c>
+      <c r="H57" s="2">
         <v>45143</v>
       </c>
-      <c r="G57">
+      <c r="I57">
         <v>131.78</v>
       </c>
-      <c r="H57">
+      <c r="J57">
         <v>131.63</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -2321,25 +2683,31 @@
         <v>107</v>
       </c>
       <c r="C58" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" t="s">
         <v>130</v>
       </c>
-      <c r="D58" t="s">
-        <v>132</v>
-      </c>
       <c r="E58" t="s">
-        <v>133</v>
-      </c>
-      <c r="F58" s="2">
+        <v>132</v>
+      </c>
+      <c r="F58" t="s">
+        <v>133</v>
+      </c>
+      <c r="G58" t="s">
+        <v>138</v>
+      </c>
+      <c r="H58" s="2">
         <v>45143</v>
       </c>
-      <c r="G58">
+      <c r="I58">
         <v>134.33000000000001</v>
       </c>
-      <c r="H58">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J58">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -2347,25 +2715,31 @@
         <v>121</v>
       </c>
       <c r="C59" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" t="s">
         <v>130</v>
       </c>
-      <c r="D59" t="s">
-        <v>132</v>
-      </c>
       <c r="E59" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="2">
+        <v>132</v>
+      </c>
+      <c r="F59" t="s">
+        <v>133</v>
+      </c>
+      <c r="G59" t="s">
+        <v>138</v>
+      </c>
+      <c r="H59" s="2">
         <v>45143</v>
       </c>
-      <c r="G59">
+      <c r="I59">
         <v>138.93</v>
       </c>
-      <c r="H59">
+      <c r="J59">
         <v>138.86000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -2373,25 +2747,31 @@
         <v>110</v>
       </c>
       <c r="C60" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" t="s">
         <v>130</v>
       </c>
-      <c r="D60" t="s">
-        <v>132</v>
-      </c>
       <c r="E60" t="s">
-        <v>133</v>
-      </c>
-      <c r="F60" s="2">
+        <v>132</v>
+      </c>
+      <c r="F60" t="s">
+        <v>133</v>
+      </c>
+      <c r="G60" t="s">
+        <v>138</v>
+      </c>
+      <c r="H60" s="2">
         <v>45143</v>
       </c>
-      <c r="G60">
+      <c r="I60">
         <v>142.38999999999999</v>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>142.36000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -2399,25 +2779,31 @@
         <v>121</v>
       </c>
       <c r="C61" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" t="s">
         <v>130</v>
       </c>
-      <c r="D61" t="s">
-        <v>132</v>
-      </c>
       <c r="E61" t="s">
-        <v>133</v>
-      </c>
-      <c r="F61" s="2">
+        <v>132</v>
+      </c>
+      <c r="F61" t="s">
+        <v>133</v>
+      </c>
+      <c r="G61" t="s">
+        <v>138</v>
+      </c>
+      <c r="H61" s="2">
         <v>45143</v>
       </c>
-      <c r="G61">
+      <c r="I61">
         <v>137.91</v>
       </c>
-      <c r="H61">
+      <c r="J61">
         <v>137.69999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -2425,25 +2811,31 @@
         <v>122</v>
       </c>
       <c r="C62" t="s">
+        <v>135</v>
+      </c>
+      <c r="D62" t="s">
         <v>130</v>
       </c>
-      <c r="D62" t="s">
-        <v>132</v>
-      </c>
       <c r="E62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F62" s="2">
+        <v>132</v>
+      </c>
+      <c r="F62" t="s">
+        <v>133</v>
+      </c>
+      <c r="G62" t="s">
+        <v>138</v>
+      </c>
+      <c r="H62" s="2">
         <v>45143</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>132.57</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>132.55000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -2451,25 +2843,31 @@
         <v>119</v>
       </c>
       <c r="C63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" t="s">
         <v>130</v>
       </c>
-      <c r="D63" t="s">
-        <v>132</v>
-      </c>
       <c r="E63" t="s">
-        <v>133</v>
-      </c>
-      <c r="F63" s="2">
+        <v>132</v>
+      </c>
+      <c r="F63" t="s">
+        <v>133</v>
+      </c>
+      <c r="G63" t="s">
+        <v>138</v>
+      </c>
+      <c r="H63" s="2">
         <v>45143</v>
       </c>
-      <c r="G63">
+      <c r="I63">
         <v>128.46</v>
       </c>
-      <c r="H63">
+      <c r="J63">
         <v>128.25</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -2477,25 +2875,31 @@
         <v>123</v>
       </c>
       <c r="C64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" t="s">
         <v>130</v>
       </c>
-      <c r="D64" t="s">
-        <v>132</v>
-      </c>
       <c r="E64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F64" s="2">
+        <v>132</v>
+      </c>
+      <c r="F64" t="s">
+        <v>133</v>
+      </c>
+      <c r="G64" t="s">
+        <v>138</v>
+      </c>
+      <c r="H64" s="2">
         <v>45143</v>
       </c>
-      <c r="G64">
+      <c r="I64">
         <v>133.41</v>
       </c>
-      <c r="H64">
+      <c r="J64">
         <v>133.31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -2503,25 +2907,31 @@
         <v>106</v>
       </c>
       <c r="C65" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" t="s">
         <v>130</v>
       </c>
-      <c r="D65" t="s">
-        <v>132</v>
-      </c>
       <c r="E65" t="s">
-        <v>133</v>
-      </c>
-      <c r="F65" s="2">
+        <v>132</v>
+      </c>
+      <c r="F65" t="s">
+        <v>133</v>
+      </c>
+      <c r="G65" t="s">
+        <v>138</v>
+      </c>
+      <c r="H65" s="2">
         <v>45143</v>
       </c>
-      <c r="G65">
+      <c r="I65">
         <v>126.68</v>
       </c>
-      <c r="H65">
+      <c r="J65">
         <v>126.69</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -2529,25 +2939,31 @@
         <v>115</v>
       </c>
       <c r="C66" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" t="s">
         <v>130</v>
       </c>
-      <c r="D66" t="s">
-        <v>132</v>
-      </c>
       <c r="E66" t="s">
-        <v>133</v>
-      </c>
-      <c r="F66" s="2">
+        <v>132</v>
+      </c>
+      <c r="F66" t="s">
+        <v>133</v>
+      </c>
+      <c r="G66" t="s">
+        <v>138</v>
+      </c>
+      <c r="H66" s="2">
         <v>45143</v>
       </c>
-      <c r="G66">
+      <c r="I66">
         <v>130.86000000000001</v>
       </c>
-      <c r="H66">
+      <c r="J66">
         <v>130.85</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -2555,25 +2971,31 @@
         <v>114</v>
       </c>
       <c r="C67" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" t="s">
         <v>130</v>
       </c>
-      <c r="D67" t="s">
-        <v>132</v>
-      </c>
       <c r="E67" t="s">
-        <v>133</v>
-      </c>
-      <c r="F67" s="2">
+        <v>132</v>
+      </c>
+      <c r="F67" t="s">
+        <v>133</v>
+      </c>
+      <c r="G67" t="s">
+        <v>138</v>
+      </c>
+      <c r="H67" s="2">
         <v>45143</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>140.13</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>139.91</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>61</v>
       </c>
@@ -2581,25 +3003,31 @@
         <v>112</v>
       </c>
       <c r="C68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s">
         <v>130</v>
       </c>
-      <c r="D68" t="s">
-        <v>132</v>
-      </c>
       <c r="E68" t="s">
-        <v>133</v>
-      </c>
-      <c r="F68" s="2">
+        <v>132</v>
+      </c>
+      <c r="F68" t="s">
+        <v>133</v>
+      </c>
+      <c r="G68" t="s">
+        <v>138</v>
+      </c>
+      <c r="H68" s="2">
         <v>45143</v>
       </c>
-      <c r="G68">
+      <c r="I68">
         <v>137.49</v>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>137.44999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>62</v>
       </c>
@@ -2607,25 +3035,31 @@
         <v>113</v>
       </c>
       <c r="C69" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" t="s">
         <v>130</v>
       </c>
-      <c r="D69" t="s">
-        <v>132</v>
-      </c>
       <c r="E69" t="s">
-        <v>133</v>
-      </c>
-      <c r="F69" s="2">
+        <v>132</v>
+      </c>
+      <c r="F69" t="s">
+        <v>133</v>
+      </c>
+      <c r="G69" t="s">
+        <v>138</v>
+      </c>
+      <c r="H69" s="2">
         <v>45143</v>
       </c>
-      <c r="G69">
+      <c r="I69">
         <v>120.58</v>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>120.6</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>63</v>
       </c>
@@ -2633,25 +3067,31 @@
         <v>124</v>
       </c>
       <c r="C70" t="s">
+        <v>135</v>
+      </c>
+      <c r="D70" t="s">
         <v>130</v>
       </c>
-      <c r="D70" t="s">
-        <v>132</v>
-      </c>
       <c r="E70" t="s">
-        <v>133</v>
-      </c>
-      <c r="F70" s="2">
+        <v>132</v>
+      </c>
+      <c r="F70" t="s">
+        <v>133</v>
+      </c>
+      <c r="G70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H70" s="2">
         <v>45143</v>
       </c>
-      <c r="G70">
+      <c r="I70">
         <v>138.85</v>
       </c>
-      <c r="H70">
+      <c r="J70">
         <v>138.86000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -2659,25 +3099,31 @@
         <v>107</v>
       </c>
       <c r="C71" t="s">
+        <v>135</v>
+      </c>
+      <c r="D71" t="s">
         <v>131</v>
       </c>
-      <c r="D71" t="s">
-        <v>132</v>
-      </c>
       <c r="E71" t="s">
-        <v>134</v>
-      </c>
-      <c r="F71" s="2">
+        <v>132</v>
+      </c>
+      <c r="F71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G71" t="s">
+        <v>140</v>
+      </c>
+      <c r="H71" s="2">
         <v>45147</v>
       </c>
-      <c r="G71">
+      <c r="I71">
         <v>120.98</v>
       </c>
-      <c r="H71">
+      <c r="J71">
         <v>120.71</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>63</v>
       </c>
@@ -2685,25 +3131,31 @@
         <v>124</v>
       </c>
       <c r="C72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72" t="s">
         <v>131</v>
       </c>
-      <c r="D72" t="s">
-        <v>132</v>
-      </c>
       <c r="E72" t="s">
-        <v>134</v>
-      </c>
-      <c r="F72" s="2">
+        <v>132</v>
+      </c>
+      <c r="F72" t="s">
+        <v>133</v>
+      </c>
+      <c r="G72" t="s">
+        <v>140</v>
+      </c>
+      <c r="H72" s="2">
         <v>45147</v>
       </c>
-      <c r="G72">
+      <c r="I72">
         <v>134.69</v>
       </c>
-      <c r="H72">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J72">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>47</v>
       </c>
@@ -2711,25 +3163,31 @@
         <v>119</v>
       </c>
       <c r="C73" t="s">
+        <v>135</v>
+      </c>
+      <c r="D73" t="s">
         <v>131</v>
       </c>
-      <c r="D73" t="s">
-        <v>132</v>
-      </c>
       <c r="E73" t="s">
-        <v>134</v>
-      </c>
-      <c r="F73" s="2">
+        <v>132</v>
+      </c>
+      <c r="F73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G73" t="s">
+        <v>140</v>
+      </c>
+      <c r="H73" s="2">
         <v>45147</v>
       </c>
-      <c r="G73">
+      <c r="I73">
         <v>134.06</v>
       </c>
-      <c r="H73">
+      <c r="J73">
         <v>133.31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>32</v>
       </c>
@@ -2737,25 +3195,31 @@
         <v>110</v>
       </c>
       <c r="C74" t="s">
+        <v>135</v>
+      </c>
+      <c r="D74" t="s">
         <v>131</v>
       </c>
-      <c r="D74" t="s">
-        <v>132</v>
-      </c>
       <c r="E74" t="s">
-        <v>134</v>
-      </c>
-      <c r="F74" s="2">
+        <v>132</v>
+      </c>
+      <c r="F74" t="s">
+        <v>133</v>
+      </c>
+      <c r="G74" t="s">
+        <v>140</v>
+      </c>
+      <c r="H74" s="2">
         <v>45147</v>
       </c>
-      <c r="G74">
+      <c r="I74">
         <v>129.27000000000001</v>
       </c>
-      <c r="H74">
+      <c r="J74">
         <v>129.21</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>64</v>
       </c>
@@ -2763,25 +3227,31 @@
         <v>106</v>
       </c>
       <c r="C75" t="s">
+        <v>135</v>
+      </c>
+      <c r="D75" t="s">
         <v>131</v>
       </c>
-      <c r="D75" t="s">
-        <v>132</v>
-      </c>
       <c r="E75" t="s">
-        <v>134</v>
-      </c>
-      <c r="F75" s="2">
+        <v>132</v>
+      </c>
+      <c r="F75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G75" t="s">
+        <v>140</v>
+      </c>
+      <c r="H75" s="2">
         <v>45147</v>
       </c>
-      <c r="G75">
+      <c r="I75">
         <v>123.65</v>
       </c>
-      <c r="H75">
+      <c r="J75">
         <v>123.75</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>35</v>
       </c>
@@ -2789,25 +3259,31 @@
         <v>107</v>
       </c>
       <c r="C76" t="s">
+        <v>135</v>
+      </c>
+      <c r="D76" t="s">
         <v>131</v>
       </c>
-      <c r="D76" t="s">
-        <v>132</v>
-      </c>
       <c r="E76" t="s">
-        <v>134</v>
-      </c>
-      <c r="F76" s="2">
+        <v>132</v>
+      </c>
+      <c r="F76" t="s">
+        <v>133</v>
+      </c>
+      <c r="G76" t="s">
+        <v>140</v>
+      </c>
+      <c r="H76" s="2">
         <v>45147</v>
       </c>
-      <c r="G76">
+      <c r="I76">
         <v>117.92</v>
       </c>
-      <c r="H76">
+      <c r="J76">
         <v>117.82</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>41</v>
       </c>
@@ -2815,25 +3291,31 @@
         <v>115</v>
       </c>
       <c r="C77" t="s">
+        <v>135</v>
+      </c>
+      <c r="D77" t="s">
         <v>131</v>
       </c>
-      <c r="D77" t="s">
-        <v>132</v>
-      </c>
       <c r="E77" t="s">
-        <v>135</v>
-      </c>
-      <c r="F77" s="2">
+        <v>132</v>
+      </c>
+      <c r="F77" t="s">
+        <v>133</v>
+      </c>
+      <c r="G77" t="s">
+        <v>141</v>
+      </c>
+      <c r="H77" s="2">
         <v>45147</v>
       </c>
-      <c r="G77">
+      <c r="I77">
         <v>119.49</v>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>119.57</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>51</v>
       </c>
@@ -2841,25 +3323,31 @@
         <v>107</v>
       </c>
       <c r="C78" t="s">
+        <v>135</v>
+      </c>
+      <c r="D78" t="s">
         <v>131</v>
       </c>
-      <c r="D78" t="s">
-        <v>132</v>
-      </c>
       <c r="E78" t="s">
-        <v>135</v>
-      </c>
-      <c r="F78" s="2">
+        <v>132</v>
+      </c>
+      <c r="F78" t="s">
+        <v>133</v>
+      </c>
+      <c r="G78" t="s">
+        <v>141</v>
+      </c>
+      <c r="H78" s="2">
         <v>45147</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>126.69</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>126.69</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2867,25 +3355,31 @@
         <v>119</v>
       </c>
       <c r="C79" t="s">
+        <v>135</v>
+      </c>
+      <c r="D79" t="s">
         <v>131</v>
       </c>
-      <c r="D79" t="s">
-        <v>132</v>
-      </c>
       <c r="E79" t="s">
-        <v>135</v>
-      </c>
-      <c r="F79" s="2">
+        <v>132</v>
+      </c>
+      <c r="F79" t="s">
+        <v>133</v>
+      </c>
+      <c r="G79" t="s">
+        <v>141</v>
+      </c>
+      <c r="H79" s="2">
         <v>45147</v>
       </c>
-      <c r="G79">
+      <c r="I79">
         <v>134.6</v>
       </c>
-      <c r="H79">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J79">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>33</v>
       </c>
@@ -2893,25 +3387,31 @@
         <v>106</v>
       </c>
       <c r="C80" t="s">
+        <v>135</v>
+      </c>
+      <c r="D80" t="s">
         <v>131</v>
       </c>
-      <c r="D80" t="s">
-        <v>132</v>
-      </c>
       <c r="E80" t="s">
-        <v>135</v>
-      </c>
-      <c r="F80" s="2">
+        <v>132</v>
+      </c>
+      <c r="F80" t="s">
+        <v>133</v>
+      </c>
+      <c r="G80" t="s">
+        <v>141</v>
+      </c>
+      <c r="H80" s="2">
         <v>45147</v>
       </c>
-      <c r="G80">
+      <c r="I80">
         <v>125.9</v>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>126</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2919,25 +3419,31 @@
         <v>118</v>
       </c>
       <c r="C81" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" t="s">
         <v>131</v>
       </c>
-      <c r="D81" t="s">
-        <v>132</v>
-      </c>
       <c r="E81" t="s">
-        <v>135</v>
-      </c>
-      <c r="F81" s="2">
+        <v>132</v>
+      </c>
+      <c r="F81" t="s">
+        <v>133</v>
+      </c>
+      <c r="G81" t="s">
+        <v>141</v>
+      </c>
+      <c r="H81" s="2">
         <v>45147</v>
       </c>
-      <c r="G81">
+      <c r="I81">
         <v>127.8</v>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>127.8</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>42</v>
       </c>
@@ -2945,25 +3451,31 @@
         <v>115</v>
       </c>
       <c r="C82" t="s">
+        <v>135</v>
+      </c>
+      <c r="D82" t="s">
         <v>131</v>
       </c>
-      <c r="D82" t="s">
-        <v>132</v>
-      </c>
       <c r="E82" t="s">
-        <v>135</v>
-      </c>
-      <c r="F82" s="2">
+        <v>132</v>
+      </c>
+      <c r="F82" t="s">
+        <v>133</v>
+      </c>
+      <c r="G82" t="s">
+        <v>141</v>
+      </c>
+      <c r="H82" s="2">
         <v>45147</v>
       </c>
-      <c r="G82">
+      <c r="I82">
         <v>121.06</v>
       </c>
-      <c r="H82">
+      <c r="J82">
         <v>120.71</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>33</v>
       </c>
@@ -2971,25 +3483,31 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
+        <v>135</v>
+      </c>
+      <c r="D83" t="s">
         <v>131</v>
       </c>
-      <c r="D83" t="s">
-        <v>132</v>
-      </c>
       <c r="E83" t="s">
-        <v>136</v>
-      </c>
-      <c r="F83" s="2">
+        <v>132</v>
+      </c>
+      <c r="F83" t="s">
+        <v>133</v>
+      </c>
+      <c r="G83" t="s">
+        <v>139</v>
+      </c>
+      <c r="H83" s="2">
         <v>45146</v>
       </c>
-      <c r="G83">
+      <c r="I83">
         <v>124.31</v>
       </c>
-      <c r="H83">
+      <c r="J83">
         <v>124.2</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>63</v>
       </c>
@@ -2997,25 +3515,31 @@
         <v>124</v>
       </c>
       <c r="C84" t="s">
+        <v>135</v>
+      </c>
+      <c r="D84" t="s">
         <v>131</v>
       </c>
-      <c r="D84" t="s">
-        <v>132</v>
-      </c>
       <c r="E84" t="s">
-        <v>136</v>
-      </c>
-      <c r="F84" s="2">
+        <v>132</v>
+      </c>
+      <c r="F84" t="s">
+        <v>133</v>
+      </c>
+      <c r="G84" t="s">
+        <v>139</v>
+      </c>
+      <c r="H84" s="2">
         <v>45146</v>
       </c>
-      <c r="G84">
+      <c r="I84">
         <v>134.76</v>
       </c>
-      <c r="H84">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J84">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>65</v>
       </c>
@@ -3023,25 +3547,31 @@
         <v>119</v>
       </c>
       <c r="C85" t="s">
+        <v>135</v>
+      </c>
+      <c r="D85" t="s">
         <v>131</v>
       </c>
-      <c r="D85" t="s">
-        <v>132</v>
-      </c>
       <c r="E85" t="s">
-        <v>136</v>
-      </c>
-      <c r="F85" s="2">
+        <v>132</v>
+      </c>
+      <c r="F85" t="s">
+        <v>133</v>
+      </c>
+      <c r="G85" t="s">
+        <v>139</v>
+      </c>
+      <c r="H85" s="2">
         <v>45146</v>
       </c>
-      <c r="G85">
+      <c r="I85">
         <v>133.96</v>
       </c>
-      <c r="H85">
+      <c r="J85">
         <v>133.31</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>67</v>
       </c>
@@ -3049,25 +3579,31 @@
         <v>110</v>
       </c>
       <c r="C86" t="s">
+        <v>135</v>
+      </c>
+      <c r="D86" t="s">
         <v>131</v>
       </c>
-      <c r="D86" t="s">
-        <v>132</v>
-      </c>
       <c r="E86" t="s">
-        <v>136</v>
-      </c>
-      <c r="F86" s="2">
+        <v>132</v>
+      </c>
+      <c r="F86" t="s">
+        <v>133</v>
+      </c>
+      <c r="G86" t="s">
+        <v>139</v>
+      </c>
+      <c r="H86" s="2">
         <v>45146</v>
       </c>
-      <c r="G86">
+      <c r="I86">
         <v>128.38</v>
       </c>
-      <c r="H86">
+      <c r="J86">
         <v>128.25</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>47</v>
       </c>
@@ -3075,25 +3611,31 @@
         <v>119</v>
       </c>
       <c r="C87" t="s">
+        <v>135</v>
+      </c>
+      <c r="D87" t="s">
         <v>131</v>
       </c>
-      <c r="D87" t="s">
-        <v>132</v>
-      </c>
       <c r="E87" t="s">
-        <v>136</v>
-      </c>
-      <c r="F87" s="2">
+        <v>132</v>
+      </c>
+      <c r="F87" t="s">
+        <v>133</v>
+      </c>
+      <c r="G87" t="s">
+        <v>139</v>
+      </c>
+      <c r="H87" s="2">
         <v>45146</v>
       </c>
-      <c r="G87">
+      <c r="I87">
         <v>133.83000000000001</v>
       </c>
-      <c r="H87">
+      <c r="J87">
         <v>133.31</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -3101,25 +3643,31 @@
         <v>118</v>
       </c>
       <c r="C88" t="s">
+        <v>135</v>
+      </c>
+      <c r="D88" t="s">
         <v>131</v>
       </c>
-      <c r="D88" t="s">
-        <v>132</v>
-      </c>
       <c r="E88" t="s">
-        <v>136</v>
-      </c>
-      <c r="F88" s="2">
+        <v>132</v>
+      </c>
+      <c r="F88" t="s">
+        <v>133</v>
+      </c>
+      <c r="G88" t="s">
+        <v>139</v>
+      </c>
+      <c r="H88" s="2">
         <v>45146</v>
       </c>
-      <c r="G88">
+      <c r="I88">
         <v>127.72</v>
       </c>
-      <c r="H88">
+      <c r="J88">
         <v>127.64</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>31</v>
       </c>
@@ -3127,25 +3675,31 @@
         <v>109</v>
       </c>
       <c r="C89" t="s">
+        <v>135</v>
+      </c>
+      <c r="D89" t="s">
         <v>131</v>
       </c>
-      <c r="D89" t="s">
-        <v>132</v>
-      </c>
       <c r="E89" t="s">
-        <v>136</v>
-      </c>
-      <c r="F89" s="2">
+        <v>132</v>
+      </c>
+      <c r="F89" t="s">
+        <v>133</v>
+      </c>
+      <c r="G89" t="s">
+        <v>139</v>
+      </c>
+      <c r="H89" s="2">
         <v>45146</v>
       </c>
-      <c r="G89">
+      <c r="I89">
         <v>131.66</v>
       </c>
-      <c r="H89">
+      <c r="J89">
         <v>131.63</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>51</v>
       </c>
@@ -3153,25 +3707,31 @@
         <v>107</v>
       </c>
       <c r="C90" t="s">
+        <v>135</v>
+      </c>
+      <c r="D90" t="s">
         <v>131</v>
       </c>
-      <c r="D90" t="s">
-        <v>132</v>
-      </c>
       <c r="E90" t="s">
-        <v>136</v>
-      </c>
-      <c r="F90" s="2">
+        <v>132</v>
+      </c>
+      <c r="F90" t="s">
+        <v>133</v>
+      </c>
+      <c r="G90" t="s">
+        <v>139</v>
+      </c>
+      <c r="H90" s="2">
         <v>45146</v>
       </c>
-      <c r="G90">
+      <c r="I90">
         <v>125.98</v>
       </c>
-      <c r="H90">
+      <c r="J90">
         <v>126</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>48</v>
       </c>
@@ -3179,25 +3739,31 @@
         <v>120</v>
       </c>
       <c r="C91" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" t="s">
         <v>131</v>
       </c>
-      <c r="D91" t="s">
-        <v>132</v>
-      </c>
       <c r="E91" t="s">
-        <v>136</v>
-      </c>
-      <c r="F91" s="2">
+        <v>132</v>
+      </c>
+      <c r="F91" t="s">
+        <v>133</v>
+      </c>
+      <c r="G91" t="s">
+        <v>139</v>
+      </c>
+      <c r="H91" s="2">
         <v>45146</v>
       </c>
-      <c r="G91">
+      <c r="I91">
         <v>127.01</v>
       </c>
-      <c r="H91">
+      <c r="J91">
         <v>127.06</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>64</v>
       </c>
@@ -3205,25 +3771,31 @@
         <v>106</v>
       </c>
       <c r="C92" t="s">
+        <v>135</v>
+      </c>
+      <c r="D92" t="s">
         <v>131</v>
       </c>
-      <c r="D92" t="s">
-        <v>132</v>
-      </c>
       <c r="E92" t="s">
-        <v>136</v>
-      </c>
-      <c r="F92" s="2">
+        <v>132</v>
+      </c>
+      <c r="F92" t="s">
+        <v>133</v>
+      </c>
+      <c r="G92" t="s">
+        <v>139</v>
+      </c>
+      <c r="H92" s="2">
         <v>45146</v>
       </c>
-      <c r="G92">
+      <c r="I92">
         <v>124.3</v>
       </c>
-      <c r="H92">
+      <c r="J92">
         <v>124.2</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>68</v>
       </c>
@@ -3231,25 +3803,31 @@
         <v>125</v>
       </c>
       <c r="C93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D93" t="s">
         <v>131</v>
       </c>
-      <c r="D93" t="s">
-        <v>132</v>
-      </c>
       <c r="E93" t="s">
-        <v>136</v>
-      </c>
-      <c r="F93" s="2">
+        <v>132</v>
+      </c>
+      <c r="F93" t="s">
+        <v>133</v>
+      </c>
+      <c r="G93" t="s">
+        <v>139</v>
+      </c>
+      <c r="H93" s="2">
         <v>45146</v>
       </c>
-      <c r="G93">
+      <c r="I93">
         <v>121.47</v>
       </c>
-      <c r="H93">
+      <c r="J93">
         <v>121.5</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -3257,25 +3835,31 @@
         <v>110</v>
       </c>
       <c r="C94" t="s">
+        <v>135</v>
+      </c>
+      <c r="D94" t="s">
         <v>131</v>
       </c>
-      <c r="D94" t="s">
-        <v>132</v>
-      </c>
       <c r="E94" t="s">
-        <v>136</v>
-      </c>
-      <c r="F94" s="2">
+        <v>132</v>
+      </c>
+      <c r="F94" t="s">
+        <v>133</v>
+      </c>
+      <c r="G94" t="s">
+        <v>139</v>
+      </c>
+      <c r="H94" s="2">
         <v>45146</v>
       </c>
-      <c r="G94">
+      <c r="I94">
         <v>129.1</v>
       </c>
-      <c r="H94">
+      <c r="J94">
         <v>129.21</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>69</v>
       </c>
@@ -3283,25 +3867,31 @@
         <v>115</v>
       </c>
       <c r="C95" t="s">
+        <v>135</v>
+      </c>
+      <c r="D95" t="s">
         <v>131</v>
       </c>
-      <c r="D95" t="s">
-        <v>132</v>
-      </c>
       <c r="E95" t="s">
-        <v>136</v>
-      </c>
-      <c r="F95" s="2">
+        <v>132</v>
+      </c>
+      <c r="F95" t="s">
+        <v>133</v>
+      </c>
+      <c r="G95" t="s">
+        <v>139</v>
+      </c>
+      <c r="H95" s="2">
         <v>45146</v>
       </c>
-      <c r="G95">
+      <c r="I95">
         <v>120.33</v>
       </c>
-      <c r="H95">
+      <c r="J95">
         <v>120.27</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>38</v>
       </c>
@@ -3309,25 +3899,31 @@
         <v>113</v>
       </c>
       <c r="C96" t="s">
+        <v>135</v>
+      </c>
+      <c r="D96" t="s">
         <v>131</v>
       </c>
-      <c r="D96" t="s">
-        <v>132</v>
-      </c>
       <c r="E96" t="s">
-        <v>136</v>
-      </c>
-      <c r="F96" s="2">
+        <v>132</v>
+      </c>
+      <c r="F96" t="s">
+        <v>133</v>
+      </c>
+      <c r="G96" t="s">
+        <v>139</v>
+      </c>
+      <c r="H96" s="2">
         <v>45146</v>
       </c>
-      <c r="G96">
+      <c r="I96">
         <v>122.05</v>
       </c>
-      <c r="H96">
+      <c r="J96">
         <v>122.29</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>70</v>
       </c>
@@ -3335,25 +3931,31 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
+        <v>135</v>
+      </c>
+      <c r="D97" t="s">
         <v>131</v>
       </c>
-      <c r="D97" t="s">
-        <v>132</v>
-      </c>
       <c r="E97" t="s">
-        <v>136</v>
-      </c>
-      <c r="F97" s="2">
+        <v>132</v>
+      </c>
+      <c r="F97" t="s">
+        <v>133</v>
+      </c>
+      <c r="G97" t="s">
+        <v>139</v>
+      </c>
+      <c r="H97" s="2">
         <v>45146</v>
       </c>
-      <c r="G97">
+      <c r="I97">
         <v>131.25</v>
       </c>
-      <c r="H97">
+      <c r="J97">
         <v>131.13999999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>35</v>
       </c>
@@ -3361,25 +3963,31 @@
         <v>107</v>
       </c>
       <c r="C98" t="s">
+        <v>135</v>
+      </c>
+      <c r="D98" t="s">
         <v>131</v>
       </c>
-      <c r="D98" t="s">
-        <v>132</v>
-      </c>
       <c r="E98" t="s">
-        <v>136</v>
-      </c>
-      <c r="F98" s="2">
+        <v>132</v>
+      </c>
+      <c r="F98" t="s">
+        <v>133</v>
+      </c>
+      <c r="G98" t="s">
+        <v>139</v>
+      </c>
+      <c r="H98" s="2">
         <v>45146</v>
       </c>
-      <c r="G98">
+      <c r="I98">
         <v>117.35</v>
       </c>
-      <c r="H98">
+      <c r="J98">
         <v>117.53</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>57</v>
       </c>
@@ -3387,25 +3995,31 @@
         <v>123</v>
       </c>
       <c r="C99" t="s">
+        <v>135</v>
+      </c>
+      <c r="D99" t="s">
         <v>131</v>
       </c>
-      <c r="D99" t="s">
-        <v>132</v>
-      </c>
       <c r="E99" t="s">
-        <v>136</v>
-      </c>
-      <c r="F99" s="2">
+        <v>132</v>
+      </c>
+      <c r="F99" t="s">
+        <v>133</v>
+      </c>
+      <c r="G99" t="s">
+        <v>139</v>
+      </c>
+      <c r="H99" s="2">
         <v>45146</v>
       </c>
-      <c r="G99">
+      <c r="I99">
         <v>124.06</v>
       </c>
-      <c r="H99">
+      <c r="J99">
         <v>124.2</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>71</v>
       </c>
@@ -3413,25 +4027,31 @@
         <v>118</v>
       </c>
       <c r="C100" t="s">
+        <v>135</v>
+      </c>
+      <c r="D100" t="s">
         <v>131</v>
       </c>
-      <c r="D100" t="s">
-        <v>132</v>
-      </c>
       <c r="E100" t="s">
-        <v>136</v>
-      </c>
-      <c r="F100" s="2">
+        <v>132</v>
+      </c>
+      <c r="F100" t="s">
+        <v>133</v>
+      </c>
+      <c r="G100" t="s">
+        <v>139</v>
+      </c>
+      <c r="H100" s="2">
         <v>45146</v>
       </c>
-      <c r="G100">
+      <c r="I100">
         <v>128.22</v>
       </c>
-      <c r="H100">
+      <c r="J100">
         <v>128.25</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>72</v>
       </c>
@@ -3439,25 +4059,31 @@
         <v>112</v>
       </c>
       <c r="C101" t="s">
+        <v>135</v>
+      </c>
+      <c r="D101" t="s">
         <v>131</v>
       </c>
-      <c r="D101" t="s">
-        <v>132</v>
-      </c>
       <c r="E101" t="s">
-        <v>136</v>
-      </c>
-      <c r="F101" s="2">
+        <v>132</v>
+      </c>
+      <c r="F101" t="s">
+        <v>133</v>
+      </c>
+      <c r="G101" t="s">
+        <v>139</v>
+      </c>
+      <c r="H101" s="2">
         <v>45146</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>123.36</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>123.43</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>39</v>
       </c>
@@ -3465,25 +4091,31 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
+        <v>135</v>
+      </c>
+      <c r="D102" t="s">
         <v>131</v>
       </c>
-      <c r="D102" t="s">
-        <v>132</v>
-      </c>
       <c r="E102" t="s">
-        <v>136</v>
-      </c>
-      <c r="F102" s="2">
+        <v>132</v>
+      </c>
+      <c r="F102" t="s">
+        <v>133</v>
+      </c>
+      <c r="G102" t="s">
+        <v>139</v>
+      </c>
+      <c r="H102" s="2">
         <v>45146</v>
       </c>
-      <c r="G102">
+      <c r="I102">
         <v>116.92</v>
       </c>
-      <c r="H102">
+      <c r="J102">
         <v>117</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>41</v>
       </c>
@@ -3491,25 +4123,31 @@
         <v>115</v>
       </c>
       <c r="C103" t="s">
+        <v>135</v>
+      </c>
+      <c r="D103" t="s">
         <v>131</v>
       </c>
-      <c r="D103" t="s">
-        <v>132</v>
-      </c>
       <c r="E103" t="s">
-        <v>136</v>
-      </c>
-      <c r="F103" s="2">
+        <v>132</v>
+      </c>
+      <c r="F103" t="s">
+        <v>133</v>
+      </c>
+      <c r="G103" t="s">
+        <v>139</v>
+      </c>
+      <c r="H103" s="2">
         <v>45146</v>
       </c>
-      <c r="G103">
+      <c r="I103">
         <v>118.85</v>
       </c>
-      <c r="H103">
+      <c r="J103">
         <v>118.8</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -3517,25 +4155,31 @@
         <v>110</v>
       </c>
       <c r="C104" t="s">
+        <v>135</v>
+      </c>
+      <c r="D104" t="s">
         <v>131</v>
       </c>
-      <c r="D104" t="s">
-        <v>132</v>
-      </c>
       <c r="E104" t="s">
-        <v>136</v>
-      </c>
-      <c r="F104" s="2">
+        <v>132</v>
+      </c>
+      <c r="F104" t="s">
+        <v>133</v>
+      </c>
+      <c r="G104" t="s">
+        <v>139</v>
+      </c>
+      <c r="H104" s="2">
         <v>45146</v>
       </c>
-      <c r="G104">
+      <c r="I104">
         <v>130.74</v>
       </c>
-      <c r="H104">
+      <c r="J104">
         <v>130.85</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>42</v>
       </c>
@@ -3543,25 +4187,31 @@
         <v>115</v>
       </c>
       <c r="C105" t="s">
+        <v>135</v>
+      </c>
+      <c r="D105" t="s">
         <v>131</v>
       </c>
-      <c r="D105" t="s">
-        <v>132</v>
-      </c>
       <c r="E105" t="s">
-        <v>136</v>
-      </c>
-      <c r="F105" s="2">
+        <v>132</v>
+      </c>
+      <c r="F105" t="s">
+        <v>133</v>
+      </c>
+      <c r="G105" t="s">
+        <v>139</v>
+      </c>
+      <c r="H105" s="2">
         <v>45146</v>
       </c>
-      <c r="G105">
+      <c r="I105">
         <v>119.15</v>
       </c>
-      <c r="H105">
+      <c r="J105">
         <v>119.12</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>73</v>
       </c>
@@ -3569,25 +4219,31 @@
         <v>126</v>
       </c>
       <c r="C106" t="s">
+        <v>135</v>
+      </c>
+      <c r="D106" t="s">
         <v>131</v>
       </c>
-      <c r="D106" t="s">
-        <v>132</v>
-      </c>
       <c r="E106" t="s">
-        <v>136</v>
-      </c>
-      <c r="F106" s="2">
+        <v>132</v>
+      </c>
+      <c r="F106" t="s">
+        <v>133</v>
+      </c>
+      <c r="G106" t="s">
+        <v>139</v>
+      </c>
+      <c r="H106" s="2">
         <v>45146</v>
       </c>
-      <c r="G106">
+      <c r="I106">
         <v>138.37</v>
       </c>
-      <c r="H106">
+      <c r="J106">
         <v>138.6</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>36</v>
       </c>
@@ -3595,25 +4251,31 @@
         <v>104</v>
       </c>
       <c r="C107" t="s">
+        <v>135</v>
+      </c>
+      <c r="D107" t="s">
         <v>131</v>
       </c>
-      <c r="D107" t="s">
-        <v>132</v>
-      </c>
       <c r="E107" t="s">
-        <v>136</v>
-      </c>
-      <c r="F107" s="2">
+        <v>132</v>
+      </c>
+      <c r="F107" t="s">
+        <v>133</v>
+      </c>
+      <c r="G107" t="s">
+        <v>139</v>
+      </c>
+      <c r="H107" s="2">
         <v>45146</v>
       </c>
-      <c r="G107">
+      <c r="I107">
         <v>122.74</v>
       </c>
-      <c r="H107">
+      <c r="J107">
         <v>122.73</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>60</v>
       </c>
@@ -3621,25 +4283,31 @@
         <v>114</v>
       </c>
       <c r="C108" t="s">
+        <v>135</v>
+      </c>
+      <c r="D108" t="s">
         <v>131</v>
       </c>
-      <c r="D108" t="s">
-        <v>132</v>
-      </c>
       <c r="E108" t="s">
-        <v>136</v>
-      </c>
-      <c r="F108" s="2">
+        <v>132</v>
+      </c>
+      <c r="F108" t="s">
+        <v>133</v>
+      </c>
+      <c r="G108" t="s">
+        <v>139</v>
+      </c>
+      <c r="H108" s="2">
         <v>45146</v>
       </c>
-      <c r="G108">
+      <c r="I108">
         <v>123.91</v>
       </c>
-      <c r="H108">
+      <c r="J108">
         <v>123.88</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>74</v>
       </c>
@@ -3647,25 +4315,31 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
+        <v>135</v>
+      </c>
+      <c r="D109" t="s">
         <v>131</v>
       </c>
-      <c r="D109" t="s">
-        <v>132</v>
-      </c>
       <c r="E109" t="s">
-        <v>136</v>
-      </c>
-      <c r="F109" s="2">
+        <v>132</v>
+      </c>
+      <c r="F109" t="s">
+        <v>133</v>
+      </c>
+      <c r="G109" t="s">
+        <v>139</v>
+      </c>
+      <c r="H109" s="2">
         <v>45146</v>
       </c>
-      <c r="G109">
+      <c r="I109">
         <v>125.74</v>
       </c>
-      <c r="H109">
+      <c r="J109">
         <v>126</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3673,25 +4347,31 @@
         <v>127</v>
       </c>
       <c r="C110" t="s">
+        <v>135</v>
+      </c>
+      <c r="D110" t="s">
         <v>131</v>
       </c>
-      <c r="D110" t="s">
-        <v>132</v>
-      </c>
       <c r="E110" t="s">
-        <v>136</v>
-      </c>
-      <c r="F110" s="2">
+        <v>132</v>
+      </c>
+      <c r="F110" t="s">
+        <v>133</v>
+      </c>
+      <c r="G110" t="s">
+        <v>139</v>
+      </c>
+      <c r="H110" s="2">
         <v>45146</v>
       </c>
-      <c r="G110">
+      <c r="I110">
         <v>125.79</v>
       </c>
-      <c r="H110">
+      <c r="J110">
         <v>126</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>76</v>
       </c>
@@ -3699,25 +4379,31 @@
         <v>107</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
-      </c>
-      <c r="D111">
+        <v>136</v>
+      </c>
+      <c r="D111" t="s">
+        <v>129</v>
+      </c>
+      <c r="E111">
         <v>1</v>
       </c>
-      <c r="E111" t="s">
-        <v>137</v>
-      </c>
-      <c r="F111" s="2">
+      <c r="F111" t="s">
+        <v>133</v>
+      </c>
+      <c r="G111" t="s">
+        <v>138</v>
+      </c>
+      <c r="H111" s="2">
         <v>45142</v>
       </c>
-      <c r="G111">
+      <c r="I111">
         <v>113.29</v>
       </c>
-      <c r="H111">
+      <c r="J111">
         <v>113.4</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>77</v>
       </c>
@@ -3725,25 +4411,31 @@
         <v>107</v>
       </c>
       <c r="C112" t="s">
-        <v>129</v>
-      </c>
-      <c r="D112">
+        <v>136</v>
+      </c>
+      <c r="D112" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112">
         <v>2</v>
       </c>
-      <c r="E112" t="s">
-        <v>137</v>
-      </c>
-      <c r="F112" s="2">
+      <c r="F112" t="s">
+        <v>133</v>
+      </c>
+      <c r="G112" t="s">
+        <v>138</v>
+      </c>
+      <c r="H112" s="2">
         <v>45142</v>
       </c>
-      <c r="G112">
+      <c r="I112">
         <v>112.57</v>
       </c>
-      <c r="H112">
+      <c r="J112">
         <v>112.5</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>78</v>
       </c>
@@ -3751,25 +4443,31 @@
         <v>107</v>
       </c>
       <c r="C113" t="s">
-        <v>129</v>
-      </c>
-      <c r="D113">
+        <v>136</v>
+      </c>
+      <c r="D113" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113">
         <v>3</v>
       </c>
-      <c r="E113" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="2">
+      <c r="F113" t="s">
+        <v>133</v>
+      </c>
+      <c r="G113" t="s">
+        <v>138</v>
+      </c>
+      <c r="H113" s="2">
         <v>45142</v>
       </c>
-      <c r="G113">
+      <c r="I113">
         <v>111.39</v>
       </c>
-      <c r="H113">
+      <c r="J113">
         <v>111.38</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>79</v>
       </c>
@@ -3777,25 +4475,31 @@
         <v>107</v>
       </c>
       <c r="C114" t="s">
-        <v>129</v>
-      </c>
-      <c r="D114">
+        <v>136</v>
+      </c>
+      <c r="D114" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114">
         <v>4</v>
       </c>
-      <c r="E114" t="s">
-        <v>137</v>
-      </c>
-      <c r="F114" s="2">
+      <c r="F114" t="s">
+        <v>133</v>
+      </c>
+      <c r="G114" t="s">
+        <v>138</v>
+      </c>
+      <c r="H114" s="2">
         <v>45142</v>
       </c>
-      <c r="G114">
+      <c r="I114">
         <v>113.14</v>
       </c>
-      <c r="H114">
+      <c r="J114">
         <v>113.06</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>80</v>
       </c>
@@ -3803,25 +4507,31 @@
         <v>114</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
-      </c>
-      <c r="D115">
+        <v>136</v>
+      </c>
+      <c r="D115" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115">
         <v>1</v>
       </c>
-      <c r="E115" t="s">
-        <v>137</v>
-      </c>
-      <c r="F115" s="2">
+      <c r="F115" t="s">
+        <v>133</v>
+      </c>
+      <c r="G115" t="s">
+        <v>138</v>
+      </c>
+      <c r="H115" s="2">
         <v>45142</v>
       </c>
-      <c r="G115">
+      <c r="I115">
         <v>126.35</v>
       </c>
-      <c r="H115">
+      <c r="J115">
         <v>126.56</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>81</v>
       </c>
@@ -3829,25 +4539,31 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>129</v>
-      </c>
-      <c r="D116">
+        <v>136</v>
+      </c>
+      <c r="D116" t="s">
+        <v>129</v>
+      </c>
+      <c r="E116">
         <v>2</v>
       </c>
-      <c r="E116" t="s">
-        <v>137</v>
-      </c>
-      <c r="F116" s="2">
+      <c r="F116" t="s">
+        <v>133</v>
+      </c>
+      <c r="G116" t="s">
+        <v>138</v>
+      </c>
+      <c r="H116" s="2">
         <v>45142</v>
       </c>
-      <c r="G116">
+      <c r="I116">
         <v>128.83000000000001</v>
       </c>
-      <c r="H116">
+      <c r="J116">
         <v>128.77000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>82</v>
       </c>
@@ -3855,25 +4571,31 @@
         <v>114</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
-      </c>
-      <c r="D117">
+        <v>136</v>
+      </c>
+      <c r="D117" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117">
         <v>3</v>
       </c>
-      <c r="E117" t="s">
-        <v>137</v>
-      </c>
-      <c r="F117" s="2">
+      <c r="F117" t="s">
+        <v>133</v>
+      </c>
+      <c r="G117" t="s">
+        <v>138</v>
+      </c>
+      <c r="H117" s="2">
         <v>45142</v>
       </c>
-      <c r="G117">
+      <c r="I117">
         <v>124.79</v>
       </c>
-      <c r="H117">
+      <c r="J117">
         <v>124.88</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>83</v>
       </c>
@@ -3881,25 +4603,31 @@
         <v>114</v>
       </c>
       <c r="C118" t="s">
-        <v>129</v>
-      </c>
-      <c r="D118">
+        <v>136</v>
+      </c>
+      <c r="D118" t="s">
+        <v>129</v>
+      </c>
+      <c r="E118">
         <v>4</v>
       </c>
-      <c r="E118" t="s">
-        <v>137</v>
-      </c>
-      <c r="F118" s="2">
+      <c r="F118" t="s">
+        <v>133</v>
+      </c>
+      <c r="G118" t="s">
+        <v>138</v>
+      </c>
+      <c r="H118" s="2">
         <v>45142</v>
       </c>
-      <c r="G118">
+      <c r="I118">
         <v>129.38999999999999</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>129.21</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>84</v>
       </c>
@@ -3907,25 +4635,31 @@
         <v>106</v>
       </c>
       <c r="C119" t="s">
-        <v>129</v>
-      </c>
-      <c r="D119">
+        <v>136</v>
+      </c>
+      <c r="D119" t="s">
+        <v>129</v>
+      </c>
+      <c r="E119">
         <v>1</v>
       </c>
-      <c r="E119" t="s">
-        <v>137</v>
-      </c>
-      <c r="F119" s="2">
+      <c r="F119" t="s">
+        <v>133</v>
+      </c>
+      <c r="G119" t="s">
+        <v>138</v>
+      </c>
+      <c r="H119" s="2">
         <v>45142</v>
       </c>
-      <c r="G119">
+      <c r="I119">
         <v>110.19</v>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>110.25</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>85</v>
       </c>
@@ -3933,25 +4667,31 @@
         <v>106</v>
       </c>
       <c r="C120" t="s">
-        <v>129</v>
-      </c>
-      <c r="D120">
+        <v>136</v>
+      </c>
+      <c r="D120" t="s">
+        <v>129</v>
+      </c>
+      <c r="E120">
         <v>2</v>
       </c>
-      <c r="E120" t="s">
-        <v>137</v>
-      </c>
-      <c r="F120" s="2">
+      <c r="F120" t="s">
+        <v>133</v>
+      </c>
+      <c r="G120" t="s">
+        <v>138</v>
+      </c>
+      <c r="H120" s="2">
         <v>45142</v>
       </c>
-      <c r="G120">
+      <c r="I120">
         <v>110.3</v>
       </c>
-      <c r="H120">
+      <c r="J120">
         <v>110.25</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>86</v>
       </c>
@@ -3959,25 +4699,31 @@
         <v>106</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
-      </c>
-      <c r="D121">
+        <v>136</v>
+      </c>
+      <c r="D121" t="s">
+        <v>129</v>
+      </c>
+      <c r="E121">
         <v>3</v>
       </c>
-      <c r="E121" t="s">
-        <v>137</v>
-      </c>
-      <c r="F121" s="2">
+      <c r="F121" t="s">
+        <v>133</v>
+      </c>
+      <c r="G121" t="s">
+        <v>138</v>
+      </c>
+      <c r="H121" s="2">
         <v>45142</v>
       </c>
-      <c r="G121">
+      <c r="I121">
         <v>110.27</v>
       </c>
-      <c r="H121">
+      <c r="J121">
         <v>110.25</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>87</v>
       </c>
@@ -3985,25 +4731,31 @@
         <v>106</v>
       </c>
       <c r="C122" t="s">
-        <v>129</v>
-      </c>
-      <c r="D122">
+        <v>136</v>
+      </c>
+      <c r="D122" t="s">
+        <v>129</v>
+      </c>
+      <c r="E122">
         <v>4</v>
       </c>
-      <c r="E122" t="s">
-        <v>137</v>
-      </c>
-      <c r="F122" s="2">
+      <c r="F122" t="s">
+        <v>133</v>
+      </c>
+      <c r="G122" t="s">
+        <v>138</v>
+      </c>
+      <c r="H122" s="2">
         <v>45142</v>
       </c>
-      <c r="G122">
+      <c r="I122">
         <v>110.59</v>
       </c>
-      <c r="H122">
+      <c r="J122">
         <v>110.45</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -4011,25 +4763,31 @@
         <v>113</v>
       </c>
       <c r="C123" t="s">
-        <v>129</v>
-      </c>
-      <c r="D123">
+        <v>136</v>
+      </c>
+      <c r="D123" t="s">
+        <v>129</v>
+      </c>
+      <c r="E123">
         <v>1</v>
       </c>
-      <c r="E123" t="s">
-        <v>137</v>
-      </c>
-      <c r="F123" s="2">
+      <c r="F123" t="s">
+        <v>133</v>
+      </c>
+      <c r="G123" t="s">
+        <v>138</v>
+      </c>
+      <c r="H123" s="2">
         <v>45142</v>
       </c>
-      <c r="G123">
+      <c r="I123">
         <v>111.69</v>
       </c>
-      <c r="H123">
+      <c r="J123">
         <v>111.6</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>89</v>
       </c>
@@ -4037,25 +4795,31 @@
         <v>113</v>
       </c>
       <c r="C124" t="s">
-        <v>129</v>
-      </c>
-      <c r="D124">
+        <v>136</v>
+      </c>
+      <c r="D124" t="s">
+        <v>129</v>
+      </c>
+      <c r="E124">
         <v>2</v>
       </c>
-      <c r="E124" t="s">
-        <v>137</v>
-      </c>
-      <c r="F124" s="2">
+      <c r="F124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G124" t="s">
+        <v>138</v>
+      </c>
+      <c r="H124" s="2">
         <v>45142</v>
       </c>
-      <c r="G124">
+      <c r="I124">
         <v>112.86</v>
       </c>
-      <c r="H124">
+      <c r="J124">
         <v>112.91</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>90</v>
       </c>
@@ -4063,25 +4827,31 @@
         <v>113</v>
       </c>
       <c r="C125" t="s">
-        <v>129</v>
-      </c>
-      <c r="D125">
+        <v>136</v>
+      </c>
+      <c r="D125" t="s">
+        <v>129</v>
+      </c>
+      <c r="E125">
         <v>3</v>
       </c>
-      <c r="E125" t="s">
-        <v>137</v>
-      </c>
-      <c r="F125" s="2">
+      <c r="F125" t="s">
+        <v>133</v>
+      </c>
+      <c r="G125" t="s">
+        <v>138</v>
+      </c>
+      <c r="H125" s="2">
         <v>45142</v>
       </c>
-      <c r="G125">
+      <c r="I125">
         <v>111.11</v>
       </c>
-      <c r="H125">
+      <c r="J125">
         <v>111.18</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>91</v>
       </c>
@@ -4089,25 +4859,31 @@
         <v>113</v>
       </c>
       <c r="C126" t="s">
-        <v>129</v>
-      </c>
-      <c r="D126">
+        <v>136</v>
+      </c>
+      <c r="D126" t="s">
+        <v>129</v>
+      </c>
+      <c r="E126">
         <v>4</v>
       </c>
-      <c r="E126" t="s">
-        <v>137</v>
-      </c>
-      <c r="F126" s="2">
+      <c r="F126" t="s">
+        <v>133</v>
+      </c>
+      <c r="G126" t="s">
+        <v>138</v>
+      </c>
+      <c r="H126" s="2">
         <v>45142</v>
       </c>
-      <c r="G126">
+      <c r="I126">
         <v>119.42</v>
       </c>
-      <c r="H126">
+      <c r="J126">
         <v>119.57</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>92</v>
       </c>
@@ -4115,25 +4891,31 @@
         <v>108</v>
       </c>
       <c r="C127" t="s">
-        <v>129</v>
-      </c>
-      <c r="D127">
+        <v>136</v>
+      </c>
+      <c r="D127" t="s">
+        <v>129</v>
+      </c>
+      <c r="E127">
         <v>1</v>
       </c>
-      <c r="E127" t="s">
-        <v>137</v>
-      </c>
-      <c r="F127" s="2">
+      <c r="F127" t="s">
+        <v>133</v>
+      </c>
+      <c r="G127" t="s">
+        <v>138</v>
+      </c>
+      <c r="H127" s="2">
         <v>45142</v>
       </c>
-      <c r="G127">
+      <c r="I127">
         <v>111.61</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>111.6</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>93</v>
       </c>
@@ -4141,25 +4923,31 @@
         <v>108</v>
       </c>
       <c r="C128" t="s">
-        <v>129</v>
-      </c>
-      <c r="D128">
+        <v>136</v>
+      </c>
+      <c r="D128" t="s">
+        <v>129</v>
+      </c>
+      <c r="E128">
         <v>2</v>
       </c>
-      <c r="E128" t="s">
-        <v>137</v>
-      </c>
-      <c r="F128" s="2">
+      <c r="F128" t="s">
+        <v>133</v>
+      </c>
+      <c r="G128" t="s">
+        <v>138</v>
+      </c>
+      <c r="H128" s="2">
         <v>45142</v>
       </c>
-      <c r="G128">
+      <c r="I128">
         <v>112.21</v>
       </c>
-      <c r="H128">
+      <c r="J128">
         <v>112.26</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -4167,25 +4955,31 @@
         <v>108</v>
       </c>
       <c r="C129" t="s">
-        <v>129</v>
-      </c>
-      <c r="D129">
+        <v>136</v>
+      </c>
+      <c r="D129" t="s">
+        <v>129</v>
+      </c>
+      <c r="E129">
         <v>3</v>
       </c>
-      <c r="E129" t="s">
-        <v>137</v>
-      </c>
-      <c r="F129" s="2">
+      <c r="F129" t="s">
+        <v>133</v>
+      </c>
+      <c r="G129" t="s">
+        <v>138</v>
+      </c>
+      <c r="H129" s="2">
         <v>45142</v>
       </c>
-      <c r="G129">
+      <c r="I129">
         <v>111.92</v>
       </c>
-      <c r="H129">
+      <c r="J129">
         <v>111.86</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>95</v>
       </c>
@@ -4193,25 +4987,31 @@
         <v>108</v>
       </c>
       <c r="C130" t="s">
-        <v>129</v>
-      </c>
-      <c r="D130">
+        <v>136</v>
+      </c>
+      <c r="D130" t="s">
+        <v>129</v>
+      </c>
+      <c r="E130">
         <v>4</v>
       </c>
-      <c r="E130" t="s">
-        <v>137</v>
-      </c>
-      <c r="F130" s="2">
+      <c r="F130" t="s">
+        <v>133</v>
+      </c>
+      <c r="G130" t="s">
+        <v>138</v>
+      </c>
+      <c r="H130" s="2">
         <v>45142</v>
       </c>
-      <c r="G130">
+      <c r="I130">
         <v>112.25</v>
       </c>
-      <c r="H130">
+      <c r="J130">
         <v>112.26</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>96</v>
       </c>
@@ -4219,25 +5019,31 @@
         <v>104</v>
       </c>
       <c r="C131" t="s">
-        <v>129</v>
-      </c>
-      <c r="D131">
+        <v>136</v>
+      </c>
+      <c r="D131" t="s">
+        <v>129</v>
+      </c>
+      <c r="E131">
         <v>1</v>
       </c>
-      <c r="E131" t="s">
-        <v>137</v>
-      </c>
-      <c r="F131" s="2">
+      <c r="F131" t="s">
+        <v>133</v>
+      </c>
+      <c r="G131" t="s">
+        <v>138</v>
+      </c>
+      <c r="H131" s="2">
         <v>45142</v>
       </c>
-      <c r="G131">
+      <c r="I131">
         <v>113.15</v>
       </c>
-      <c r="H131">
+      <c r="J131">
         <v>113.06</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>97</v>
       </c>
@@ -4245,25 +5051,31 @@
         <v>104</v>
       </c>
       <c r="C132" t="s">
-        <v>129</v>
-      </c>
-      <c r="D132">
+        <v>136</v>
+      </c>
+      <c r="D132" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132">
         <v>2</v>
       </c>
-      <c r="E132" t="s">
-        <v>137</v>
-      </c>
-      <c r="F132" s="2">
+      <c r="F132" t="s">
+        <v>133</v>
+      </c>
+      <c r="G132" t="s">
+        <v>138</v>
+      </c>
+      <c r="H132" s="2">
         <v>45142</v>
       </c>
-      <c r="G132">
+      <c r="I132">
         <v>111.44</v>
       </c>
-      <c r="H132">
+      <c r="J132">
         <v>111.38</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>98</v>
       </c>
@@ -4271,25 +5083,31 @@
         <v>104</v>
       </c>
       <c r="C133" t="s">
-        <v>129</v>
-      </c>
-      <c r="D133">
+        <v>136</v>
+      </c>
+      <c r="D133" t="s">
+        <v>129</v>
+      </c>
+      <c r="E133">
         <v>3</v>
       </c>
-      <c r="E133" t="s">
-        <v>137</v>
-      </c>
-      <c r="F133" s="2">
+      <c r="F133" t="s">
+        <v>133</v>
+      </c>
+      <c r="G133" t="s">
+        <v>138</v>
+      </c>
+      <c r="H133" s="2">
         <v>45142</v>
       </c>
-      <c r="G133">
+      <c r="I133">
         <v>113.25</v>
       </c>
-      <c r="H133">
+      <c r="J133">
         <v>113.4</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>99</v>
       </c>
@@ -4297,25 +5115,31 @@
         <v>104</v>
       </c>
       <c r="C134" t="s">
-        <v>129</v>
-      </c>
-      <c r="D134">
+        <v>136</v>
+      </c>
+      <c r="D134" t="s">
+        <v>129</v>
+      </c>
+      <c r="E134">
         <v>4</v>
       </c>
-      <c r="E134" t="s">
-        <v>137</v>
-      </c>
-      <c r="F134" s="2">
+      <c r="F134" t="s">
+        <v>133</v>
+      </c>
+      <c r="G134" t="s">
+        <v>138</v>
+      </c>
+      <c r="H134" s="2">
         <v>45142</v>
       </c>
-      <c r="G134">
+      <c r="I134">
         <v>113.16</v>
       </c>
-      <c r="H134">
+      <c r="J134">
         <v>113.06</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>100</v>
       </c>
@@ -4323,25 +5147,31 @@
         <v>128</v>
       </c>
       <c r="C135" t="s">
-        <v>129</v>
-      </c>
-      <c r="D135">
+        <v>136</v>
+      </c>
+      <c r="D135" t="s">
+        <v>129</v>
+      </c>
+      <c r="E135">
         <v>1</v>
       </c>
-      <c r="E135" t="s">
-        <v>137</v>
-      </c>
-      <c r="F135" s="2">
+      <c r="F135" t="s">
+        <v>133</v>
+      </c>
+      <c r="G135" t="s">
+        <v>138</v>
+      </c>
+      <c r="H135" s="2">
         <v>45142</v>
       </c>
-      <c r="G135">
+      <c r="I135">
         <v>111.95</v>
       </c>
-      <c r="H135">
+      <c r="J135">
         <v>111.86</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>101</v>
       </c>
@@ -4349,25 +5179,31 @@
         <v>128</v>
       </c>
       <c r="C136" t="s">
-        <v>129</v>
-      </c>
-      <c r="D136">
+        <v>136</v>
+      </c>
+      <c r="D136" t="s">
+        <v>129</v>
+      </c>
+      <c r="E136">
         <v>2</v>
       </c>
-      <c r="E136" t="s">
-        <v>137</v>
-      </c>
-      <c r="F136" s="2">
+      <c r="F136" t="s">
+        <v>133</v>
+      </c>
+      <c r="G136" t="s">
+        <v>138</v>
+      </c>
+      <c r="H136" s="2">
         <v>45142</v>
       </c>
-      <c r="G136">
+      <c r="I136">
         <v>111.39</v>
       </c>
-      <c r="H136">
+      <c r="J136">
         <v>111.38</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>102</v>
       </c>
@@ -4375,25 +5211,31 @@
         <v>128</v>
       </c>
       <c r="C137" t="s">
-        <v>129</v>
-      </c>
-      <c r="D137">
+        <v>136</v>
+      </c>
+      <c r="D137" t="s">
+        <v>129</v>
+      </c>
+      <c r="E137">
         <v>3</v>
       </c>
-      <c r="E137" t="s">
-        <v>137</v>
-      </c>
-      <c r="F137" s="2">
+      <c r="F137" t="s">
+        <v>133</v>
+      </c>
+      <c r="G137" t="s">
+        <v>138</v>
+      </c>
+      <c r="H137" s="2">
         <v>45142</v>
       </c>
-      <c r="G137">
+      <c r="I137">
         <v>111.39</v>
       </c>
-      <c r="H137">
+      <c r="J137">
         <v>111.38</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>103</v>
       </c>
@@ -4401,25 +5243,32 @@
         <v>128</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
-      </c>
-      <c r="D138">
+        <v>136</v>
+      </c>
+      <c r="D138" t="s">
+        <v>129</v>
+      </c>
+      <c r="E138">
         <v>4</v>
       </c>
-      <c r="E138" t="s">
-        <v>137</v>
-      </c>
-      <c r="F138" s="2">
+      <c r="F138" t="s">
+        <v>133</v>
+      </c>
+      <c r="G138" t="s">
+        <v>138</v>
+      </c>
+      <c r="H138" s="2">
         <v>45142</v>
       </c>
-      <c r="G138">
+      <c r="I138">
         <v>111.91</v>
       </c>
-      <c r="H138">
+      <c r="J138">
         <v>111.86</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -1,39 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Gear_Calculator\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAADA45-4C21-4783-B5AE-15F2190EBF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="184">
   <si>
     <t>Name</t>
   </si>
@@ -41,6 +22,9 @@
     <t>Nation</t>
   </si>
   <si>
+    <t>Sex</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -50,6 +34,9 @@
     <t>Competition</t>
   </si>
   <si>
+    <t>Round</t>
+  </si>
+  <si>
     <t>Competition Date</t>
   </si>
   <si>
@@ -347,6 +334,114 @@
     <t>DYGERT Chloe</t>
   </si>
   <si>
+    <t>ANDREWS Ellesse</t>
+  </si>
+  <si>
+    <t>BAYONA PINEDA Martha</t>
+  </si>
+  <si>
+    <t>BILETSKA Alla</t>
+  </si>
+  <si>
+    <t>CAPEWELL Sophie</t>
+  </si>
+  <si>
+    <t>CASAS ROIGE Helena</t>
+  </si>
+  <si>
+    <t>CLONAN Kristina</t>
+  </si>
+  <si>
+    <t>DEGRENDELE Nicky</t>
+  </si>
+  <si>
+    <t>FINUCANE Emma</t>
+  </si>
+  <si>
+    <t>FRIEDRICH Lea Sophie</t>
+  </si>
+  <si>
+    <t>FULTON Shaane Hazel</t>
+  </si>
+  <si>
+    <t>GAXIOLA GONZALEZ Daniela</t>
+  </si>
+  <si>
+    <t>GENEST Lauriane</t>
+  </si>
+  <si>
+    <t>GRABOSCH Pauline</t>
+  </si>
+  <si>
+    <t>GROS Mathilde</t>
+  </si>
+  <si>
+    <t>GUO Yufang</t>
+  </si>
+  <si>
+    <t>HINZE Emma</t>
+  </si>
+  <si>
+    <t>JABORNIKOVA Veronika</t>
+  </si>
+  <si>
+    <t>KOUAME Taky Marie-Divine</t>
+  </si>
+  <si>
+    <t>LENDEL Migle</t>
+  </si>
+  <si>
+    <t>MARQUARDT Mandy</t>
+  </si>
+  <si>
+    <t>MICHAUX Julie</t>
+  </si>
+  <si>
+    <t>MITCHELL Kelsey</t>
+  </si>
+  <si>
+    <t>MOHAMED Shahd</t>
+  </si>
+  <si>
+    <t>MOHD ASRI Nurul</t>
+  </si>
+  <si>
+    <t>OHTA Riyu</t>
+  </si>
+  <si>
+    <t>ORBAN Sarah</t>
+  </si>
+  <si>
+    <t>PETRI Paulina</t>
+  </si>
+  <si>
+    <t>ROSIDI Anis Amira</t>
+  </si>
+  <si>
+    <t>SATO Mina</t>
+  </si>
+  <si>
+    <t>SIBIAK Nikola</t>
+  </si>
+  <si>
+    <t>UMEKAWA Fuko</t>
+  </si>
+  <si>
+    <t>van der PEET Steffie</t>
+  </si>
+  <si>
+    <t>van der WOUW Hetty</t>
+  </si>
+  <si>
+    <t>VECE Miriam</t>
+  </si>
+  <si>
+    <t>YEUNG Cho Yiu</t>
+  </si>
+  <si>
+    <t>YUAN Liying</t>
+  </si>
+  <si>
     <t>NZL</t>
   </si>
   <si>
@@ -422,6 +517,30 @@
     <t>USA</t>
   </si>
   <si>
+    <t>UKR</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
+    <t>EGY</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Team Pursuit</t>
   </si>
   <si>
@@ -435,18 +554,6 @@
   </si>
   <si>
     <t>WCH</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Round</t>
   </si>
   <si>
     <t>Q</t>
@@ -464,11 +571,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,12 +587,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -538,21 +639,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -590,7 +683,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -624,7 +717,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -659,10 +751,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -835,23 +926,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J138"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.21875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J174"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,51 +938,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H2" s="2">
         <v>45141</v>
@@ -915,27 +994,27 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G3" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H3" s="2">
         <v>45141</v>
@@ -947,27 +1026,27 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H4" s="2">
         <v>45141</v>
@@ -979,27 +1058,27 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H5" s="2">
         <v>45141</v>
@@ -1011,59 +1090,59 @@
         <v>120.46</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G6" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H6" s="2">
         <v>45141</v>
       </c>
       <c r="I6">
-        <v>128.16999999999999</v>
+        <v>128.17</v>
       </c>
       <c r="J6">
         <v>128.25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G7" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H7" s="2">
         <v>45141</v>
@@ -1075,27 +1154,27 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G8" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H8" s="2">
         <v>45141</v>
@@ -1107,27 +1186,27 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G9" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H9" s="2">
         <v>45141</v>
@@ -1139,27 +1218,27 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G10" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H10" s="2">
         <v>45141</v>
@@ -1171,27 +1250,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H11" s="2">
         <v>45141</v>
@@ -1203,27 +1282,27 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G12" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H12" s="2">
         <v>45141</v>
@@ -1235,27 +1314,27 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G13" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H13" s="2">
         <v>45141</v>
@@ -1267,27 +1346,27 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G14" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H14" s="2">
         <v>45141</v>
@@ -1299,27 +1378,27 @@
         <v>123.19</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G15" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H15" s="2">
         <v>45141</v>
@@ -1331,27 +1410,27 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H16" s="2">
         <v>45141</v>
@@ -1363,27 +1442,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G17" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H17" s="2">
         <v>45141</v>
@@ -1395,27 +1474,27 @@
         <v>125.18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H18" s="2">
         <v>45141</v>
@@ -1427,27 +1506,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G19" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H19" s="2">
         <v>45141</v>
@@ -1459,27 +1538,27 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G20" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H20" s="2">
         <v>45141</v>
@@ -1491,27 +1570,27 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E21">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G21" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H21" s="2">
         <v>45141</v>
@@ -1523,27 +1602,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H22" s="2">
         <v>45142</v>
@@ -1555,27 +1634,27 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H23" s="2">
         <v>45142</v>
@@ -1587,27 +1666,27 @@
         <v>127.29</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H24" s="2">
         <v>45142</v>
@@ -1619,27 +1698,27 @@
         <v>127.29</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H25" s="2">
         <v>45142</v>
@@ -1651,27 +1730,27 @@
         <v>129.21</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="H26" s="2">
         <v>45143</v>
@@ -1683,27 +1762,27 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="H27" s="2">
         <v>45143</v>
@@ -1715,27 +1794,27 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="H28" s="2">
         <v>45143</v>
@@ -1747,27 +1826,27 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="H29" s="2">
         <v>45143</v>
@@ -1779,27 +1858,27 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H30" s="2">
         <v>45143</v>
@@ -1811,27 +1890,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H31" s="2">
         <v>45143</v>
@@ -1843,27 +1922,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H32" s="2">
         <v>45143</v>
@@ -1875,27 +1954,27 @@
         <v>123.75</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H33" s="2">
         <v>45143</v>
@@ -1907,27 +1986,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H34" s="2">
         <v>45142</v>
@@ -1939,27 +2018,27 @@
         <v>120.71</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H35" s="2">
         <v>45142</v>
@@ -1971,27 +2050,27 @@
         <v>122.54</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G36" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H36" s="2">
         <v>45142</v>
@@ -2003,27 +2082,27 @@
         <v>124.62</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D37" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G37" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H37" s="2">
         <v>45142</v>
@@ -2035,27 +2114,27 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F38" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H38" s="2">
         <v>45143</v>
@@ -2067,27 +2146,27 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F39" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G39" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H39" s="2">
         <v>45143</v>
@@ -2096,30 +2175,30 @@
         <v>132.49</v>
       </c>
       <c r="J39">
-        <v>132.55000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>132.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F40" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H40" s="2">
         <v>45143</v>
@@ -2131,59 +2210,59 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F41" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H41" s="2">
         <v>45143</v>
       </c>
       <c r="I41">
-        <v>130.80000000000001</v>
+        <v>130.8</v>
       </c>
       <c r="J41">
         <v>130.85</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F42" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H42" s="2">
         <v>45143</v>
@@ -2192,62 +2271,62 @@
         <v>128.87</v>
       </c>
       <c r="J42">
-        <v>128.77000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>128.77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F43" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G43" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H43" s="2">
         <v>45143</v>
       </c>
       <c r="I43">
-        <v>134.36000000000001</v>
+        <v>134.36</v>
       </c>
       <c r="J43">
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E44" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F44" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G44" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H44" s="2">
         <v>45143</v>
@@ -2259,27 +2338,27 @@
         <v>129.6</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D45" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E45" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F45" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G45" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H45" s="2">
         <v>45143</v>
@@ -2291,91 +2370,91 @@
         <v>129.21</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F46" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G46" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H46" s="2">
         <v>45143</v>
       </c>
       <c r="I46">
-        <v>136.58000000000001</v>
+        <v>136.58</v>
       </c>
       <c r="J46">
-        <v>136.80000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>136.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E47" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F47" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G47" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H47" s="2">
         <v>45143</v>
       </c>
       <c r="I47">
-        <v>133.88999999999999</v>
+        <v>133.89</v>
       </c>
       <c r="J47">
         <v>133.31</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C48" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D48" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E48" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F48" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G48" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H48" s="2">
         <v>45143</v>
@@ -2387,27 +2466,27 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E49" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F49" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G49" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H49" s="2">
         <v>45143</v>
@@ -2419,59 +2498,59 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E50" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F50" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G50" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H50" s="2">
         <v>45143</v>
       </c>
       <c r="I50">
-        <v>139.72999999999999</v>
+        <v>139.73</v>
       </c>
       <c r="J50">
         <v>139.91</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E51" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F51" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G51" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H51" s="2">
         <v>45143</v>
@@ -2483,27 +2562,27 @@
         <v>130.85</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D52" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E52" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F52" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G52" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H52" s="2">
         <v>45143</v>
@@ -2515,59 +2594,59 @@
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F53" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G53" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H53" s="2">
         <v>45143</v>
       </c>
       <c r="I53">
-        <v>131.72999999999999</v>
+        <v>131.73</v>
       </c>
       <c r="J53">
         <v>131.63</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E54" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F54" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G54" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H54" s="2">
         <v>45143</v>
@@ -2579,27 +2658,27 @@
         <v>139.15</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E55" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F55" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G55" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H55" s="2">
         <v>45143</v>
@@ -2611,27 +2690,27 @@
         <v>140.79</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D56" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E56" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F56" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G56" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H56" s="2">
         <v>45143</v>
@@ -2643,27 +2722,27 @@
         <v>119.57</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E57" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F57" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G57" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H57" s="2">
         <v>45143</v>
@@ -2675,59 +2754,59 @@
         <v>131.63</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F58" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G58" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H58" s="2">
         <v>45143</v>
       </c>
       <c r="I58">
-        <v>134.33000000000001</v>
+        <v>134.33</v>
       </c>
       <c r="J58">
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D59" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E59" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F59" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G59" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H59" s="2">
         <v>45143</v>
@@ -2736,62 +2815,62 @@
         <v>138.93</v>
       </c>
       <c r="J59">
-        <v>138.86000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138.86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D60" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E60" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F60" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G60" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H60" s="2">
         <v>45143</v>
       </c>
       <c r="I60">
-        <v>142.38999999999999</v>
+        <v>142.39</v>
       </c>
       <c r="J60">
-        <v>142.36000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+        <v>142.36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C61" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E61" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F61" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G61" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H61" s="2">
         <v>45143</v>
@@ -2800,30 +2879,30 @@
         <v>137.91</v>
       </c>
       <c r="J61">
-        <v>137.69999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+        <v>137.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D62" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E62" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F62" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G62" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H62" s="2">
         <v>45143</v>
@@ -2832,30 +2911,30 @@
         <v>132.57</v>
       </c>
       <c r="J62">
-        <v>132.55000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+        <v>132.55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C63" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G63" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H63" s="2">
         <v>45143</v>
@@ -2867,27 +2946,27 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E64" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G64" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H64" s="2">
         <v>45143</v>
@@ -2899,27 +2978,27 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D65" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E65" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F65" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G65" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H65" s="2">
         <v>45143</v>
@@ -2931,59 +3010,59 @@
         <v>126.69</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D66" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E66" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F66" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G66" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H66" s="2">
         <v>45143</v>
       </c>
       <c r="I66">
-        <v>130.86000000000001</v>
+        <v>130.86</v>
       </c>
       <c r="J66">
         <v>130.85</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D67" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F67" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G67" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H67" s="2">
         <v>45143</v>
@@ -2995,27 +3074,27 @@
         <v>139.91</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E68" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F68" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G68" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H68" s="2">
         <v>45143</v>
@@ -3024,30 +3103,30 @@
         <v>137.49</v>
       </c>
       <c r="J68">
-        <v>137.44999999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+        <v>137.45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D69" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E69" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F69" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G69" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H69" s="2">
         <v>45143</v>
@@ -3059,27 +3138,27 @@
         <v>120.6</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C70" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="E70" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G70" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H70" s="2">
         <v>45143</v>
@@ -3088,30 +3167,30 @@
         <v>138.85</v>
       </c>
       <c r="J70">
-        <v>138.86000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138.86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D71" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E71" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F71" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G71" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="H71" s="2">
         <v>45147</v>
@@ -3123,27 +3202,27 @@
         <v>120.71</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D72" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E72" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G72" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="H72" s="2">
         <v>45147</v>
@@ -3155,27 +3234,27 @@
         <v>135</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B73" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D73" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E73" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G73" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="H73" s="2">
         <v>45147</v>
@@ -3187,59 +3266,59 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D74" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E74" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G74" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="H74" s="2">
         <v>45147</v>
       </c>
       <c r="I74">
-        <v>129.27000000000001</v>
+        <v>129.27</v>
       </c>
       <c r="J74">
         <v>129.21</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C75" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D75" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E75" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G75" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="H75" s="2">
         <v>45147</v>
@@ -3251,27 +3330,27 @@
         <v>123.75</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C76" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D76" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E76" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F76" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G76" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="H76" s="2">
         <v>45147</v>
@@ -3283,27 +3362,27 @@
         <v>117.82</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D77" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E77" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F77" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G77" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="H77" s="2">
         <v>45147</v>
@@ -3315,27 +3394,27 @@
         <v>119.57</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C78" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D78" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E78" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G78" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="H78" s="2">
         <v>45147</v>
@@ -3347,27 +3426,27 @@
         <v>126.69</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C79" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D79" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E79" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G79" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="H79" s="2">
         <v>45147</v>
@@ -3379,27 +3458,27 @@
         <v>135</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D80" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E80" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F80" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G80" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="H80" s="2">
         <v>45147</v>
@@ -3411,27 +3490,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D81" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E81" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G81" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="H81" s="2">
         <v>45147</v>
@@ -3443,27 +3522,27 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D82" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E82" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F82" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G82" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="H82" s="2">
         <v>45147</v>
@@ -3475,27 +3554,27 @@
         <v>120.71</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C83" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E83" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F83" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G83" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H83" s="2">
         <v>45146</v>
@@ -3507,27 +3586,27 @@
         <v>124.2</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C84" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D84" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E84" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F84" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G84" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H84" s="2">
         <v>45146</v>
@@ -3539,27 +3618,27 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C85" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E85" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F85" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G85" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H85" s="2">
         <v>45146</v>
@@ -3571,27 +3650,27 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B86" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C86" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E86" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F86" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G86" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H86" s="2">
         <v>45146</v>
@@ -3603,59 +3682,59 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B87" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E87" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F87" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G87" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H87" s="2">
         <v>45146</v>
       </c>
       <c r="I87">
-        <v>133.83000000000001</v>
+        <v>133.83</v>
       </c>
       <c r="J87">
         <v>133.31</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C88" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E88" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F88" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G88" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H88" s="2">
         <v>45146</v>
@@ -3667,27 +3746,27 @@
         <v>127.64</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C89" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E89" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F89" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G89" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H89" s="2">
         <v>45146</v>
@@ -3699,27 +3778,27 @@
         <v>131.63</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B90" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C90" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E90" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F90" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G90" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H90" s="2">
         <v>45146</v>
@@ -3731,27 +3810,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C91" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E91" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F91" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G91" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H91" s="2">
         <v>45146</v>
@@ -3763,27 +3842,27 @@
         <v>127.06</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C92" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E92" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F92" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G92" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H92" s="2">
         <v>45146</v>
@@ -3795,27 +3874,27 @@
         <v>124.2</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C93" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E93" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F93" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G93" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H93" s="2">
         <v>45146</v>
@@ -3827,27 +3906,27 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C94" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E94" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F94" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G94" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H94" s="2">
         <v>45146</v>
@@ -3859,27 +3938,27 @@
         <v>129.21</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B95" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C95" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E95" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F95" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G95" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H95" s="2">
         <v>45146</v>
@@ -3891,27 +3970,27 @@
         <v>120.27</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C96" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E96" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F96" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G96" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H96" s="2">
         <v>45146</v>
@@ -3923,27 +4002,27 @@
         <v>122.29</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D97" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E97" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F97" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G97" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H97" s="2">
         <v>45146</v>
@@ -3952,30 +4031,30 @@
         <v>131.25</v>
       </c>
       <c r="J97">
-        <v>131.13999999999999</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+        <v>131.14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D98" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E98" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F98" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G98" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H98" s="2">
         <v>45146</v>
@@ -3987,27 +4066,27 @@
         <v>117.53</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C99" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D99" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E99" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F99" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G99" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H99" s="2">
         <v>45146</v>
@@ -4019,27 +4098,27 @@
         <v>124.2</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B100" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C100" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D100" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E100" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F100" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G100" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H100" s="2">
         <v>45146</v>
@@ -4051,27 +4130,27 @@
         <v>128.25</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C101" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D101" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E101" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F101" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G101" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H101" s="2">
         <v>45146</v>
@@ -4083,27 +4162,27 @@
         <v>123.43</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C102" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D102" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E102" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F102" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G102" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H102" s="2">
         <v>45146</v>
@@ -4115,27 +4194,27 @@
         <v>117</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D103" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E103" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F103" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G103" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H103" s="2">
         <v>45146</v>
@@ -4147,27 +4226,27 @@
         <v>118.8</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C104" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D104" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E104" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F104" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G104" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H104" s="2">
         <v>45146</v>
@@ -4179,27 +4258,27 @@
         <v>130.85</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D105" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E105" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F105" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G105" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H105" s="2">
         <v>45146</v>
@@ -4211,27 +4290,27 @@
         <v>119.12</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B106" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C106" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E106" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F106" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G106" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H106" s="2">
         <v>45146</v>
@@ -4243,27 +4322,27 @@
         <v>138.6</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C107" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D107" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E107" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F107" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G107" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H107" s="2">
         <v>45146</v>
@@ -4275,27 +4354,27 @@
         <v>122.73</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C108" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D108" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E108" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F108" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G108" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H108" s="2">
         <v>45146</v>
@@ -4307,27 +4386,27 @@
         <v>123.88</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C109" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D109" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E109" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F109" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G109" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H109" s="2">
         <v>45146</v>
@@ -4339,27 +4418,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10">
       <c r="A110" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C110" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E110" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F110" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G110" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H110" s="2">
         <v>45146</v>
@@ -4371,27 +4450,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10">
       <c r="A111" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C111" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D111" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G111" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H111" s="2">
         <v>45142</v>
@@ -4403,27 +4482,27 @@
         <v>113.4</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10">
       <c r="A112" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C112" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D112" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E112">
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G112" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H112" s="2">
         <v>45142</v>
@@ -4435,27 +4514,27 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C113" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G113" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H113" s="2">
         <v>45142</v>
@@ -4467,27 +4546,27 @@
         <v>111.38</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C114" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D114" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E114">
         <v>4</v>
       </c>
       <c r="F114" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G114" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H114" s="2">
         <v>45142</v>
@@ -4499,27 +4578,27 @@
         <v>113.06</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C115" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D115" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G115" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H115" s="2">
         <v>45142</v>
@@ -4531,59 +4610,59 @@
         <v>126.56</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C116" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D116" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E116">
         <v>2</v>
       </c>
       <c r="F116" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G116" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H116" s="2">
         <v>45142</v>
       </c>
       <c r="I116">
-        <v>128.83000000000001</v>
+        <v>128.83</v>
       </c>
       <c r="J116">
-        <v>128.77000000000001</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+        <v>128.77</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C117" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D117" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G117" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H117" s="2">
         <v>45142</v>
@@ -4595,59 +4674,59 @@
         <v>124.88</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C118" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D118" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E118">
         <v>4</v>
       </c>
       <c r="F118" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G118" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H118" s="2">
         <v>45142</v>
       </c>
       <c r="I118">
-        <v>129.38999999999999</v>
+        <v>129.39</v>
       </c>
       <c r="J118">
         <v>129.21</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D119" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E119">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G119" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H119" s="2">
         <v>45142</v>
@@ -4659,27 +4738,27 @@
         <v>110.25</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C120" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D120" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E120">
         <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G120" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H120" s="2">
         <v>45142</v>
@@ -4691,27 +4770,27 @@
         <v>110.25</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B121" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D121" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G121" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H121" s="2">
         <v>45142</v>
@@ -4723,27 +4802,27 @@
         <v>110.25</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B122" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D122" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E122">
         <v>4</v>
       </c>
       <c r="F122" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G122" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H122" s="2">
         <v>45142</v>
@@ -4755,27 +4834,27 @@
         <v>110.45</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B123" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D123" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E123">
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G123" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H123" s="2">
         <v>45142</v>
@@ -4787,27 +4866,27 @@
         <v>111.6</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B124" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C124" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D124" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E124">
         <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G124" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H124" s="2">
         <v>45142</v>
@@ -4819,27 +4898,27 @@
         <v>112.91</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B125" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C125" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D125" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G125" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H125" s="2">
         <v>45142</v>
@@ -4851,27 +4930,27 @@
         <v>111.18</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B126" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C126" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D126" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
       <c r="F126" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G126" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H126" s="2">
         <v>45142</v>
@@ -4883,27 +4962,27 @@
         <v>119.57</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B127" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C127" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D127" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E127">
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G127" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H127" s="2">
         <v>45142</v>
@@ -4915,27 +4994,27 @@
         <v>111.6</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B128" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C128" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D128" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E128">
         <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G128" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H128" s="2">
         <v>45142</v>
@@ -4947,27 +5026,27 @@
         <v>112.26</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10">
       <c r="A129" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B129" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C129" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D129" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G129" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H129" s="2">
         <v>45142</v>
@@ -4979,27 +5058,27 @@
         <v>111.86</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10">
       <c r="A130" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B130" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C130" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D130" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E130">
         <v>4</v>
       </c>
       <c r="F130" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G130" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H130" s="2">
         <v>45142</v>
@@ -5011,27 +5090,27 @@
         <v>112.26</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10">
       <c r="A131" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B131" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D131" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E131">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G131" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H131" s="2">
         <v>45142</v>
@@ -5043,27 +5122,27 @@
         <v>113.06</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10">
       <c r="A132" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B132" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C132" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D132" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E132">
         <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G132" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H132" s="2">
         <v>45142</v>
@@ -5075,27 +5154,27 @@
         <v>111.38</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10">
       <c r="A133" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B133" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C133" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D133" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E133">
         <v>3</v>
       </c>
       <c r="F133" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G133" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H133" s="2">
         <v>45142</v>
@@ -5107,27 +5186,27 @@
         <v>113.4</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10">
       <c r="A134" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B134" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C134" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D134" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E134">
         <v>4</v>
       </c>
       <c r="F134" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G134" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H134" s="2">
         <v>45142</v>
@@ -5139,27 +5218,27 @@
         <v>113.06</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10">
       <c r="A135" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B135" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C135" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D135" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G135" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H135" s="2">
         <v>45142</v>
@@ -5171,27 +5250,27 @@
         <v>111.86</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10">
       <c r="A136" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B136" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C136" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D136" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E136">
         <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G136" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H136" s="2">
         <v>45142</v>
@@ -5203,27 +5282,27 @@
         <v>111.38</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10">
       <c r="A137" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B137" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C137" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D137" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G137" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H137" s="2">
         <v>45142</v>
@@ -5235,27 +5314,27 @@
         <v>111.38</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10">
       <c r="A138" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B138" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C138" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D138" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="E138">
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="G138" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="H138" s="2">
         <v>45142</v>
@@ -5267,8 +5346,1159 @@
         <v>111.86</v>
       </c>
     </row>
+    <row r="139" spans="1:10">
+      <c r="A139" t="s">
+        <v>106</v>
+      </c>
+      <c r="B139" t="s">
+        <v>142</v>
+      </c>
+      <c r="C139" t="s">
+        <v>174</v>
+      </c>
+      <c r="D139" t="s">
+        <v>176</v>
+      </c>
+      <c r="E139" t="s">
+        <v>178</v>
+      </c>
+      <c r="F139" t="s">
+        <v>179</v>
+      </c>
+      <c r="G139" t="s">
+        <v>180</v>
+      </c>
+      <c r="H139" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I139">
+        <v>115.37</v>
+      </c>
+      <c r="J139">
+        <v>115.36</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" t="s">
+        <v>107</v>
+      </c>
+      <c r="B140" t="s">
+        <v>156</v>
+      </c>
+      <c r="C140" t="s">
+        <v>174</v>
+      </c>
+      <c r="D140" t="s">
+        <v>176</v>
+      </c>
+      <c r="E140" t="s">
+        <v>178</v>
+      </c>
+      <c r="F140" t="s">
+        <v>179</v>
+      </c>
+      <c r="G140" t="s">
+        <v>180</v>
+      </c>
+      <c r="H140" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I140">
+        <v>125.5</v>
+      </c>
+      <c r="J140">
+        <v>125.47</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" t="s">
+        <v>108</v>
+      </c>
+      <c r="B141" t="s">
+        <v>167</v>
+      </c>
+      <c r="C141" t="s">
+        <v>174</v>
+      </c>
+      <c r="D141" t="s">
+        <v>176</v>
+      </c>
+      <c r="E141" t="s">
+        <v>178</v>
+      </c>
+      <c r="F141" t="s">
+        <v>179</v>
+      </c>
+      <c r="G141" t="s">
+        <v>180</v>
+      </c>
+      <c r="H141" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I141">
+        <v>114.37</v>
+      </c>
+      <c r="J141">
+        <v>114.35</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" t="s">
+        <v>109</v>
+      </c>
+      <c r="B142" t="s">
+        <v>144</v>
+      </c>
+      <c r="C142" t="s">
+        <v>174</v>
+      </c>
+      <c r="D142" t="s">
+        <v>176</v>
+      </c>
+      <c r="E142" t="s">
+        <v>178</v>
+      </c>
+      <c r="F142" t="s">
+        <v>179</v>
+      </c>
+      <c r="G142" t="s">
+        <v>180</v>
+      </c>
+      <c r="H142" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I142">
+        <v>131.8</v>
+      </c>
+      <c r="J142">
+        <v>131.63</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" t="s">
+        <v>110</v>
+      </c>
+      <c r="B143" t="s">
+        <v>155</v>
+      </c>
+      <c r="C143" t="s">
+        <v>174</v>
+      </c>
+      <c r="D143" t="s">
+        <v>176</v>
+      </c>
+      <c r="E143" t="s">
+        <v>178</v>
+      </c>
+      <c r="F143" t="s">
+        <v>179</v>
+      </c>
+      <c r="G143" t="s">
+        <v>180</v>
+      </c>
+      <c r="H143" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I143">
+        <v>121.6</v>
+      </c>
+      <c r="J143">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" t="s">
+        <v>111</v>
+      </c>
+      <c r="B144" t="s">
+        <v>145</v>
+      </c>
+      <c r="C144" t="s">
+        <v>174</v>
+      </c>
+      <c r="D144" t="s">
+        <v>176</v>
+      </c>
+      <c r="E144" t="s">
+        <v>178</v>
+      </c>
+      <c r="F144" t="s">
+        <v>179</v>
+      </c>
+      <c r="G144" t="s">
+        <v>180</v>
+      </c>
+      <c r="H144" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I144">
+        <v>114.94</v>
+      </c>
+      <c r="J144">
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" t="s">
+        <v>112</v>
+      </c>
+      <c r="B145" t="s">
+        <v>168</v>
+      </c>
+      <c r="C145" t="s">
+        <v>174</v>
+      </c>
+      <c r="D145" t="s">
+        <v>176</v>
+      </c>
+      <c r="E145" t="s">
+        <v>178</v>
+      </c>
+      <c r="F145" t="s">
+        <v>179</v>
+      </c>
+      <c r="G145" t="s">
+        <v>180</v>
+      </c>
+      <c r="H145" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I145">
+        <v>117.45</v>
+      </c>
+      <c r="J145">
+        <v>117.53</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" t="s">
+        <v>113</v>
+      </c>
+      <c r="B146" t="s">
+        <v>144</v>
+      </c>
+      <c r="C146" t="s">
+        <v>174</v>
+      </c>
+      <c r="D146" t="s">
+        <v>176</v>
+      </c>
+      <c r="E146" t="s">
+        <v>178</v>
+      </c>
+      <c r="F146" t="s">
+        <v>179</v>
+      </c>
+      <c r="G146" t="s">
+        <v>180</v>
+      </c>
+      <c r="H146" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I146">
+        <v>127.54</v>
+      </c>
+      <c r="J146">
+        <v>127.64</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" t="s">
+        <v>114</v>
+      </c>
+      <c r="B147" t="s">
+        <v>151</v>
+      </c>
+      <c r="C147" t="s">
+        <v>174</v>
+      </c>
+      <c r="D147" t="s">
+        <v>176</v>
+      </c>
+      <c r="E147" t="s">
+        <v>178</v>
+      </c>
+      <c r="F147" t="s">
+        <v>179</v>
+      </c>
+      <c r="G147" t="s">
+        <v>180</v>
+      </c>
+      <c r="H147" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I147">
+        <v>113.9</v>
+      </c>
+      <c r="J147">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" t="s">
+        <v>115</v>
+      </c>
+      <c r="B148" t="s">
+        <v>142</v>
+      </c>
+      <c r="C148" t="s">
+        <v>174</v>
+      </c>
+      <c r="D148" t="s">
+        <v>176</v>
+      </c>
+      <c r="E148" t="s">
+        <v>178</v>
+      </c>
+      <c r="F148" t="s">
+        <v>179</v>
+      </c>
+      <c r="G148" t="s">
+        <v>180</v>
+      </c>
+      <c r="H148" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I148">
+        <v>116.75</v>
+      </c>
+      <c r="J148">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" t="s">
+        <v>116</v>
+      </c>
+      <c r="B149" t="s">
+        <v>169</v>
+      </c>
+      <c r="C149" t="s">
+        <v>174</v>
+      </c>
+      <c r="D149" t="s">
+        <v>176</v>
+      </c>
+      <c r="E149" t="s">
+        <v>178</v>
+      </c>
+      <c r="F149" t="s">
+        <v>179</v>
+      </c>
+      <c r="G149" t="s">
+        <v>180</v>
+      </c>
+      <c r="H149" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I149">
+        <v>120.16</v>
+      </c>
+      <c r="J149">
+        <v>120.27</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" t="s">
+        <v>117</v>
+      </c>
+      <c r="B150" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150" t="s">
+        <v>174</v>
+      </c>
+      <c r="D150" t="s">
+        <v>176</v>
+      </c>
+      <c r="E150" t="s">
+        <v>178</v>
+      </c>
+      <c r="F150" t="s">
+        <v>179</v>
+      </c>
+      <c r="G150" t="s">
+        <v>180</v>
+      </c>
+      <c r="H150" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I150">
+        <v>121.74</v>
+      </c>
+      <c r="J150">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" t="s">
+        <v>118</v>
+      </c>
+      <c r="B151" t="s">
+        <v>151</v>
+      </c>
+      <c r="C151" t="s">
+        <v>174</v>
+      </c>
+      <c r="D151" t="s">
+        <v>176</v>
+      </c>
+      <c r="E151" t="s">
+        <v>178</v>
+      </c>
+      <c r="F151" t="s">
+        <v>179</v>
+      </c>
+      <c r="G151" t="s">
+        <v>180</v>
+      </c>
+      <c r="H151" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I151">
+        <v>122.07</v>
+      </c>
+      <c r="J151">
+        <v>122.29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" t="s">
+        <v>119</v>
+      </c>
+      <c r="B152" t="s">
+        <v>152</v>
+      </c>
+      <c r="C152" t="s">
+        <v>174</v>
+      </c>
+      <c r="D152" t="s">
+        <v>176</v>
+      </c>
+      <c r="E152" t="s">
+        <v>178</v>
+      </c>
+      <c r="F152" t="s">
+        <v>179</v>
+      </c>
+      <c r="G152" t="s">
+        <v>180</v>
+      </c>
+      <c r="H152" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I152">
+        <v>127.05</v>
+      </c>
+      <c r="J152">
+        <v>127.06</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" t="s">
+        <v>120</v>
+      </c>
+      <c r="B153" t="s">
+        <v>170</v>
+      </c>
+      <c r="C153" t="s">
+        <v>174</v>
+      </c>
+      <c r="D153" t="s">
+        <v>176</v>
+      </c>
+      <c r="E153" t="s">
+        <v>178</v>
+      </c>
+      <c r="F153" t="s">
+        <v>179</v>
+      </c>
+      <c r="G153" t="s">
+        <v>180</v>
+      </c>
+      <c r="H153" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I153">
+        <v>123.6</v>
+      </c>
+      <c r="J153">
+        <v>123.75</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" t="s">
+        <v>121</v>
+      </c>
+      <c r="B154" t="s">
+        <v>151</v>
+      </c>
+      <c r="C154" t="s">
+        <v>174</v>
+      </c>
+      <c r="D154" t="s">
+        <v>176</v>
+      </c>
+      <c r="E154" t="s">
+        <v>178</v>
+      </c>
+      <c r="F154" t="s">
+        <v>179</v>
+      </c>
+      <c r="G154" t="s">
+        <v>180</v>
+      </c>
+      <c r="H154" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I154">
+        <v>110.23</v>
+      </c>
+      <c r="J154">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" t="s">
+        <v>122</v>
+      </c>
+      <c r="B155" t="s">
+        <v>149</v>
+      </c>
+      <c r="C155" t="s">
+        <v>174</v>
+      </c>
+      <c r="D155" t="s">
+        <v>176</v>
+      </c>
+      <c r="E155" t="s">
+        <v>178</v>
+      </c>
+      <c r="F155" t="s">
+        <v>179</v>
+      </c>
+      <c r="G155" t="s">
+        <v>180</v>
+      </c>
+      <c r="H155" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I155">
+        <v>121.19</v>
+      </c>
+      <c r="J155">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" t="s">
+        <v>123</v>
+      </c>
+      <c r="B156" t="s">
+        <v>152</v>
+      </c>
+      <c r="C156" t="s">
+        <v>174</v>
+      </c>
+      <c r="D156" t="s">
+        <v>176</v>
+      </c>
+      <c r="E156" t="s">
+        <v>178</v>
+      </c>
+      <c r="F156" t="s">
+        <v>179</v>
+      </c>
+      <c r="G156" t="s">
+        <v>180</v>
+      </c>
+      <c r="H156" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I156">
+        <v>129.28</v>
+      </c>
+      <c r="J156">
+        <v>129.21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" t="s">
+        <v>124</v>
+      </c>
+      <c r="B157" t="s">
+        <v>154</v>
+      </c>
+      <c r="C157" t="s">
+        <v>174</v>
+      </c>
+      <c r="D157" t="s">
+        <v>176</v>
+      </c>
+      <c r="E157" t="s">
+        <v>178</v>
+      </c>
+      <c r="F157" t="s">
+        <v>179</v>
+      </c>
+      <c r="G157" t="s">
+        <v>180</v>
+      </c>
+      <c r="H157" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I157">
+        <v>127.26</v>
+      </c>
+      <c r="J157">
+        <v>127.29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" t="s">
+        <v>125</v>
+      </c>
+      <c r="B158" t="s">
+        <v>166</v>
+      </c>
+      <c r="C158" t="s">
+        <v>174</v>
+      </c>
+      <c r="D158" t="s">
+        <v>176</v>
+      </c>
+      <c r="E158" t="s">
+        <v>178</v>
+      </c>
+      <c r="F158" t="s">
+        <v>179</v>
+      </c>
+      <c r="G158" t="s">
+        <v>180</v>
+      </c>
+      <c r="H158" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I158">
+        <v>122.9</v>
+      </c>
+      <c r="J158">
+        <v>122.73</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" t="s">
+        <v>126</v>
+      </c>
+      <c r="B159" t="s">
+        <v>152</v>
+      </c>
+      <c r="C159" t="s">
+        <v>174</v>
+      </c>
+      <c r="D159" t="s">
+        <v>176</v>
+      </c>
+      <c r="E159" t="s">
+        <v>178</v>
+      </c>
+      <c r="F159" t="s">
+        <v>179</v>
+      </c>
+      <c r="G159" t="s">
+        <v>180</v>
+      </c>
+      <c r="H159" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I159">
+        <v>122.28</v>
+      </c>
+      <c r="J159">
+        <v>122.29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" t="s">
+        <v>127</v>
+      </c>
+      <c r="B160" t="s">
+        <v>150</v>
+      </c>
+      <c r="C160" t="s">
+        <v>174</v>
+      </c>
+      <c r="D160" t="s">
+        <v>176</v>
+      </c>
+      <c r="E160" t="s">
+        <v>178</v>
+      </c>
+      <c r="F160" t="s">
+        <v>179</v>
+      </c>
+      <c r="G160" t="s">
+        <v>180</v>
+      </c>
+      <c r="H160" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I160">
+        <v>119.95</v>
+      </c>
+      <c r="J160">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" t="s">
+        <v>128</v>
+      </c>
+      <c r="B161" t="s">
+        <v>171</v>
+      </c>
+      <c r="C161" t="s">
+        <v>174</v>
+      </c>
+      <c r="D161" t="s">
+        <v>176</v>
+      </c>
+      <c r="E161" t="s">
+        <v>178</v>
+      </c>
+      <c r="F161" t="s">
+        <v>179</v>
+      </c>
+      <c r="G161" t="s">
+        <v>180</v>
+      </c>
+      <c r="H161" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I161">
+        <v>109.37</v>
+      </c>
+      <c r="J161">
+        <v>109.42</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" t="s">
+        <v>129</v>
+      </c>
+      <c r="B162" t="s">
+        <v>148</v>
+      </c>
+      <c r="C162" t="s">
+        <v>174</v>
+      </c>
+      <c r="D162" t="s">
+        <v>176</v>
+      </c>
+      <c r="E162" t="s">
+        <v>178</v>
+      </c>
+      <c r="F162" t="s">
+        <v>179</v>
+      </c>
+      <c r="G162" t="s">
+        <v>180</v>
+      </c>
+      <c r="H162" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I162">
+        <v>114.72</v>
+      </c>
+      <c r="J162">
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" t="s">
+        <v>130</v>
+      </c>
+      <c r="B163" t="s">
+        <v>157</v>
+      </c>
+      <c r="C163" t="s">
+        <v>174</v>
+      </c>
+      <c r="D163" t="s">
+        <v>176</v>
+      </c>
+      <c r="E163" t="s">
+        <v>178</v>
+      </c>
+      <c r="F163" t="s">
+        <v>179</v>
+      </c>
+      <c r="G163" t="s">
+        <v>180</v>
+      </c>
+      <c r="H163" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I163">
+        <v>124.75</v>
+      </c>
+      <c r="J163">
+        <v>124.62</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" t="s">
+        <v>131</v>
+      </c>
+      <c r="B164" t="s">
+        <v>150</v>
+      </c>
+      <c r="C164" t="s">
+        <v>174</v>
+      </c>
+      <c r="D164" t="s">
+        <v>176</v>
+      </c>
+      <c r="E164" t="s">
+        <v>178</v>
+      </c>
+      <c r="F164" t="s">
+        <v>179</v>
+      </c>
+      <c r="G164" t="s">
+        <v>180</v>
+      </c>
+      <c r="H164" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I164">
+        <v>122.28</v>
+      </c>
+      <c r="J164">
+        <v>122.29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" t="s">
+        <v>132</v>
+      </c>
+      <c r="B165" t="s">
+        <v>159</v>
+      </c>
+      <c r="C165" t="s">
+        <v>174</v>
+      </c>
+      <c r="D165" t="s">
+        <v>176</v>
+      </c>
+      <c r="E165" t="s">
+        <v>178</v>
+      </c>
+      <c r="F165" t="s">
+        <v>179</v>
+      </c>
+      <c r="G165" t="s">
+        <v>180</v>
+      </c>
+      <c r="H165" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I165">
+        <v>116.07</v>
+      </c>
+      <c r="J165">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" t="s">
+        <v>133</v>
+      </c>
+      <c r="B166" t="s">
+        <v>148</v>
+      </c>
+      <c r="C166" t="s">
+        <v>174</v>
+      </c>
+      <c r="D166" t="s">
+        <v>176</v>
+      </c>
+      <c r="E166" t="s">
+        <v>178</v>
+      </c>
+      <c r="F166" t="s">
+        <v>179</v>
+      </c>
+      <c r="G166" t="s">
+        <v>180</v>
+      </c>
+      <c r="H166" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I166">
+        <v>115.74</v>
+      </c>
+      <c r="J166">
+        <v>115.71</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" t="s">
+        <v>134</v>
+      </c>
+      <c r="B167" t="s">
+        <v>157</v>
+      </c>
+      <c r="C167" t="s">
+        <v>174</v>
+      </c>
+      <c r="D167" t="s">
+        <v>176</v>
+      </c>
+      <c r="E167" t="s">
+        <v>178</v>
+      </c>
+      <c r="F167" t="s">
+        <v>179</v>
+      </c>
+      <c r="G167" t="s">
+        <v>180</v>
+      </c>
+      <c r="H167" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I167">
+        <v>119.89</v>
+      </c>
+      <c r="J167">
+        <v>119.81</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" t="s">
+        <v>135</v>
+      </c>
+      <c r="B168" t="s">
+        <v>159</v>
+      </c>
+      <c r="C168" t="s">
+        <v>174</v>
+      </c>
+      <c r="D168" t="s">
+        <v>176</v>
+      </c>
+      <c r="E168" t="s">
+        <v>178</v>
+      </c>
+      <c r="F168" t="s">
+        <v>179</v>
+      </c>
+      <c r="G168" t="s">
+        <v>180</v>
+      </c>
+      <c r="H168" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I168">
+        <v>116.07</v>
+      </c>
+      <c r="J168">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" t="s">
+        <v>136</v>
+      </c>
+      <c r="B169" t="s">
+        <v>157</v>
+      </c>
+      <c r="C169" t="s">
+        <v>174</v>
+      </c>
+      <c r="D169" t="s">
+        <v>176</v>
+      </c>
+      <c r="E169" t="s">
+        <v>178</v>
+      </c>
+      <c r="F169" t="s">
+        <v>179</v>
+      </c>
+      <c r="G169" t="s">
+        <v>180</v>
+      </c>
+      <c r="H169" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I169">
+        <v>121.25</v>
+      </c>
+      <c r="J169">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" t="s">
+        <v>137</v>
+      </c>
+      <c r="B170" t="s">
+        <v>153</v>
+      </c>
+      <c r="C170" t="s">
+        <v>174</v>
+      </c>
+      <c r="D170" t="s">
+        <v>176</v>
+      </c>
+      <c r="E170" t="s">
+        <v>178</v>
+      </c>
+      <c r="F170" t="s">
+        <v>179</v>
+      </c>
+      <c r="G170" t="s">
+        <v>180</v>
+      </c>
+      <c r="H170" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I170">
+        <v>116.07</v>
+      </c>
+      <c r="J170">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" t="s">
+        <v>138</v>
+      </c>
+      <c r="B171" t="s">
+        <v>153</v>
+      </c>
+      <c r="C171" t="s">
+        <v>174</v>
+      </c>
+      <c r="D171" t="s">
+        <v>176</v>
+      </c>
+      <c r="E171" t="s">
+        <v>178</v>
+      </c>
+      <c r="F171" t="s">
+        <v>179</v>
+      </c>
+      <c r="G171" t="s">
+        <v>180</v>
+      </c>
+      <c r="H171" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I171">
+        <v>117.48</v>
+      </c>
+      <c r="J171">
+        <v>117.53</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" t="s">
+        <v>139</v>
+      </c>
+      <c r="B172" t="s">
+        <v>146</v>
+      </c>
+      <c r="C172" t="s">
+        <v>174</v>
+      </c>
+      <c r="D172" t="s">
+        <v>176</v>
+      </c>
+      <c r="E172" t="s">
+        <v>178</v>
+      </c>
+      <c r="F172" t="s">
+        <v>179</v>
+      </c>
+      <c r="G172" t="s">
+        <v>180</v>
+      </c>
+      <c r="H172" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I172">
+        <v>112.28</v>
+      </c>
+      <c r="J172">
+        <v>112.26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" t="s">
+        <v>140</v>
+      </c>
+      <c r="B173" t="s">
+        <v>172</v>
+      </c>
+      <c r="C173" t="s">
+        <v>174</v>
+      </c>
+      <c r="D173" t="s">
+        <v>176</v>
+      </c>
+      <c r="E173" t="s">
+        <v>178</v>
+      </c>
+      <c r="F173" t="s">
+        <v>179</v>
+      </c>
+      <c r="G173" t="s">
+        <v>180</v>
+      </c>
+      <c r="H173" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I173">
+        <v>114.12</v>
+      </c>
+      <c r="J173">
+        <v>114.23</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" t="s">
+        <v>141</v>
+      </c>
+      <c r="B174" t="s">
+        <v>170</v>
+      </c>
+      <c r="C174" t="s">
+        <v>174</v>
+      </c>
+      <c r="D174" t="s">
+        <v>176</v>
+      </c>
+      <c r="E174" t="s">
+        <v>178</v>
+      </c>
+      <c r="F174" t="s">
+        <v>179</v>
+      </c>
+      <c r="G174" t="s">
+        <v>180</v>
+      </c>
+      <c r="H174" s="2">
+        <v>45145</v>
+      </c>
+      <c r="I174">
+        <v>119.35</v>
+      </c>
+      <c r="J174">
+        <v>119.25</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="196">
   <si>
     <t>Name</t>
   </si>
@@ -442,6 +442,39 @@
     <t>YUAN Liying</t>
   </si>
   <si>
+    <t>KOUAMI Taky Marie-Divine</t>
+  </si>
+  <si>
+    <t>BELL Lauren</t>
+  </si>
+  <si>
+    <t>SAKAI Aki</t>
+  </si>
+  <si>
+    <t>SALAZAR VALLES Jessica</t>
+  </si>
+  <si>
+    <t>VERDUGO OSUNA Yuli</t>
+  </si>
+  <si>
+    <t>GAXIOLA GONZALEZ Luz Daniela</t>
+  </si>
+  <si>
+    <t>LAMBERINK Kyra</t>
+  </si>
+  <si>
+    <t>PETCH Rebecca</t>
+  </si>
+  <si>
+    <t>KARWACKA Marlena</t>
+  </si>
+  <si>
+    <t>LOS Urszula</t>
+  </si>
+  <si>
+    <t>BAO Shanju</t>
+  </si>
+  <si>
     <t>NZL</t>
   </si>
   <si>
@@ -548,6 +581,9 @@
   </si>
   <si>
     <t>Keirin</t>
+  </si>
+  <si>
+    <t>Team Sprint</t>
   </si>
   <si>
     <t>Null</t>
@@ -927,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -967,22 +1003,22 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H2" s="2">
         <v>45141</v>
@@ -999,22 +1035,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H3" s="2">
         <v>45141</v>
@@ -1031,22 +1067,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H4" s="2">
         <v>45141</v>
@@ -1063,22 +1099,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H5" s="2">
         <v>45141</v>
@@ -1095,22 +1131,22 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H6" s="2">
         <v>45141</v>
@@ -1127,22 +1163,22 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H7" s="2">
         <v>45141</v>
@@ -1159,22 +1195,22 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H8" s="2">
         <v>45141</v>
@@ -1191,22 +1227,22 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G9" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H9" s="2">
         <v>45141</v>
@@ -1223,22 +1259,22 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H10" s="2">
         <v>45141</v>
@@ -1255,22 +1291,22 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G11" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H11" s="2">
         <v>45141</v>
@@ -1287,22 +1323,22 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H12" s="2">
         <v>45141</v>
@@ -1319,22 +1355,22 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G13" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H13" s="2">
         <v>45141</v>
@@ -1351,22 +1387,22 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H14" s="2">
         <v>45141</v>
@@ -1383,22 +1419,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H15" s="2">
         <v>45141</v>
@@ -1415,22 +1451,22 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H16" s="2">
         <v>45141</v>
@@ -1447,22 +1483,22 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G17" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2">
         <v>45141</v>
@@ -1479,22 +1515,22 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G18" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H18" s="2">
         <v>45141</v>
@@ -1511,22 +1547,22 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G19" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H19" s="2">
         <v>45141</v>
@@ -1543,22 +1579,22 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H20" s="2">
         <v>45141</v>
@@ -1575,22 +1611,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E21">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H21" s="2">
         <v>45141</v>
@@ -1607,22 +1643,22 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H22" s="2">
         <v>45142</v>
@@ -1639,22 +1675,22 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H23" s="2">
         <v>45142</v>
@@ -1671,22 +1707,22 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G24" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H24" s="2">
         <v>45142</v>
@@ -1703,22 +1739,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G25" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H25" s="2">
         <v>45142</v>
@@ -1735,22 +1771,22 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H26" s="2">
         <v>45143</v>
@@ -1767,22 +1803,22 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D27" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H27" s="2">
         <v>45143</v>
@@ -1799,22 +1835,22 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H28" s="2">
         <v>45143</v>
@@ -1831,22 +1867,22 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D29" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H29" s="2">
         <v>45143</v>
@@ -1863,22 +1899,22 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G30" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H30" s="2">
         <v>45143</v>
@@ -1895,22 +1931,22 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D31" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G31" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H31" s="2">
         <v>45143</v>
@@ -1927,22 +1963,22 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G32" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H32" s="2">
         <v>45143</v>
@@ -1959,22 +1995,22 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G33" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H33" s="2">
         <v>45143</v>
@@ -1991,22 +2027,22 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G34" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H34" s="2">
         <v>45142</v>
@@ -2023,22 +2059,22 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D35" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G35" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H35" s="2">
         <v>45142</v>
@@ -2055,22 +2091,22 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G36" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H36" s="2">
         <v>45142</v>
@@ -2087,22 +2123,22 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G37" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H37" s="2">
         <v>45142</v>
@@ -2119,22 +2155,22 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F38" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H38" s="2">
         <v>45143</v>
@@ -2151,22 +2187,22 @@
         <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E39" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G39" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H39" s="2">
         <v>45143</v>
@@ -2183,22 +2219,22 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F40" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G40" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H40" s="2">
         <v>45143</v>
@@ -2215,22 +2251,22 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F41" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G41" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H41" s="2">
         <v>45143</v>
@@ -2247,22 +2283,22 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D42" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E42" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F42" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G42" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H42" s="2">
         <v>45143</v>
@@ -2279,22 +2315,22 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D43" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E43" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F43" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G43" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H43" s="2">
         <v>45143</v>
@@ -2311,22 +2347,22 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D44" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E44" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F44" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G44" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H44" s="2">
         <v>45143</v>
@@ -2343,22 +2379,22 @@
         <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D45" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E45" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G45" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H45" s="2">
         <v>45143</v>
@@ -2375,22 +2411,22 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D46" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E46" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F46" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G46" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H46" s="2">
         <v>45143</v>
@@ -2407,22 +2443,22 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D47" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E47" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F47" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G47" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H47" s="2">
         <v>45143</v>
@@ -2439,22 +2475,22 @@
         <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D48" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F48" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G48" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H48" s="2">
         <v>45143</v>
@@ -2471,22 +2507,22 @@
         <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D49" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F49" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G49" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H49" s="2">
         <v>45143</v>
@@ -2503,22 +2539,22 @@
         <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C50" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F50" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G50" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H50" s="2">
         <v>45143</v>
@@ -2535,22 +2571,22 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E51" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F51" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G51" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H51" s="2">
         <v>45143</v>
@@ -2567,22 +2603,22 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D52" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E52" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F52" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H52" s="2">
         <v>45143</v>
@@ -2599,22 +2635,22 @@
         <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D53" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E53" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F53" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G53" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H53" s="2">
         <v>45143</v>
@@ -2631,22 +2667,22 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D54" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F54" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G54" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H54" s="2">
         <v>45143</v>
@@ -2663,22 +2699,22 @@
         <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E55" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F55" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G55" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H55" s="2">
         <v>45143</v>
@@ -2695,22 +2731,22 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F56" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G56" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H56" s="2">
         <v>45143</v>
@@ -2727,22 +2763,22 @@
         <v>52</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C57" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D57" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F57" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G57" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H57" s="2">
         <v>45143</v>
@@ -2759,22 +2795,22 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E58" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G58" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H58" s="2">
         <v>45143</v>
@@ -2791,22 +2827,22 @@
         <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D59" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E59" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F59" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G59" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H59" s="2">
         <v>45143</v>
@@ -2823,22 +2859,22 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D60" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F60" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G60" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H60" s="2">
         <v>45143</v>
@@ -2855,22 +2891,22 @@
         <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E61" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F61" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G61" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H61" s="2">
         <v>45143</v>
@@ -2887,22 +2923,22 @@
         <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C62" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E62" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F62" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G62" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H62" s="2">
         <v>45143</v>
@@ -2919,22 +2955,22 @@
         <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C63" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D63" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E63" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F63" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G63" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H63" s="2">
         <v>45143</v>
@@ -2951,22 +2987,22 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C64" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D64" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E64" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F64" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G64" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H64" s="2">
         <v>45143</v>
@@ -2983,22 +3019,22 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F65" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G65" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H65" s="2">
         <v>45143</v>
@@ -3015,22 +3051,22 @@
         <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D66" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E66" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F66" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G66" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H66" s="2">
         <v>45143</v>
@@ -3047,22 +3083,22 @@
         <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C67" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D67" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E67" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F67" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G67" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H67" s="2">
         <v>45143</v>
@@ -3079,22 +3115,22 @@
         <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D68" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E68" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F68" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G68" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H68" s="2">
         <v>45143</v>
@@ -3111,22 +3147,22 @@
         <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D69" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E69" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F69" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G69" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H69" s="2">
         <v>45143</v>
@@ -3143,22 +3179,22 @@
         <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E70" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F70" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G70" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H70" s="2">
         <v>45143</v>
@@ -3175,22 +3211,22 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C71" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D71" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E71" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F71" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G71" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H71" s="2">
         <v>45147</v>
@@ -3207,22 +3243,22 @@
         <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C72" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E72" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F72" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G72" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H72" s="2">
         <v>45147</v>
@@ -3239,22 +3275,22 @@
         <v>49</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C73" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E73" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F73" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G73" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H73" s="2">
         <v>45147</v>
@@ -3271,22 +3307,22 @@
         <v>34</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E74" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F74" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G74" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H74" s="2">
         <v>45147</v>
@@ -3303,22 +3339,22 @@
         <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D75" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E75" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F75" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G75" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H75" s="2">
         <v>45147</v>
@@ -3335,22 +3371,22 @@
         <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E76" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F76" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G76" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H76" s="2">
         <v>45147</v>
@@ -3367,22 +3403,22 @@
         <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D77" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E77" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F77" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G77" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H77" s="2">
         <v>45147</v>
@@ -3399,22 +3435,22 @@
         <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C78" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E78" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F78" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G78" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H78" s="2">
         <v>45147</v>
@@ -3431,22 +3467,22 @@
         <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E79" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F79" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G79" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H79" s="2">
         <v>45147</v>
@@ -3463,22 +3499,22 @@
         <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C80" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E80" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F80" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G80" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H80" s="2">
         <v>45147</v>
@@ -3495,22 +3531,22 @@
         <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C81" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E81" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F81" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G81" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H81" s="2">
         <v>45147</v>
@@ -3527,22 +3563,22 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D82" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E82" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F82" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G82" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H82" s="2">
         <v>45147</v>
@@ -3559,22 +3595,22 @@
         <v>35</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C83" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D83" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E83" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F83" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G83" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H83" s="2">
         <v>45146</v>
@@ -3591,22 +3627,22 @@
         <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D84" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E84" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F84" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G84" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H84" s="2">
         <v>45146</v>
@@ -3623,22 +3659,22 @@
         <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D85" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F85" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G85" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H85" s="2">
         <v>45146</v>
@@ -3655,22 +3691,22 @@
         <v>69</v>
       </c>
       <c r="B86" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D86" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E86" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G86" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H86" s="2">
         <v>45146</v>
@@ -3687,22 +3723,22 @@
         <v>49</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E87" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F87" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G87" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H87" s="2">
         <v>45146</v>
@@ -3719,22 +3755,22 @@
         <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C88" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E88" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F88" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G88" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H88" s="2">
         <v>45146</v>
@@ -3751,22 +3787,22 @@
         <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C89" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D89" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E89" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F89" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G89" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H89" s="2">
         <v>45146</v>
@@ -3783,22 +3819,22 @@
         <v>53</v>
       </c>
       <c r="B90" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C90" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D90" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E90" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F90" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G90" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H90" s="2">
         <v>45146</v>
@@ -3815,22 +3851,22 @@
         <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C91" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D91" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E91" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F91" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G91" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H91" s="2">
         <v>45146</v>
@@ -3847,22 +3883,22 @@
         <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C92" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E92" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F92" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G92" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H92" s="2">
         <v>45146</v>
@@ -3879,22 +3915,22 @@
         <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D93" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E93" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F93" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G93" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H93" s="2">
         <v>45146</v>
@@ -3911,22 +3947,22 @@
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D94" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E94" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F94" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G94" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H94" s="2">
         <v>45146</v>
@@ -3943,22 +3979,22 @@
         <v>71</v>
       </c>
       <c r="B95" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C95" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E95" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G95" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H95" s="2">
         <v>45146</v>
@@ -3975,22 +4011,22 @@
         <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C96" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D96" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E96" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F96" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G96" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H96" s="2">
         <v>45146</v>
@@ -4007,22 +4043,22 @@
         <v>72</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C97" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D97" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E97" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F97" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G97" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H97" s="2">
         <v>45146</v>
@@ -4039,22 +4075,22 @@
         <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C98" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E98" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F98" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G98" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H98" s="2">
         <v>45146</v>
@@ -4071,22 +4107,22 @@
         <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C99" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D99" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E99" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F99" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G99" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H99" s="2">
         <v>45146</v>
@@ -4103,22 +4139,22 @@
         <v>73</v>
       </c>
       <c r="B100" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C100" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E100" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F100" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G100" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H100" s="2">
         <v>45146</v>
@@ -4135,22 +4171,22 @@
         <v>74</v>
       </c>
       <c r="B101" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C101" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D101" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E101" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F101" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G101" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H101" s="2">
         <v>45146</v>
@@ -4167,22 +4203,22 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C102" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D102" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E102" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F102" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G102" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H102" s="2">
         <v>45146</v>
@@ -4199,22 +4235,22 @@
         <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C103" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D103" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E103" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F103" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G103" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H103" s="2">
         <v>45146</v>
@@ -4231,22 +4267,22 @@
         <v>55</v>
       </c>
       <c r="B104" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D104" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E104" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F104" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G104" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H104" s="2">
         <v>45146</v>
@@ -4263,22 +4299,22 @@
         <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C105" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D105" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E105" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F105" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G105" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H105" s="2">
         <v>45146</v>
@@ -4295,22 +4331,22 @@
         <v>75</v>
       </c>
       <c r="B106" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C106" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D106" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E106" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F106" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G106" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H106" s="2">
         <v>45146</v>
@@ -4327,22 +4363,22 @@
         <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C107" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D107" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E107" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F107" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G107" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H107" s="2">
         <v>45146</v>
@@ -4359,22 +4395,22 @@
         <v>62</v>
       </c>
       <c r="B108" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C108" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D108" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E108" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F108" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G108" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H108" s="2">
         <v>45146</v>
@@ -4391,22 +4427,22 @@
         <v>76</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C109" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D109" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E109" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F109" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G109" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H109" s="2">
         <v>45146</v>
@@ -4423,22 +4459,22 @@
         <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C110" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E110" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F110" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G110" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H110" s="2">
         <v>45146</v>
@@ -4455,22 +4491,22 @@
         <v>78</v>
       </c>
       <c r="B111" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C111" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D111" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G111" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H111" s="2">
         <v>45142</v>
@@ -4487,22 +4523,22 @@
         <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C112" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D112" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E112">
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G112" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H112" s="2">
         <v>45142</v>
@@ -4519,22 +4555,22 @@
         <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C113" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D113" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G113" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H113" s="2">
         <v>45142</v>
@@ -4551,22 +4587,22 @@
         <v>81</v>
       </c>
       <c r="B114" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C114" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D114" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E114">
         <v>4</v>
       </c>
       <c r="F114" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G114" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H114" s="2">
         <v>45142</v>
@@ -4583,22 +4619,22 @@
         <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C115" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D115" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G115" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H115" s="2">
         <v>45142</v>
@@ -4615,22 +4651,22 @@
         <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C116" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D116" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E116">
         <v>2</v>
       </c>
       <c r="F116" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G116" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H116" s="2">
         <v>45142</v>
@@ -4647,22 +4683,22 @@
         <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C117" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D117" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G117" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H117" s="2">
         <v>45142</v>
@@ -4679,22 +4715,22 @@
         <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C118" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D118" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E118">
         <v>4</v>
       </c>
       <c r="F118" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G118" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H118" s="2">
         <v>45142</v>
@@ -4711,22 +4747,22 @@
         <v>86</v>
       </c>
       <c r="B119" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C119" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D119" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E119">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G119" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H119" s="2">
         <v>45142</v>
@@ -4743,22 +4779,22 @@
         <v>87</v>
       </c>
       <c r="B120" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C120" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D120" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E120">
         <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G120" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H120" s="2">
         <v>45142</v>
@@ -4775,22 +4811,22 @@
         <v>88</v>
       </c>
       <c r="B121" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D121" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G121" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H121" s="2">
         <v>45142</v>
@@ -4807,22 +4843,22 @@
         <v>89</v>
       </c>
       <c r="B122" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C122" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D122" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E122">
         <v>4</v>
       </c>
       <c r="F122" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G122" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H122" s="2">
         <v>45142</v>
@@ -4839,22 +4875,22 @@
         <v>90</v>
       </c>
       <c r="B123" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C123" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D123" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E123">
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G123" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H123" s="2">
         <v>45142</v>
@@ -4871,22 +4907,22 @@
         <v>91</v>
       </c>
       <c r="B124" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C124" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E124">
         <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G124" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H124" s="2">
         <v>45142</v>
@@ -4903,22 +4939,22 @@
         <v>92</v>
       </c>
       <c r="B125" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C125" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D125" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G125" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H125" s="2">
         <v>45142</v>
@@ -4935,22 +4971,22 @@
         <v>93</v>
       </c>
       <c r="B126" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C126" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D126" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
       <c r="F126" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G126" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H126" s="2">
         <v>45142</v>
@@ -4967,22 +5003,22 @@
         <v>94</v>
       </c>
       <c r="B127" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C127" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D127" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E127">
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G127" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H127" s="2">
         <v>45142</v>
@@ -4999,22 +5035,22 @@
         <v>95</v>
       </c>
       <c r="B128" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C128" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D128" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E128">
         <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G128" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H128" s="2">
         <v>45142</v>
@@ -5031,22 +5067,22 @@
         <v>96</v>
       </c>
       <c r="B129" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C129" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D129" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G129" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H129" s="2">
         <v>45142</v>
@@ -5063,22 +5099,22 @@
         <v>97</v>
       </c>
       <c r="B130" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C130" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D130" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E130">
         <v>4</v>
       </c>
       <c r="F130" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G130" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H130" s="2">
         <v>45142</v>
@@ -5095,22 +5131,22 @@
         <v>98</v>
       </c>
       <c r="B131" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C131" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D131" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E131">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G131" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H131" s="2">
         <v>45142</v>
@@ -5127,22 +5163,22 @@
         <v>99</v>
       </c>
       <c r="B132" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C132" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D132" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E132">
         <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G132" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H132" s="2">
         <v>45142</v>
@@ -5159,22 +5195,22 @@
         <v>100</v>
       </c>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C133" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D133" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E133">
         <v>3</v>
       </c>
       <c r="F133" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G133" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H133" s="2">
         <v>45142</v>
@@ -5191,22 +5227,22 @@
         <v>101</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C134" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D134" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E134">
         <v>4</v>
       </c>
       <c r="F134" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G134" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H134" s="2">
         <v>45142</v>
@@ -5223,22 +5259,22 @@
         <v>102</v>
       </c>
       <c r="B135" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C135" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D135" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G135" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H135" s="2">
         <v>45142</v>
@@ -5255,22 +5291,22 @@
         <v>103</v>
       </c>
       <c r="B136" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C136" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D136" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E136">
         <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G136" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H136" s="2">
         <v>45142</v>
@@ -5287,22 +5323,22 @@
         <v>104</v>
       </c>
       <c r="B137" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C137" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D137" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G137" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H137" s="2">
         <v>45142</v>
@@ -5319,22 +5355,22 @@
         <v>105</v>
       </c>
       <c r="B138" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C138" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E138">
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G138" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H138" s="2">
         <v>45142</v>
@@ -5351,22 +5387,22 @@
         <v>106</v>
       </c>
       <c r="B139" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C139" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D139" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E139" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F139" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G139" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H139" s="2">
         <v>45145</v>
@@ -5383,22 +5419,22 @@
         <v>107</v>
       </c>
       <c r="B140" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D140" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E140" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F140" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G140" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H140" s="2">
         <v>45145</v>
@@ -5415,22 +5451,22 @@
         <v>108</v>
       </c>
       <c r="B141" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C141" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D141" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E141" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F141" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G141" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H141" s="2">
         <v>45145</v>
@@ -5447,22 +5483,22 @@
         <v>109</v>
       </c>
       <c r="B142" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D142" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E142" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F142" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G142" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H142" s="2">
         <v>45145</v>
@@ -5479,22 +5515,22 @@
         <v>110</v>
       </c>
       <c r="B143" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D143" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E143" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F143" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G143" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H143" s="2">
         <v>45145</v>
@@ -5511,22 +5547,22 @@
         <v>111</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D144" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E144" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F144" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G144" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H144" s="2">
         <v>45145</v>
@@ -5543,22 +5579,22 @@
         <v>112</v>
       </c>
       <c r="B145" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C145" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D145" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E145" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F145" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G145" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H145" s="2">
         <v>45145</v>
@@ -5575,22 +5611,22 @@
         <v>113</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C146" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D146" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E146" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F146" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G146" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H146" s="2">
         <v>45145</v>
@@ -5607,22 +5643,22 @@
         <v>114</v>
       </c>
       <c r="B147" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C147" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D147" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E147" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F147" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G147" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H147" s="2">
         <v>45145</v>
@@ -5639,22 +5675,22 @@
         <v>115</v>
       </c>
       <c r="B148" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D148" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E148" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F148" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G148" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H148" s="2">
         <v>45145</v>
@@ -5671,22 +5707,22 @@
         <v>116</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C149" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D149" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E149" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F149" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G149" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H149" s="2">
         <v>45145</v>
@@ -5703,22 +5739,22 @@
         <v>117</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C150" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D150" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E150" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F150" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G150" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H150" s="2">
         <v>45145</v>
@@ -5735,22 +5771,22 @@
         <v>118</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C151" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D151" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E151" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F151" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G151" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H151" s="2">
         <v>45145</v>
@@ -5767,22 +5803,22 @@
         <v>119</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C152" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D152" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E152" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F152" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G152" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H152" s="2">
         <v>45145</v>
@@ -5799,22 +5835,22 @@
         <v>120</v>
       </c>
       <c r="B153" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C153" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D153" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E153" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F153" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G153" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H153" s="2">
         <v>45145</v>
@@ -5831,22 +5867,22 @@
         <v>121</v>
       </c>
       <c r="B154" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C154" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D154" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E154" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F154" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G154" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H154" s="2">
         <v>45145</v>
@@ -5863,22 +5899,22 @@
         <v>122</v>
       </c>
       <c r="B155" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C155" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D155" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E155" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F155" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G155" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H155" s="2">
         <v>45145</v>
@@ -5895,22 +5931,22 @@
         <v>123</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C156" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D156" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E156" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F156" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G156" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H156" s="2">
         <v>45145</v>
@@ -5927,22 +5963,22 @@
         <v>124</v>
       </c>
       <c r="B157" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C157" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D157" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E157" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F157" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G157" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H157" s="2">
         <v>45145</v>
@@ -5959,22 +5995,22 @@
         <v>125</v>
       </c>
       <c r="B158" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C158" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D158" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E158" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F158" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G158" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H158" s="2">
         <v>45145</v>
@@ -5991,22 +6027,22 @@
         <v>126</v>
       </c>
       <c r="B159" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D159" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E159" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F159" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G159" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H159" s="2">
         <v>45145</v>
@@ -6023,22 +6059,22 @@
         <v>127</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C160" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D160" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E160" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F160" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G160" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H160" s="2">
         <v>45145</v>
@@ -6055,22 +6091,22 @@
         <v>128</v>
       </c>
       <c r="B161" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C161" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D161" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E161" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F161" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G161" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H161" s="2">
         <v>45145</v>
@@ -6087,22 +6123,22 @@
         <v>129</v>
       </c>
       <c r="B162" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C162" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D162" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E162" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F162" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G162" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H162" s="2">
         <v>45145</v>
@@ -6119,22 +6155,22 @@
         <v>130</v>
       </c>
       <c r="B163" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C163" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D163" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E163" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F163" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G163" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H163" s="2">
         <v>45145</v>
@@ -6151,22 +6187,22 @@
         <v>131</v>
       </c>
       <c r="B164" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C164" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D164" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E164" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F164" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G164" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H164" s="2">
         <v>45145</v>
@@ -6183,22 +6219,22 @@
         <v>132</v>
       </c>
       <c r="B165" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D165" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E165" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F165" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G165" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H165" s="2">
         <v>45145</v>
@@ -6215,22 +6251,22 @@
         <v>133</v>
       </c>
       <c r="B166" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C166" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D166" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E166" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F166" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G166" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H166" s="2">
         <v>45145</v>
@@ -6247,22 +6283,22 @@
         <v>134</v>
       </c>
       <c r="B167" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C167" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D167" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E167" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F167" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G167" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H167" s="2">
         <v>45145</v>
@@ -6279,22 +6315,22 @@
         <v>135</v>
       </c>
       <c r="B168" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C168" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D168" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E168" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F168" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G168" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H168" s="2">
         <v>45145</v>
@@ -6311,22 +6347,22 @@
         <v>136</v>
       </c>
       <c r="B169" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C169" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D169" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E169" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F169" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G169" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H169" s="2">
         <v>45145</v>
@@ -6343,22 +6379,22 @@
         <v>137</v>
       </c>
       <c r="B170" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C170" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D170" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E170" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F170" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G170" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H170" s="2">
         <v>45145</v>
@@ -6375,22 +6411,22 @@
         <v>138</v>
       </c>
       <c r="B171" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C171" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D171" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E171" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F171" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G171" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H171" s="2">
         <v>45145</v>
@@ -6407,22 +6443,22 @@
         <v>139</v>
       </c>
       <c r="B172" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C172" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D172" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E172" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F172" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G172" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H172" s="2">
         <v>45145</v>
@@ -6439,22 +6475,22 @@
         <v>140</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C173" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D173" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E173" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F173" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G173" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H173" s="2">
         <v>45145</v>
@@ -6471,22 +6507,22 @@
         <v>141</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C174" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D174" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E174" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F174" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G174" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H174" s="2">
         <v>45145</v>
@@ -6496,6 +6532,2118 @@
       </c>
       <c r="J174">
         <v>119.25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" t="s">
+        <v>142</v>
+      </c>
+      <c r="B175" t="s">
+        <v>163</v>
+      </c>
+      <c r="C175" t="s">
+        <v>185</v>
+      </c>
+      <c r="D175" t="s">
+        <v>189</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="F175" t="s">
+        <v>191</v>
+      </c>
+      <c r="G175" t="s">
+        <v>192</v>
+      </c>
+      <c r="H175" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I175">
+        <v>114.48</v>
+      </c>
+      <c r="J175">
+        <v>114.35</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" t="s">
+        <v>126</v>
+      </c>
+      <c r="B176" t="s">
+        <v>163</v>
+      </c>
+      <c r="C176" t="s">
+        <v>185</v>
+      </c>
+      <c r="D176" t="s">
+        <v>189</v>
+      </c>
+      <c r="E176">
+        <v>2</v>
+      </c>
+      <c r="F176" t="s">
+        <v>191</v>
+      </c>
+      <c r="G176" t="s">
+        <v>192</v>
+      </c>
+      <c r="H176" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I176">
+        <v>112.44</v>
+      </c>
+      <c r="J176">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" t="s">
+        <v>119</v>
+      </c>
+      <c r="B177" t="s">
+        <v>163</v>
+      </c>
+      <c r="C177" t="s">
+        <v>185</v>
+      </c>
+      <c r="D177" t="s">
+        <v>189</v>
+      </c>
+      <c r="E177">
+        <v>3</v>
+      </c>
+      <c r="F177" t="s">
+        <v>191</v>
+      </c>
+      <c r="G177" t="s">
+        <v>192</v>
+      </c>
+      <c r="H177" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I177">
+        <v>116.48</v>
+      </c>
+      <c r="J177">
+        <v>116.44</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" t="s">
+        <v>143</v>
+      </c>
+      <c r="B178" t="s">
+        <v>155</v>
+      </c>
+      <c r="C178" t="s">
+        <v>185</v>
+      </c>
+      <c r="D178" t="s">
+        <v>189</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178" t="s">
+        <v>191</v>
+      </c>
+      <c r="G178" t="s">
+        <v>192</v>
+      </c>
+      <c r="H178" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I178">
+        <v>96.62</v>
+      </c>
+      <c r="J178">
+        <v>96.63</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" t="s">
+        <v>109</v>
+      </c>
+      <c r="B179" t="s">
+        <v>155</v>
+      </c>
+      <c r="C179" t="s">
+        <v>185</v>
+      </c>
+      <c r="D179" t="s">
+        <v>189</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="F179" t="s">
+        <v>191</v>
+      </c>
+      <c r="G179" t="s">
+        <v>192</v>
+      </c>
+      <c r="H179" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I179">
+        <v>114.3</v>
+      </c>
+      <c r="J179">
+        <v>114.35</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" t="s">
+        <v>113</v>
+      </c>
+      <c r="B180" t="s">
+        <v>155</v>
+      </c>
+      <c r="C180" t="s">
+        <v>185</v>
+      </c>
+      <c r="D180" t="s">
+        <v>189</v>
+      </c>
+      <c r="E180">
+        <v>3</v>
+      </c>
+      <c r="F180" t="s">
+        <v>191</v>
+      </c>
+      <c r="G180" t="s">
+        <v>192</v>
+      </c>
+      <c r="H180" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I180">
+        <v>111.93</v>
+      </c>
+      <c r="J180">
+        <v>111.86</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" t="s">
+        <v>118</v>
+      </c>
+      <c r="B181" t="s">
+        <v>162</v>
+      </c>
+      <c r="C181" t="s">
+        <v>185</v>
+      </c>
+      <c r="D181" t="s">
+        <v>189</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181" t="s">
+        <v>191</v>
+      </c>
+      <c r="G181" t="s">
+        <v>192</v>
+      </c>
+      <c r="H181" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I181">
+        <v>96.89</v>
+      </c>
+      <c r="J181">
+        <v>96.88</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" t="s">
+        <v>162</v>
+      </c>
+      <c r="C182" t="s">
+        <v>185</v>
+      </c>
+      <c r="D182" t="s">
+        <v>189</v>
+      </c>
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="F182" t="s">
+        <v>191</v>
+      </c>
+      <c r="G182" t="s">
+        <v>192</v>
+      </c>
+      <c r="H182" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I182">
+        <v>106.91</v>
+      </c>
+      <c r="J182">
+        <v>106.65</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" t="s">
+        <v>114</v>
+      </c>
+      <c r="B183" t="s">
+        <v>162</v>
+      </c>
+      <c r="C183" t="s">
+        <v>185</v>
+      </c>
+      <c r="D183" t="s">
+        <v>189</v>
+      </c>
+      <c r="E183">
+        <v>3</v>
+      </c>
+      <c r="F183" t="s">
+        <v>191</v>
+      </c>
+      <c r="G183" t="s">
+        <v>192</v>
+      </c>
+      <c r="H183" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I183">
+        <v>108.71</v>
+      </c>
+      <c r="J183">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" t="s">
+        <v>144</v>
+      </c>
+      <c r="B184" t="s">
+        <v>168</v>
+      </c>
+      <c r="C184" t="s">
+        <v>185</v>
+      </c>
+      <c r="D184" t="s">
+        <v>189</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184" t="s">
+        <v>191</v>
+      </c>
+      <c r="G184" t="s">
+        <v>192</v>
+      </c>
+      <c r="H184" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I184">
+        <v>95.17</v>
+      </c>
+      <c r="J184">
+        <v>95.14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" t="s">
+        <v>134</v>
+      </c>
+      <c r="B185" t="s">
+        <v>168</v>
+      </c>
+      <c r="C185" t="s">
+        <v>185</v>
+      </c>
+      <c r="D185" t="s">
+        <v>189</v>
+      </c>
+      <c r="E185">
+        <v>2</v>
+      </c>
+      <c r="F185" t="s">
+        <v>191</v>
+      </c>
+      <c r="G185" t="s">
+        <v>192</v>
+      </c>
+      <c r="H185" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I185">
+        <v>106.02</v>
+      </c>
+      <c r="J185">
+        <v>106.07</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" t="s">
+        <v>136</v>
+      </c>
+      <c r="B186" t="s">
+        <v>168</v>
+      </c>
+      <c r="C186" t="s">
+        <v>185</v>
+      </c>
+      <c r="D186" t="s">
+        <v>189</v>
+      </c>
+      <c r="E186">
+        <v>3</v>
+      </c>
+      <c r="F186" t="s">
+        <v>191</v>
+      </c>
+      <c r="G186" t="s">
+        <v>192</v>
+      </c>
+      <c r="H186" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I186">
+        <v>105.62</v>
+      </c>
+      <c r="J186">
+        <v>105.55</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187" t="s">
+        <v>145</v>
+      </c>
+      <c r="B187" t="s">
+        <v>180</v>
+      </c>
+      <c r="C187" t="s">
+        <v>185</v>
+      </c>
+      <c r="D187" t="s">
+        <v>189</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187" t="s">
+        <v>191</v>
+      </c>
+      <c r="G187" t="s">
+        <v>192</v>
+      </c>
+      <c r="H187" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I187">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="J187">
+        <v>98.05</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188" t="s">
+        <v>146</v>
+      </c>
+      <c r="B188" t="s">
+        <v>180</v>
+      </c>
+      <c r="C188" t="s">
+        <v>185</v>
+      </c>
+      <c r="D188" t="s">
+        <v>189</v>
+      </c>
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188" t="s">
+        <v>191</v>
+      </c>
+      <c r="G188" t="s">
+        <v>192</v>
+      </c>
+      <c r="H188" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I188">
+        <v>111.99</v>
+      </c>
+      <c r="J188">
+        <v>111.86</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" t="s">
+        <v>147</v>
+      </c>
+      <c r="B189" t="s">
+        <v>180</v>
+      </c>
+      <c r="C189" t="s">
+        <v>185</v>
+      </c>
+      <c r="D189" t="s">
+        <v>189</v>
+      </c>
+      <c r="E189">
+        <v>3</v>
+      </c>
+      <c r="F189" t="s">
+        <v>191</v>
+      </c>
+      <c r="G189" t="s">
+        <v>192</v>
+      </c>
+      <c r="H189" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I189">
+        <v>112.18</v>
+      </c>
+      <c r="J189">
+        <v>112.15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" t="s">
+        <v>148</v>
+      </c>
+      <c r="B190" t="s">
+        <v>164</v>
+      </c>
+      <c r="C190" t="s">
+        <v>185</v>
+      </c>
+      <c r="D190" t="s">
+        <v>189</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190" t="s">
+        <v>191</v>
+      </c>
+      <c r="G190" t="s">
+        <v>192</v>
+      </c>
+      <c r="H190" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I190">
+        <v>98.84</v>
+      </c>
+      <c r="J190">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" t="s">
+        <v>138</v>
+      </c>
+      <c r="B191" t="s">
+        <v>164</v>
+      </c>
+      <c r="C191" t="s">
+        <v>185</v>
+      </c>
+      <c r="D191" t="s">
+        <v>189</v>
+      </c>
+      <c r="E191">
+        <v>2</v>
+      </c>
+      <c r="F191" t="s">
+        <v>191</v>
+      </c>
+      <c r="G191" t="s">
+        <v>192</v>
+      </c>
+      <c r="H191" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I191">
+        <v>112.31</v>
+      </c>
+      <c r="J191">
+        <v>112.26</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" t="s">
+        <v>137</v>
+      </c>
+      <c r="B192" t="s">
+        <v>164</v>
+      </c>
+      <c r="C192" t="s">
+        <v>185</v>
+      </c>
+      <c r="D192" t="s">
+        <v>189</v>
+      </c>
+      <c r="E192">
+        <v>3</v>
+      </c>
+      <c r="F192" t="s">
+        <v>191</v>
+      </c>
+      <c r="G192" t="s">
+        <v>192</v>
+      </c>
+      <c r="H192" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I192">
+        <v>112.84</v>
+      </c>
+      <c r="J192">
+        <v>112.91</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" t="s">
+        <v>149</v>
+      </c>
+      <c r="B193" t="s">
+        <v>153</v>
+      </c>
+      <c r="C193" t="s">
+        <v>185</v>
+      </c>
+      <c r="D193" t="s">
+        <v>189</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193" t="s">
+        <v>191</v>
+      </c>
+      <c r="G193" t="s">
+        <v>192</v>
+      </c>
+      <c r="H193" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I193">
+        <v>97.48</v>
+      </c>
+      <c r="J193">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" t="s">
+        <v>115</v>
+      </c>
+      <c r="B194" t="s">
+        <v>153</v>
+      </c>
+      <c r="C194" t="s">
+        <v>185</v>
+      </c>
+      <c r="D194" t="s">
+        <v>189</v>
+      </c>
+      <c r="E194">
+        <v>2</v>
+      </c>
+      <c r="F194" t="s">
+        <v>191</v>
+      </c>
+      <c r="G194" t="s">
+        <v>192</v>
+      </c>
+      <c r="H194" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I194">
+        <v>103.88</v>
+      </c>
+      <c r="J194">
+        <v>103.85</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" t="s">
+        <v>106</v>
+      </c>
+      <c r="B195" t="s">
+        <v>153</v>
+      </c>
+      <c r="C195" t="s">
+        <v>185</v>
+      </c>
+      <c r="D195" t="s">
+        <v>189</v>
+      </c>
+      <c r="E195">
+        <v>3</v>
+      </c>
+      <c r="F195" t="s">
+        <v>191</v>
+      </c>
+      <c r="G195" t="s">
+        <v>192</v>
+      </c>
+      <c r="H195" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I195">
+        <v>106.06</v>
+      </c>
+      <c r="J195">
+        <v>106.07</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" t="s">
+        <v>150</v>
+      </c>
+      <c r="B196" t="s">
+        <v>170</v>
+      </c>
+      <c r="C196" t="s">
+        <v>185</v>
+      </c>
+      <c r="D196" t="s">
+        <v>189</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196" t="s">
+        <v>191</v>
+      </c>
+      <c r="G196" t="s">
+        <v>192</v>
+      </c>
+      <c r="H196" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I196">
+        <v>96.12</v>
+      </c>
+      <c r="J196">
+        <v>96.19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" t="s">
+        <v>151</v>
+      </c>
+      <c r="B197" t="s">
+        <v>170</v>
+      </c>
+      <c r="C197" t="s">
+        <v>185</v>
+      </c>
+      <c r="D197" t="s">
+        <v>189</v>
+      </c>
+      <c r="E197">
+        <v>2</v>
+      </c>
+      <c r="F197" t="s">
+        <v>191</v>
+      </c>
+      <c r="G197" t="s">
+        <v>192</v>
+      </c>
+      <c r="H197" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I197">
+        <v>109.75</v>
+      </c>
+      <c r="J197">
+        <v>109.8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" t="s">
+        <v>135</v>
+      </c>
+      <c r="B198" t="s">
+        <v>170</v>
+      </c>
+      <c r="C198" t="s">
+        <v>185</v>
+      </c>
+      <c r="D198" t="s">
+        <v>189</v>
+      </c>
+      <c r="E198">
+        <v>3</v>
+      </c>
+      <c r="F198" t="s">
+        <v>191</v>
+      </c>
+      <c r="G198" t="s">
+        <v>192</v>
+      </c>
+      <c r="H198" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I198">
+        <v>109.32</v>
+      </c>
+      <c r="J198">
+        <v>109.42</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" t="s">
+        <v>131</v>
+      </c>
+      <c r="B199" t="s">
+        <v>161</v>
+      </c>
+      <c r="C199" t="s">
+        <v>185</v>
+      </c>
+      <c r="D199" t="s">
+        <v>189</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+      <c r="F199" t="s">
+        <v>191</v>
+      </c>
+      <c r="G199" t="s">
+        <v>192</v>
+      </c>
+      <c r="H199" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I199">
+        <v>91.68000000000001</v>
+      </c>
+      <c r="J199">
+        <v>91.56999999999999</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200" t="s">
+        <v>127</v>
+      </c>
+      <c r="B200" t="s">
+        <v>161</v>
+      </c>
+      <c r="C200" t="s">
+        <v>185</v>
+      </c>
+      <c r="D200" t="s">
+        <v>189</v>
+      </c>
+      <c r="E200">
+        <v>2</v>
+      </c>
+      <c r="F200" t="s">
+        <v>191</v>
+      </c>
+      <c r="G200" t="s">
+        <v>192</v>
+      </c>
+      <c r="H200" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I200">
+        <v>107.91</v>
+      </c>
+      <c r="J200">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201" t="s">
+        <v>117</v>
+      </c>
+      <c r="B201" t="s">
+        <v>161</v>
+      </c>
+      <c r="C201" t="s">
+        <v>185</v>
+      </c>
+      <c r="D201" t="s">
+        <v>189</v>
+      </c>
+      <c r="E201">
+        <v>3</v>
+      </c>
+      <c r="F201" t="s">
+        <v>191</v>
+      </c>
+      <c r="G201" t="s">
+        <v>192</v>
+      </c>
+      <c r="H201" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I201">
+        <v>110.53</v>
+      </c>
+      <c r="J201">
+        <v>110.45</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202" t="s">
+        <v>120</v>
+      </c>
+      <c r="B202" t="s">
+        <v>181</v>
+      </c>
+      <c r="C202" t="s">
+        <v>185</v>
+      </c>
+      <c r="D202" t="s">
+        <v>189</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+      <c r="F202" t="s">
+        <v>191</v>
+      </c>
+      <c r="G202" t="s">
+        <v>192</v>
+      </c>
+      <c r="H202" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I202">
+        <v>91.3</v>
+      </c>
+      <c r="J202">
+        <v>91.29000000000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203" t="s">
+        <v>152</v>
+      </c>
+      <c r="B203" t="s">
+        <v>181</v>
+      </c>
+      <c r="C203" t="s">
+        <v>185</v>
+      </c>
+      <c r="D203" t="s">
+        <v>189</v>
+      </c>
+      <c r="E203">
+        <v>2</v>
+      </c>
+      <c r="F203" t="s">
+        <v>191</v>
+      </c>
+      <c r="G203" t="s">
+        <v>192</v>
+      </c>
+      <c r="H203" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I203">
+        <v>107.27</v>
+      </c>
+      <c r="J203">
+        <v>106.65</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="A204" t="s">
+        <v>141</v>
+      </c>
+      <c r="B204" t="s">
+        <v>181</v>
+      </c>
+      <c r="C204" t="s">
+        <v>185</v>
+      </c>
+      <c r="D204" t="s">
+        <v>189</v>
+      </c>
+      <c r="E204">
+        <v>3</v>
+      </c>
+      <c r="F204" t="s">
+        <v>191</v>
+      </c>
+      <c r="G204" t="s">
+        <v>192</v>
+      </c>
+      <c r="H204" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I204">
+        <v>108.9</v>
+      </c>
+      <c r="J204">
+        <v>109.42</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="A205" t="s">
+        <v>120</v>
+      </c>
+      <c r="B205" t="s">
+        <v>181</v>
+      </c>
+      <c r="C205" t="s">
+        <v>185</v>
+      </c>
+      <c r="D205" t="s">
+        <v>189</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="F205" t="s">
+        <v>191</v>
+      </c>
+      <c r="G205" t="s">
+        <v>193</v>
+      </c>
+      <c r="H205" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I205">
+        <v>91.56</v>
+      </c>
+      <c r="J205">
+        <v>91.56999999999999</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="A206" t="s">
+        <v>152</v>
+      </c>
+      <c r="B206" t="s">
+        <v>181</v>
+      </c>
+      <c r="C206" t="s">
+        <v>185</v>
+      </c>
+      <c r="D206" t="s">
+        <v>189</v>
+      </c>
+      <c r="E206">
+        <v>2</v>
+      </c>
+      <c r="F206" t="s">
+        <v>191</v>
+      </c>
+      <c r="G206" t="s">
+        <v>193</v>
+      </c>
+      <c r="H206" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I206">
+        <v>107.27</v>
+      </c>
+      <c r="J206">
+        <v>106.65</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207" t="s">
+        <v>141</v>
+      </c>
+      <c r="B207" t="s">
+        <v>181</v>
+      </c>
+      <c r="C207" t="s">
+        <v>185</v>
+      </c>
+      <c r="D207" t="s">
+        <v>189</v>
+      </c>
+      <c r="E207">
+        <v>3</v>
+      </c>
+      <c r="F207" t="s">
+        <v>191</v>
+      </c>
+      <c r="G207" t="s">
+        <v>193</v>
+      </c>
+      <c r="H207" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I207">
+        <v>109.13</v>
+      </c>
+      <c r="J207">
+        <v>109.42</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208" t="s">
+        <v>143</v>
+      </c>
+      <c r="B208" t="s">
+        <v>155</v>
+      </c>
+      <c r="C208" t="s">
+        <v>185</v>
+      </c>
+      <c r="D208" t="s">
+        <v>189</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208" t="s">
+        <v>191</v>
+      </c>
+      <c r="G208" t="s">
+        <v>193</v>
+      </c>
+      <c r="H208" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I208">
+        <v>96.33</v>
+      </c>
+      <c r="J208">
+        <v>96.43000000000001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209" t="s">
+        <v>109</v>
+      </c>
+      <c r="B209" t="s">
+        <v>155</v>
+      </c>
+      <c r="C209" t="s">
+        <v>185</v>
+      </c>
+      <c r="D209" t="s">
+        <v>189</v>
+      </c>
+      <c r="E209">
+        <v>2</v>
+      </c>
+      <c r="F209" t="s">
+        <v>191</v>
+      </c>
+      <c r="G209" t="s">
+        <v>193</v>
+      </c>
+      <c r="H209" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I209">
+        <v>113.96</v>
+      </c>
+      <c r="J209">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210" t="s">
+        <v>113</v>
+      </c>
+      <c r="B210" t="s">
+        <v>155</v>
+      </c>
+      <c r="C210" t="s">
+        <v>185</v>
+      </c>
+      <c r="D210" t="s">
+        <v>189</v>
+      </c>
+      <c r="E210">
+        <v>3</v>
+      </c>
+      <c r="F210" t="s">
+        <v>191</v>
+      </c>
+      <c r="G210" t="s">
+        <v>193</v>
+      </c>
+      <c r="H210" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I210">
+        <v>112.63</v>
+      </c>
+      <c r="J210">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211" t="s">
+        <v>118</v>
+      </c>
+      <c r="B211" t="s">
+        <v>162</v>
+      </c>
+      <c r="C211" t="s">
+        <v>185</v>
+      </c>
+      <c r="D211" t="s">
+        <v>189</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+      <c r="F211" t="s">
+        <v>191</v>
+      </c>
+      <c r="G211" t="s">
+        <v>193</v>
+      </c>
+      <c r="H211" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I211">
+        <v>96.62</v>
+      </c>
+      <c r="J211">
+        <v>96.63</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" t="s">
+        <v>121</v>
+      </c>
+      <c r="B212" t="s">
+        <v>162</v>
+      </c>
+      <c r="C212" t="s">
+        <v>185</v>
+      </c>
+      <c r="D212" t="s">
+        <v>189</v>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
+      <c r="F212" t="s">
+        <v>191</v>
+      </c>
+      <c r="G212" t="s">
+        <v>193</v>
+      </c>
+      <c r="H212" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I212">
+        <v>106.58</v>
+      </c>
+      <c r="J212">
+        <v>106.58</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" t="s">
+        <v>114</v>
+      </c>
+      <c r="B213" t="s">
+        <v>162</v>
+      </c>
+      <c r="C213" t="s">
+        <v>185</v>
+      </c>
+      <c r="D213" t="s">
+        <v>189</v>
+      </c>
+      <c r="E213">
+        <v>3</v>
+      </c>
+      <c r="F213" t="s">
+        <v>191</v>
+      </c>
+      <c r="G213" t="s">
+        <v>193</v>
+      </c>
+      <c r="H213" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I213">
+        <v>111.33</v>
+      </c>
+      <c r="J213">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" t="s">
+        <v>148</v>
+      </c>
+      <c r="B214" t="s">
+        <v>164</v>
+      </c>
+      <c r="C214" t="s">
+        <v>185</v>
+      </c>
+      <c r="D214" t="s">
+        <v>189</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+      <c r="F214" t="s">
+        <v>191</v>
+      </c>
+      <c r="G214" t="s">
+        <v>193</v>
+      </c>
+      <c r="H214" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I214">
+        <v>98.31</v>
+      </c>
+      <c r="J214">
+        <v>98.36</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215" t="s">
+        <v>138</v>
+      </c>
+      <c r="B215" t="s">
+        <v>164</v>
+      </c>
+      <c r="C215" t="s">
+        <v>185</v>
+      </c>
+      <c r="D215" t="s">
+        <v>189</v>
+      </c>
+      <c r="E215">
+        <v>2</v>
+      </c>
+      <c r="F215" t="s">
+        <v>191</v>
+      </c>
+      <c r="G215" t="s">
+        <v>193</v>
+      </c>
+      <c r="H215" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I215">
+        <v>110.16</v>
+      </c>
+      <c r="J215">
+        <v>110.08</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216" t="s">
+        <v>137</v>
+      </c>
+      <c r="B216" t="s">
+        <v>164</v>
+      </c>
+      <c r="C216" t="s">
+        <v>185</v>
+      </c>
+      <c r="D216" t="s">
+        <v>189</v>
+      </c>
+      <c r="E216">
+        <v>3</v>
+      </c>
+      <c r="F216" t="s">
+        <v>191</v>
+      </c>
+      <c r="G216" t="s">
+        <v>193</v>
+      </c>
+      <c r="H216" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I216">
+        <v>112.46</v>
+      </c>
+      <c r="J216">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" t="s">
+        <v>131</v>
+      </c>
+      <c r="B217" t="s">
+        <v>161</v>
+      </c>
+      <c r="C217" t="s">
+        <v>185</v>
+      </c>
+      <c r="D217" t="s">
+        <v>189</v>
+      </c>
+      <c r="E217">
+        <v>1</v>
+      </c>
+      <c r="F217" t="s">
+        <v>191</v>
+      </c>
+      <c r="G217" t="s">
+        <v>193</v>
+      </c>
+      <c r="H217" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I217">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="J217">
+        <v>92.05</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218" t="s">
+        <v>127</v>
+      </c>
+      <c r="B218" t="s">
+        <v>161</v>
+      </c>
+      <c r="C218" t="s">
+        <v>185</v>
+      </c>
+      <c r="D218" t="s">
+        <v>189</v>
+      </c>
+      <c r="E218">
+        <v>2</v>
+      </c>
+      <c r="F218" t="s">
+        <v>191</v>
+      </c>
+      <c r="G218" t="s">
+        <v>193</v>
+      </c>
+      <c r="H218" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I218">
+        <v>108.02</v>
+      </c>
+      <c r="J218">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219" t="s">
+        <v>117</v>
+      </c>
+      <c r="B219" t="s">
+        <v>161</v>
+      </c>
+      <c r="C219" t="s">
+        <v>185</v>
+      </c>
+      <c r="D219" t="s">
+        <v>189</v>
+      </c>
+      <c r="E219">
+        <v>3</v>
+      </c>
+      <c r="F219" t="s">
+        <v>191</v>
+      </c>
+      <c r="G219" t="s">
+        <v>193</v>
+      </c>
+      <c r="H219" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I219">
+        <v>112.81</v>
+      </c>
+      <c r="J219">
+        <v>112.76</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220" t="s">
+        <v>145</v>
+      </c>
+      <c r="B220" t="s">
+        <v>180</v>
+      </c>
+      <c r="C220" t="s">
+        <v>185</v>
+      </c>
+      <c r="D220" t="s">
+        <v>189</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+      <c r="F220" t="s">
+        <v>191</v>
+      </c>
+      <c r="G220" t="s">
+        <v>193</v>
+      </c>
+      <c r="H220" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I220">
+        <v>98.36</v>
+      </c>
+      <c r="J220">
+        <v>98.36</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221" t="s">
+        <v>146</v>
+      </c>
+      <c r="B221" t="s">
+        <v>180</v>
+      </c>
+      <c r="C221" t="s">
+        <v>185</v>
+      </c>
+      <c r="D221" t="s">
+        <v>189</v>
+      </c>
+      <c r="E221">
+        <v>2</v>
+      </c>
+      <c r="F221" t="s">
+        <v>191</v>
+      </c>
+      <c r="G221" t="s">
+        <v>193</v>
+      </c>
+      <c r="H221" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I221">
+        <v>114.03</v>
+      </c>
+      <c r="J221">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" t="s">
+        <v>147</v>
+      </c>
+      <c r="B222" t="s">
+        <v>180</v>
+      </c>
+      <c r="C222" t="s">
+        <v>185</v>
+      </c>
+      <c r="D222" t="s">
+        <v>189</v>
+      </c>
+      <c r="E222">
+        <v>3</v>
+      </c>
+      <c r="F222" t="s">
+        <v>191</v>
+      </c>
+      <c r="G222" t="s">
+        <v>193</v>
+      </c>
+      <c r="H222" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I222">
+        <v>114.14</v>
+      </c>
+      <c r="J222">
+        <v>114.23</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" t="s">
+        <v>149</v>
+      </c>
+      <c r="B223" t="s">
+        <v>153</v>
+      </c>
+      <c r="C223" t="s">
+        <v>185</v>
+      </c>
+      <c r="D223" t="s">
+        <v>189</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+      <c r="F223" t="s">
+        <v>191</v>
+      </c>
+      <c r="G223" t="s">
+        <v>193</v>
+      </c>
+      <c r="H223" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I223">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="J223">
+        <v>95.84999999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" t="s">
+        <v>115</v>
+      </c>
+      <c r="B224" t="s">
+        <v>153</v>
+      </c>
+      <c r="C224" t="s">
+        <v>185</v>
+      </c>
+      <c r="D224" t="s">
+        <v>189</v>
+      </c>
+      <c r="E224">
+        <v>2</v>
+      </c>
+      <c r="F224" t="s">
+        <v>191</v>
+      </c>
+      <c r="G224" t="s">
+        <v>193</v>
+      </c>
+      <c r="H224" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I224">
+        <v>106.67</v>
+      </c>
+      <c r="J224">
+        <v>106.65</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225" t="s">
+        <v>106</v>
+      </c>
+      <c r="B225" t="s">
+        <v>153</v>
+      </c>
+      <c r="C225" t="s">
+        <v>185</v>
+      </c>
+      <c r="D225" t="s">
+        <v>189</v>
+      </c>
+      <c r="E225">
+        <v>3</v>
+      </c>
+      <c r="F225" t="s">
+        <v>191</v>
+      </c>
+      <c r="G225" t="s">
+        <v>193</v>
+      </c>
+      <c r="H225" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I225">
+        <v>107.6</v>
+      </c>
+      <c r="J225">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226" t="s">
+        <v>150</v>
+      </c>
+      <c r="B226" t="s">
+        <v>170</v>
+      </c>
+      <c r="C226" t="s">
+        <v>185</v>
+      </c>
+      <c r="D226" t="s">
+        <v>189</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+      <c r="F226" t="s">
+        <v>191</v>
+      </c>
+      <c r="G226" t="s">
+        <v>193</v>
+      </c>
+      <c r="H226" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I226">
+        <v>96.37</v>
+      </c>
+      <c r="J226">
+        <v>96.43000000000001</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="A227" t="s">
+        <v>151</v>
+      </c>
+      <c r="B227" t="s">
+        <v>170</v>
+      </c>
+      <c r="C227" t="s">
+        <v>185</v>
+      </c>
+      <c r="D227" t="s">
+        <v>189</v>
+      </c>
+      <c r="E227">
+        <v>2</v>
+      </c>
+      <c r="F227" t="s">
+        <v>191</v>
+      </c>
+      <c r="G227" t="s">
+        <v>193</v>
+      </c>
+      <c r="H227" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I227">
+        <v>109.72</v>
+      </c>
+      <c r="J227">
+        <v>109.69</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228" t="s">
+        <v>135</v>
+      </c>
+      <c r="B228" t="s">
+        <v>170</v>
+      </c>
+      <c r="C228" t="s">
+        <v>185</v>
+      </c>
+      <c r="D228" t="s">
+        <v>189</v>
+      </c>
+      <c r="E228">
+        <v>3</v>
+      </c>
+      <c r="F228" t="s">
+        <v>191</v>
+      </c>
+      <c r="G228" t="s">
+        <v>193</v>
+      </c>
+      <c r="H228" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I228">
+        <v>109.99</v>
+      </c>
+      <c r="J228">
+        <v>109.93</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229" t="s">
+        <v>120</v>
+      </c>
+      <c r="B229" t="s">
+        <v>181</v>
+      </c>
+      <c r="C229" t="s">
+        <v>185</v>
+      </c>
+      <c r="D229" t="s">
+        <v>189</v>
+      </c>
+      <c r="E229">
+        <v>1</v>
+      </c>
+      <c r="F229" t="s">
+        <v>191</v>
+      </c>
+      <c r="G229" t="s">
+        <v>194</v>
+      </c>
+      <c r="H229" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I229">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="J229">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230" t="s">
+        <v>152</v>
+      </c>
+      <c r="B230" t="s">
+        <v>181</v>
+      </c>
+      <c r="C230" t="s">
+        <v>185</v>
+      </c>
+      <c r="D230" t="s">
+        <v>189</v>
+      </c>
+      <c r="E230">
+        <v>2</v>
+      </c>
+      <c r="F230" t="s">
+        <v>191</v>
+      </c>
+      <c r="G230" t="s">
+        <v>194</v>
+      </c>
+      <c r="H230" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I230">
+        <v>108.54</v>
+      </c>
+      <c r="J230">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231" t="s">
+        <v>141</v>
+      </c>
+      <c r="B231" t="s">
+        <v>181</v>
+      </c>
+      <c r="C231" t="s">
+        <v>185</v>
+      </c>
+      <c r="D231" t="s">
+        <v>189</v>
+      </c>
+      <c r="E231">
+        <v>3</v>
+      </c>
+      <c r="F231" t="s">
+        <v>191</v>
+      </c>
+      <c r="G231" t="s">
+        <v>194</v>
+      </c>
+      <c r="H231" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I231">
+        <v>110.69</v>
+      </c>
+      <c r="J231">
+        <v>110.84</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="A232" t="s">
+        <v>118</v>
+      </c>
+      <c r="B232" t="s">
+        <v>162</v>
+      </c>
+      <c r="C232" t="s">
+        <v>185</v>
+      </c>
+      <c r="D232" t="s">
+        <v>189</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
+      <c r="F232" t="s">
+        <v>191</v>
+      </c>
+      <c r="G232" t="s">
+        <v>195</v>
+      </c>
+      <c r="H232" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I232">
+        <v>96.84</v>
+      </c>
+      <c r="J232">
+        <v>96.88</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="A233" t="s">
+        <v>121</v>
+      </c>
+      <c r="B233" t="s">
+        <v>162</v>
+      </c>
+      <c r="C233" t="s">
+        <v>185</v>
+      </c>
+      <c r="D233" t="s">
+        <v>189</v>
+      </c>
+      <c r="E233">
+        <v>2</v>
+      </c>
+      <c r="F233" t="s">
+        <v>191</v>
+      </c>
+      <c r="G233" t="s">
+        <v>195</v>
+      </c>
+      <c r="H233" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I233">
+        <v>106.9</v>
+      </c>
+      <c r="J233">
+        <v>106.65</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234" t="s">
+        <v>114</v>
+      </c>
+      <c r="B234" t="s">
+        <v>162</v>
+      </c>
+      <c r="C234" t="s">
+        <v>185</v>
+      </c>
+      <c r="D234" t="s">
+        <v>189</v>
+      </c>
+      <c r="E234">
+        <v>3</v>
+      </c>
+      <c r="F234" t="s">
+        <v>191</v>
+      </c>
+      <c r="G234" t="s">
+        <v>195</v>
+      </c>
+      <c r="H234" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I234">
+        <v>111.41</v>
+      </c>
+      <c r="J234">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235" t="s">
+        <v>143</v>
+      </c>
+      <c r="B235" t="s">
+        <v>155</v>
+      </c>
+      <c r="C235" t="s">
+        <v>185</v>
+      </c>
+      <c r="D235" t="s">
+        <v>189</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="F235" t="s">
+        <v>191</v>
+      </c>
+      <c r="G235" t="s">
+        <v>195</v>
+      </c>
+      <c r="H235" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I235">
+        <v>96.08</v>
+      </c>
+      <c r="J235">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236" t="s">
+        <v>109</v>
+      </c>
+      <c r="B236" t="s">
+        <v>155</v>
+      </c>
+      <c r="C236" t="s">
+        <v>185</v>
+      </c>
+      <c r="D236" t="s">
+        <v>189</v>
+      </c>
+      <c r="E236">
+        <v>2</v>
+      </c>
+      <c r="F236" t="s">
+        <v>191</v>
+      </c>
+      <c r="G236" t="s">
+        <v>195</v>
+      </c>
+      <c r="H236" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I236">
+        <v>114.66</v>
+      </c>
+      <c r="J236">
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="A237" t="s">
+        <v>113</v>
+      </c>
+      <c r="B237" t="s">
+        <v>155</v>
+      </c>
+      <c r="C237" t="s">
+        <v>185</v>
+      </c>
+      <c r="D237" t="s">
+        <v>189</v>
+      </c>
+      <c r="E237">
+        <v>3</v>
+      </c>
+      <c r="F237" t="s">
+        <v>191</v>
+      </c>
+      <c r="G237" t="s">
+        <v>195</v>
+      </c>
+      <c r="H237" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I237">
+        <v>113.99</v>
+      </c>
+      <c r="J237">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="A238" t="s">
+        <v>148</v>
+      </c>
+      <c r="B238" t="s">
+        <v>164</v>
+      </c>
+      <c r="C238" t="s">
+        <v>185</v>
+      </c>
+      <c r="D238" t="s">
+        <v>189</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+      <c r="F238" t="s">
+        <v>191</v>
+      </c>
+      <c r="G238" t="s">
+        <v>194</v>
+      </c>
+      <c r="H238" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I238">
+        <v>98.3</v>
+      </c>
+      <c r="J238">
+        <v>98.36</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="A239" t="s">
+        <v>138</v>
+      </c>
+      <c r="B239" t="s">
+        <v>164</v>
+      </c>
+      <c r="C239" t="s">
+        <v>185</v>
+      </c>
+      <c r="D239" t="s">
+        <v>189</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+      <c r="F239" t="s">
+        <v>191</v>
+      </c>
+      <c r="G239" t="s">
+        <v>194</v>
+      </c>
+      <c r="H239" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I239">
+        <v>109.53</v>
+      </c>
+      <c r="J239">
+        <v>109.5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="A240" t="s">
+        <v>137</v>
+      </c>
+      <c r="B240" t="s">
+        <v>164</v>
+      </c>
+      <c r="C240" t="s">
+        <v>185</v>
+      </c>
+      <c r="D240" t="s">
+        <v>189</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
+      <c r="F240" t="s">
+        <v>191</v>
+      </c>
+      <c r="G240" t="s">
+        <v>194</v>
+      </c>
+      <c r="H240" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I240">
+        <v>112.41</v>
+      </c>
+      <c r="J240">
+        <v>112.5</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
+++ b/pages/Gear_Calculator/Gear_Calculator_Master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="200">
   <si>
     <t>Name</t>
   </si>
@@ -475,6 +475,12 @@
     <t>BAO Shanju</t>
   </si>
   <si>
+    <t>PROPSTER Alessa-Catriona</t>
+  </si>
+  <si>
+    <t>MARCHANT Katy</t>
+  </si>
+  <si>
     <t>NZL</t>
   </si>
   <si>
@@ -602,6 +608,12 @@
   </si>
   <si>
     <t>A Final</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
   </si>
 </sst>
 </file>
@@ -963,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J282"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1003,22 +1015,22 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H2" s="2">
         <v>45141</v>
@@ -1035,22 +1047,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H3" s="2">
         <v>45141</v>
@@ -1067,22 +1079,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H4" s="2">
         <v>45141</v>
@@ -1099,22 +1111,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H5" s="2">
         <v>45141</v>
@@ -1131,22 +1143,22 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2">
         <v>45141</v>
@@ -1163,22 +1175,22 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H7" s="2">
         <v>45141</v>
@@ -1195,22 +1207,22 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H8" s="2">
         <v>45141</v>
@@ -1227,22 +1239,22 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H9" s="2">
         <v>45141</v>
@@ -1259,22 +1271,22 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H10" s="2">
         <v>45141</v>
@@ -1291,22 +1303,22 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H11" s="2">
         <v>45141</v>
@@ -1323,22 +1335,22 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H12" s="2">
         <v>45141</v>
@@ -1355,22 +1367,22 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2">
         <v>45141</v>
@@ -1387,22 +1399,22 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H14" s="2">
         <v>45141</v>
@@ -1419,22 +1431,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H15" s="2">
         <v>45141</v>
@@ -1451,22 +1463,22 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H16" s="2">
         <v>45141</v>
@@ -1483,22 +1495,22 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H17" s="2">
         <v>45141</v>
@@ -1515,22 +1527,22 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H18" s="2">
         <v>45141</v>
@@ -1547,22 +1559,22 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H19" s="2">
         <v>45141</v>
@@ -1579,22 +1591,22 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H20" s="2">
         <v>45141</v>
@@ -1611,22 +1623,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E21">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G21" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H21" s="2">
         <v>45141</v>
@@ -1643,22 +1655,22 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H22" s="2">
         <v>45142</v>
@@ -1675,22 +1687,22 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G23" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H23" s="2">
         <v>45142</v>
@@ -1707,22 +1719,22 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H24" s="2">
         <v>45142</v>
@@ -1739,22 +1751,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H25" s="2">
         <v>45142</v>
@@ -1771,22 +1783,22 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H26" s="2">
         <v>45143</v>
@@ -1803,22 +1815,22 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G27" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H27" s="2">
         <v>45143</v>
@@ -1835,22 +1847,22 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H28" s="2">
         <v>45143</v>
@@ -1867,22 +1879,22 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H29" s="2">
         <v>45143</v>
@@ -1899,22 +1911,22 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G30" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H30" s="2">
         <v>45143</v>
@@ -1931,22 +1943,22 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H31" s="2">
         <v>45143</v>
@@ -1963,22 +1975,22 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H32" s="2">
         <v>45143</v>
@@ -1995,22 +2007,22 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H33" s="2">
         <v>45143</v>
@@ -2027,22 +2039,22 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H34" s="2">
         <v>45142</v>
@@ -2059,22 +2071,22 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G35" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H35" s="2">
         <v>45142</v>
@@ -2091,22 +2103,22 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D36" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G36" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H36" s="2">
         <v>45142</v>
@@ -2123,22 +2135,22 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C37" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G37" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H37" s="2">
         <v>45142</v>
@@ -2155,22 +2167,22 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H38" s="2">
         <v>45143</v>
@@ -2187,22 +2199,22 @@
         <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E39" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G39" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H39" s="2">
         <v>45143</v>
@@ -2219,22 +2231,22 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E40" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G40" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H40" s="2">
         <v>45143</v>
@@ -2251,22 +2263,22 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D41" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E41" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F41" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G41" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H41" s="2">
         <v>45143</v>
@@ -2283,22 +2295,22 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D42" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E42" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F42" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H42" s="2">
         <v>45143</v>
@@ -2315,22 +2327,22 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F43" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G43" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H43" s="2">
         <v>45143</v>
@@ -2347,22 +2359,22 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E44" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F44" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G44" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H44" s="2">
         <v>45143</v>
@@ -2379,22 +2391,22 @@
         <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C45" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F45" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G45" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H45" s="2">
         <v>45143</v>
@@ -2411,22 +2423,22 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E46" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G46" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H46" s="2">
         <v>45143</v>
@@ -2443,22 +2455,22 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E47" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G47" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H47" s="2">
         <v>45143</v>
@@ -2475,22 +2487,22 @@
         <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D48" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E48" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G48" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H48" s="2">
         <v>45143</v>
@@ -2507,22 +2519,22 @@
         <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E49" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F49" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H49" s="2">
         <v>45143</v>
@@ -2539,22 +2551,22 @@
         <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H50" s="2">
         <v>45143</v>
@@ -2571,22 +2583,22 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E51" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F51" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G51" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H51" s="2">
         <v>45143</v>
@@ -2603,22 +2615,22 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D52" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F52" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H52" s="2">
         <v>45143</v>
@@ -2635,22 +2647,22 @@
         <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D53" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E53" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F53" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G53" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H53" s="2">
         <v>45143</v>
@@ -2667,22 +2679,22 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E54" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G54" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H54" s="2">
         <v>45143</v>
@@ -2699,22 +2711,22 @@
         <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D55" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H55" s="2">
         <v>45143</v>
@@ -2731,22 +2743,22 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E56" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H56" s="2">
         <v>45143</v>
@@ -2763,22 +2775,22 @@
         <v>52</v>
       </c>
       <c r="B57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D57" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G57" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H57" s="2">
         <v>45143</v>
@@ -2795,22 +2807,22 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D58" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F58" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H58" s="2">
         <v>45143</v>
@@ -2827,22 +2839,22 @@
         <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E59" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G59" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H59" s="2">
         <v>45143</v>
@@ -2859,22 +2871,22 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C60" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D60" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E60" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G60" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H60" s="2">
         <v>45143</v>
@@ -2891,22 +2903,22 @@
         <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E61" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F61" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H61" s="2">
         <v>45143</v>
@@ -2923,22 +2935,22 @@
         <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D62" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E62" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F62" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G62" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H62" s="2">
         <v>45143</v>
@@ -2955,22 +2967,22 @@
         <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E63" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F63" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G63" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H63" s="2">
         <v>45143</v>
@@ -2987,22 +2999,22 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H64" s="2">
         <v>45143</v>
@@ -3019,22 +3031,22 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H65" s="2">
         <v>45143</v>
@@ -3051,22 +3063,22 @@
         <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D66" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E66" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F66" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G66" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H66" s="2">
         <v>45143</v>
@@ -3083,22 +3095,22 @@
         <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C67" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D67" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F67" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G67" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H67" s="2">
         <v>45143</v>
@@ -3115,22 +3127,22 @@
         <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D68" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E68" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F68" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G68" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H68" s="2">
         <v>45143</v>
@@ -3147,22 +3159,22 @@
         <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D69" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E69" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F69" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H69" s="2">
         <v>45143</v>
@@ -3179,22 +3191,22 @@
         <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C70" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D70" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E70" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F70" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G70" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H70" s="2">
         <v>45143</v>
@@ -3211,22 +3223,22 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D71" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E71" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F71" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G71" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H71" s="2">
         <v>45147</v>
@@ -3243,22 +3255,22 @@
         <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D72" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F72" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G72" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H72" s="2">
         <v>45147</v>
@@ -3275,22 +3287,22 @@
         <v>49</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D73" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E73" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G73" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H73" s="2">
         <v>45147</v>
@@ -3307,22 +3319,22 @@
         <v>34</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D74" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E74" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F74" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G74" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H74" s="2">
         <v>45147</v>
@@ -3339,22 +3351,22 @@
         <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D75" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E75" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F75" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G75" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H75" s="2">
         <v>45147</v>
@@ -3371,22 +3383,22 @@
         <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C76" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D76" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E76" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F76" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H76" s="2">
         <v>45147</v>
@@ -3403,22 +3415,22 @@
         <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C77" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D77" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E77" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F77" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G77" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H77" s="2">
         <v>45147</v>
@@ -3435,22 +3447,22 @@
         <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E78" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F78" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G78" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H78" s="2">
         <v>45147</v>
@@ -3467,22 +3479,22 @@
         <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E79" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F79" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G79" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H79" s="2">
         <v>45147</v>
@@ -3499,22 +3511,22 @@
         <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C80" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D80" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E80" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F80" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G80" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H80" s="2">
         <v>45147</v>
@@ -3531,22 +3543,22 @@
         <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D81" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E81" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F81" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G81" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H81" s="2">
         <v>45147</v>
@@ -3563,22 +3575,22 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D82" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E82" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F82" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G82" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H82" s="2">
         <v>45147</v>
@@ -3595,22 +3607,22 @@
         <v>35</v>
       </c>
       <c r="B83" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D83" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E83" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F83" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G83" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H83" s="2">
         <v>45146</v>
@@ -3627,22 +3639,22 @@
         <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D84" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E84" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G84" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H84" s="2">
         <v>45146</v>
@@ -3659,22 +3671,22 @@
         <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D85" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E85" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F85" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G85" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H85" s="2">
         <v>45146</v>
@@ -3691,22 +3703,22 @@
         <v>69</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C86" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D86" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E86" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F86" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G86" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H86" s="2">
         <v>45146</v>
@@ -3723,22 +3735,22 @@
         <v>49</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C87" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D87" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E87" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F87" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H87" s="2">
         <v>45146</v>
@@ -3755,22 +3767,22 @@
         <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C88" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E88" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F88" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G88" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H88" s="2">
         <v>45146</v>
@@ -3787,22 +3799,22 @@
         <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E89" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F89" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G89" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H89" s="2">
         <v>45146</v>
@@ -3819,22 +3831,22 @@
         <v>53</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C90" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E90" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F90" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G90" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H90" s="2">
         <v>45146</v>
@@ -3851,22 +3863,22 @@
         <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C91" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F91" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G91" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H91" s="2">
         <v>45146</v>
@@ -3883,22 +3895,22 @@
         <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C92" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E92" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G92" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H92" s="2">
         <v>45146</v>
@@ -3915,22 +3927,22 @@
         <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C93" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D93" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E93" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G93" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H93" s="2">
         <v>45146</v>
@@ -3947,22 +3959,22 @@
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C94" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D94" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E94" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F94" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G94" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H94" s="2">
         <v>45146</v>
@@ -3979,22 +3991,22 @@
         <v>71</v>
       </c>
       <c r="B95" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C95" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D95" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F95" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G95" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H95" s="2">
         <v>45146</v>
@@ -4011,22 +4023,22 @@
         <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C96" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D96" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E96" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F96" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G96" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H96" s="2">
         <v>45146</v>
@@ -4043,22 +4055,22 @@
         <v>72</v>
       </c>
       <c r="B97" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C97" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D97" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E97" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G97" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H97" s="2">
         <v>45146</v>
@@ -4075,22 +4087,22 @@
         <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D98" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E98" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F98" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G98" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H98" s="2">
         <v>45146</v>
@@ -4107,22 +4119,22 @@
         <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C99" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D99" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E99" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F99" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G99" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H99" s="2">
         <v>45146</v>
@@ -4139,22 +4151,22 @@
         <v>73</v>
       </c>
       <c r="B100" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C100" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D100" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E100" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F100" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G100" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H100" s="2">
         <v>45146</v>
@@ -4171,22 +4183,22 @@
         <v>74</v>
       </c>
       <c r="B101" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C101" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D101" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E101" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F101" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G101" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H101" s="2">
         <v>45146</v>
@@ -4203,22 +4215,22 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C102" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D102" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E102" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F102" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G102" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H102" s="2">
         <v>45146</v>
@@ -4235,22 +4247,22 @@
         <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C103" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D103" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E103" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F103" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G103" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H103" s="2">
         <v>45146</v>
@@ -4267,22 +4279,22 @@
         <v>55</v>
       </c>
       <c r="B104" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C104" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D104" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E104" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F104" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G104" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H104" s="2">
         <v>45146</v>
@@ -4299,22 +4311,22 @@
         <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C105" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D105" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E105" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F105" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G105" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H105" s="2">
         <v>45146</v>
@@ -4331,22 +4343,22 @@
         <v>75</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C106" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D106" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E106" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F106" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G106" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H106" s="2">
         <v>45146</v>
@@ -4363,22 +4375,22 @@
         <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C107" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D107" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E107" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F107" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G107" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H107" s="2">
         <v>45146</v>
@@ -4395,22 +4407,22 @@
         <v>62</v>
       </c>
       <c r="B108" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C108" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D108" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E108" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F108" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G108" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H108" s="2">
         <v>45146</v>
@@ -4427,22 +4439,22 @@
         <v>76</v>
       </c>
       <c r="B109" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D109" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E109" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F109" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G109" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H109" s="2">
         <v>45146</v>
@@ -4459,22 +4471,22 @@
         <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C110" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D110" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E110" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F110" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G110" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H110" s="2">
         <v>45146</v>
@@ -4491,22 +4503,22 @@
         <v>78</v>
       </c>
       <c r="B111" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C111" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G111" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H111" s="2">
         <v>45142</v>
@@ -4523,22 +4535,22 @@
         <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C112" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D112" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E112">
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G112" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H112" s="2">
         <v>45142</v>
@@ -4555,22 +4567,22 @@
         <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C113" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D113" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G113" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H113" s="2">
         <v>45142</v>
@@ -4587,22 +4599,22 @@
         <v>81</v>
       </c>
       <c r="B114" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C114" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D114" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E114">
         <v>4</v>
       </c>
       <c r="F114" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G114" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H114" s="2">
         <v>45142</v>
@@ -4619,22 +4631,22 @@
         <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C115" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D115" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G115" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H115" s="2">
         <v>45142</v>
@@ -4651,22 +4663,22 @@
         <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C116" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D116" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E116">
         <v>2</v>
       </c>
       <c r="F116" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G116" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H116" s="2">
         <v>45142</v>
@@ -4683,22 +4695,22 @@
         <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C117" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D117" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G117" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H117" s="2">
         <v>45142</v>
@@ -4715,22 +4727,22 @@
         <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C118" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D118" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E118">
         <v>4</v>
       </c>
       <c r="F118" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G118" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H118" s="2">
         <v>45142</v>
@@ -4747,22 +4759,22 @@
         <v>86</v>
       </c>
       <c r="B119" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C119" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D119" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E119">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G119" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H119" s="2">
         <v>45142</v>
@@ -4779,22 +4791,22 @@
         <v>87</v>
       </c>
       <c r="B120" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D120" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E120">
         <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G120" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H120" s="2">
         <v>45142</v>
@@ -4811,22 +4823,22 @@
         <v>88</v>
       </c>
       <c r="B121" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C121" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D121" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G121" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H121" s="2">
         <v>45142</v>
@@ -4843,22 +4855,22 @@
         <v>89</v>
       </c>
       <c r="B122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C122" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D122" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E122">
         <v>4</v>
       </c>
       <c r="F122" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G122" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H122" s="2">
         <v>45142</v>
@@ -4875,22 +4887,22 @@
         <v>90</v>
       </c>
       <c r="B123" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C123" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D123" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E123">
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G123" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H123" s="2">
         <v>45142</v>
@@ -4907,22 +4919,22 @@
         <v>91</v>
       </c>
       <c r="B124" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C124" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D124" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E124">
         <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G124" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H124" s="2">
         <v>45142</v>
@@ -4939,22 +4951,22 @@
         <v>92</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C125" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D125" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E125">
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G125" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H125" s="2">
         <v>45142</v>
@@ -4971,22 +4983,22 @@
         <v>93</v>
       </c>
       <c r="B126" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C126" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D126" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
       <c r="F126" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G126" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H126" s="2">
         <v>45142</v>
@@ -5003,22 +5015,22 @@
         <v>94</v>
       </c>
       <c r="B127" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D127" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E127">
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G127" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H127" s="2">
         <v>45142</v>
@@ -5035,22 +5047,22 @@
         <v>95</v>
       </c>
       <c r="B128" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C128" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D128" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E128">
         <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G128" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H128" s="2">
         <v>45142</v>
@@ -5067,22 +5079,22 @@
         <v>96</v>
       </c>
       <c r="B129" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E129">
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G129" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H129" s="2">
         <v>45142</v>
@@ -5099,22 +5111,22 @@
         <v>97</v>
       </c>
       <c r="B130" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C130" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D130" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E130">
         <v>4</v>
       </c>
       <c r="F130" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G130" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H130" s="2">
         <v>45142</v>
@@ -5131,22 +5143,22 @@
         <v>98</v>
       </c>
       <c r="B131" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C131" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E131">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G131" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H131" s="2">
         <v>45142</v>
@@ -5163,22 +5175,22 @@
         <v>99</v>
       </c>
       <c r="B132" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D132" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E132">
         <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G132" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H132" s="2">
         <v>45142</v>
@@ -5195,22 +5207,22 @@
         <v>100</v>
       </c>
       <c r="B133" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C133" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D133" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E133">
         <v>3</v>
       </c>
       <c r="F133" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G133" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H133" s="2">
         <v>45142</v>
@@ -5227,22 +5239,22 @@
         <v>101</v>
       </c>
       <c r="B134" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C134" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D134" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E134">
         <v>4</v>
       </c>
       <c r="F134" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G134" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H134" s="2">
         <v>45142</v>
@@ -5259,22 +5271,22 @@
         <v>102</v>
       </c>
       <c r="B135" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C135" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D135" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G135" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H135" s="2">
         <v>45142</v>
@@ -5291,22 +5303,22 @@
         <v>103</v>
       </c>
       <c r="B136" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D136" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E136">
         <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G136" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H136" s="2">
         <v>45142</v>
@@ -5323,22 +5335,22 @@
         <v>104</v>
       </c>
       <c r="B137" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C137" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E137">
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G137" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H137" s="2">
         <v>45142</v>
@@ -5355,22 +5367,22 @@
         <v>105</v>
       </c>
       <c r="B138" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C138" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E138">
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G138" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H138" s="2">
         <v>45142</v>
@@ -5387,22 +5399,22 @@
         <v>106</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C139" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D139" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E139" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F139" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G139" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H139" s="2">
         <v>45145</v>
@@ -5419,22 +5431,22 @@
         <v>107</v>
       </c>
       <c r="B140" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C140" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D140" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E140" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F140" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G140" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H140" s="2">
         <v>45145</v>
@@ -5451,22 +5463,22 @@
         <v>108</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C141" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D141" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E141" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F141" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G141" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H141" s="2">
         <v>45145</v>
@@ -5483,22 +5495,22 @@
         <v>109</v>
       </c>
       <c r="B142" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C142" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D142" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E142" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F142" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G142" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H142" s="2">
         <v>45145</v>
@@ -5515,22 +5527,22 @@
         <v>110</v>
       </c>
       <c r="B143" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C143" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D143" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E143" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F143" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G143" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H143" s="2">
         <v>45145</v>
@@ -5547,22 +5559,22 @@
         <v>111</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C144" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D144" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E144" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F144" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G144" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H144" s="2">
         <v>45145</v>
@@ -5579,22 +5591,22 @@
         <v>112</v>
       </c>
       <c r="B145" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C145" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D145" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E145" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F145" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G145" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H145" s="2">
         <v>45145</v>
@@ -5611,22 +5623,22 @@
         <v>113</v>
       </c>
       <c r="B146" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C146" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D146" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E146" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F146" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G146" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H146" s="2">
         <v>45145</v>
@@ -5643,22 +5655,22 @@
         <v>114</v>
       </c>
       <c r="B147" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C147" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D147" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E147" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F147" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G147" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H147" s="2">
         <v>45145</v>
@@ -5675,22 +5687,22 @@
         <v>115</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C148" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D148" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E148" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F148" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G148" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H148" s="2">
         <v>45145</v>
@@ -5707,22 +5719,22 @@
         <v>116</v>
       </c>
       <c r="B149" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C149" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D149" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E149" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F149" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G149" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H149" s="2">
         <v>45145</v>
@@ -5739,22 +5751,22 @@
         <v>117</v>
       </c>
       <c r="B150" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D150" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E150" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F150" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G150" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H150" s="2">
         <v>45145</v>
@@ -5771,22 +5783,22 @@
         <v>118</v>
       </c>
       <c r="B151" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C151" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D151" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E151" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F151" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G151" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H151" s="2">
         <v>45145</v>
@@ -5803,22 +5815,22 @@
         <v>119</v>
       </c>
       <c r="B152" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D152" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E152" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F152" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G152" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H152" s="2">
         <v>45145</v>
@@ -5835,22 +5847,22 @@
         <v>120</v>
       </c>
       <c r="B153" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C153" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D153" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E153" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F153" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G153" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H153" s="2">
         <v>45145</v>
@@ -5867,22 +5879,22 @@
         <v>121</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C154" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E154" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F154" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G154" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H154" s="2">
         <v>45145</v>
@@ -5899,22 +5911,22 @@
         <v>122</v>
       </c>
       <c r="B155" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C155" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D155" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E155" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F155" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G155" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H155" s="2">
         <v>45145</v>
@@ -5931,22 +5943,22 @@
         <v>123</v>
       </c>
       <c r="B156" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C156" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D156" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E156" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F156" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G156" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H156" s="2">
         <v>45145</v>
@@ -5963,22 +5975,22 @@
         <v>124</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C157" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D157" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E157" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F157" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G157" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H157" s="2">
         <v>45145</v>
@@ -5995,22 +6007,22 @@
         <v>125</v>
       </c>
       <c r="B158" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C158" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D158" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E158" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F158" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G158" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H158" s="2">
         <v>45145</v>
@@ -6027,22 +6039,22 @@
         <v>126</v>
       </c>
       <c r="B159" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C159" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D159" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E159" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F159" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G159" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H159" s="2">
         <v>45145</v>
@@ -6059,22 +6071,22 @@
         <v>127</v>
       </c>
       <c r="B160" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C160" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D160" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E160" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F160" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G160" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H160" s="2">
         <v>45145</v>
@@ -6091,22 +6103,22 @@
         <v>128</v>
       </c>
       <c r="B161" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D161" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E161" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F161" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G161" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H161" s="2">
         <v>45145</v>
@@ -6123,22 +6135,22 @@
         <v>129</v>
       </c>
       <c r="B162" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C162" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D162" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E162" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F162" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G162" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H162" s="2">
         <v>45145</v>
@@ -6155,22 +6167,22 @@
         <v>130</v>
       </c>
       <c r="B163" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C163" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D163" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E163" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F163" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G163" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H163" s="2">
         <v>45145</v>
@@ -6187,22 +6199,22 @@
         <v>131</v>
       </c>
       <c r="B164" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C164" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E164" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F164" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G164" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H164" s="2">
         <v>45145</v>
@@ -6219,22 +6231,22 @@
         <v>132</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C165" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D165" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E165" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F165" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G165" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H165" s="2">
         <v>45145</v>
@@ -6251,22 +6263,22 @@
         <v>133</v>
       </c>
       <c r="B166" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C166" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D166" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E166" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F166" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G166" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H166" s="2">
         <v>45145</v>
@@ -6283,22 +6295,22 @@
         <v>134</v>
       </c>
       <c r="B167" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D167" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E167" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F167" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G167" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H167" s="2">
         <v>45145</v>
@@ -6315,22 +6327,22 @@
         <v>135</v>
       </c>
       <c r="B168" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D168" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E168" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F168" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G168" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H168" s="2">
         <v>45145</v>
@@ -6347,22 +6359,22 @@
         <v>136</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C169" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D169" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E169" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F169" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G169" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H169" s="2">
         <v>45145</v>
@@ -6379,22 +6391,22 @@
         <v>137</v>
       </c>
       <c r="B170" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C170" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D170" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E170" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F170" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G170" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H170" s="2">
         <v>45145</v>
@@ -6411,22 +6423,22 @@
         <v>138</v>
       </c>
       <c r="B171" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C171" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D171" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E171" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F171" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G171" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H171" s="2">
         <v>45145</v>
@@ -6443,22 +6455,22 @@
         <v>139</v>
       </c>
       <c r="B172" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C172" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D172" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E172" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F172" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G172" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H172" s="2">
         <v>45145</v>
@@ -6475,22 +6487,22 @@
         <v>140</v>
       </c>
       <c r="B173" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C173" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D173" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E173" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F173" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G173" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H173" s="2">
         <v>45145</v>
@@ -6507,22 +6519,22 @@
         <v>141</v>
       </c>
       <c r="B174" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C174" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D174" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E174" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F174" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G174" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H174" s="2">
         <v>45145</v>
@@ -6539,22 +6551,22 @@
         <v>142</v>
       </c>
       <c r="B175" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C175" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D175" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E175">
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G175" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H175" s="2">
         <v>45141</v>
@@ -6571,22 +6583,22 @@
         <v>126</v>
       </c>
       <c r="B176" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C176" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D176" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E176">
         <v>2</v>
       </c>
       <c r="F176" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G176" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H176" s="2">
         <v>45141</v>
@@ -6603,22 +6615,22 @@
         <v>119</v>
       </c>
       <c r="B177" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C177" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D177" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E177">
         <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G177" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H177" s="2">
         <v>45141</v>
@@ -6635,22 +6647,22 @@
         <v>143</v>
       </c>
       <c r="B178" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C178" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D178" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E178">
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G178" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H178" s="2">
         <v>45141</v>
@@ -6667,22 +6679,22 @@
         <v>109</v>
       </c>
       <c r="B179" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C179" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D179" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E179">
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G179" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H179" s="2">
         <v>45141</v>
@@ -6699,22 +6711,22 @@
         <v>113</v>
       </c>
       <c r="B180" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C180" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D180" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E180">
         <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G180" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H180" s="2">
         <v>45141</v>
@@ -6731,22 +6743,22 @@
         <v>118</v>
       </c>
       <c r="B181" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C181" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D181" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E181">
         <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G181" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H181" s="2">
         <v>45141</v>
@@ -6763,22 +6775,22 @@
         <v>121</v>
       </c>
       <c r="B182" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C182" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D182" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E182">
         <v>2</v>
       </c>
       <c r="F182" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G182" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H182" s="2">
         <v>45141</v>
@@ -6795,22 +6807,22 @@
         <v>114</v>
       </c>
       <c r="B183" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C183" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D183" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E183">
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G183" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H183" s="2">
         <v>45141</v>
@@ -6827,22 +6839,22 @@
         <v>144</v>
       </c>
       <c r="B184" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C184" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D184" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E184">
         <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G184" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H184" s="2">
         <v>45141</v>
@@ -6859,22 +6871,22 @@
         <v>134</v>
       </c>
       <c r="B185" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C185" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D185" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E185">
         <v>2</v>
       </c>
       <c r="F185" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G185" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H185" s="2">
         <v>45141</v>
@@ -6891,22 +6903,22 @@
         <v>136</v>
       </c>
       <c r="B186" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C186" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D186" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E186">
         <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G186" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H186" s="2">
         <v>45141</v>
@@ -6923,22 +6935,22 @@
         <v>145</v>
       </c>
       <c r="B187" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C187" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D187" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E187">
         <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G187" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H187" s="2">
         <v>45141</v>
@@ -6955,22 +6967,22 @@
         <v>146</v>
       </c>
       <c r="B188" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C188" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D188" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E188">
         <v>2</v>
       </c>
       <c r="F188" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G188" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H188" s="2">
         <v>45141</v>
@@ -6987,22 +6999,22 @@
         <v>147</v>
       </c>
       <c r="B189" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C189" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D189" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E189">
         <v>3</v>
       </c>
       <c r="F189" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G189" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H189" s="2">
         <v>45141</v>
@@ -7019,22 +7031,22 @@
         <v>148</v>
       </c>
       <c r="B190" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C190" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D190" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E190">
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G190" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H190" s="2">
         <v>45141</v>
@@ -7051,22 +7063,22 @@
         <v>138</v>
       </c>
       <c r="B191" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C191" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D191" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E191">
         <v>2</v>
       </c>
       <c r="F191" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G191" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H191" s="2">
         <v>45141</v>
@@ -7083,22 +7095,22 @@
         <v>137</v>
       </c>
       <c r="B192" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C192" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D192" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E192">
         <v>3</v>
       </c>
       <c r="F192" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G192" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H192" s="2">
         <v>45141</v>
@@ -7115,22 +7127,22 @@
         <v>149</v>
       </c>
       <c r="B193" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C193" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D193" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E193">
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G193" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H193" s="2">
         <v>45141</v>
@@ -7147,22 +7159,22 @@
         <v>115</v>
       </c>
       <c r="B194" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C194" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D194" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E194">
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G194" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H194" s="2">
         <v>45141</v>
@@ -7179,22 +7191,22 @@
         <v>106</v>
       </c>
       <c r="B195" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C195" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D195" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E195">
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G195" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H195" s="2">
         <v>45141</v>
@@ -7211,22 +7223,22 @@
         <v>150</v>
       </c>
       <c r="B196" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C196" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D196" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G196" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H196" s="2">
         <v>45141</v>
@@ -7243,22 +7255,22 @@
         <v>151</v>
       </c>
       <c r="B197" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C197" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D197" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E197">
         <v>2</v>
       </c>
       <c r="F197" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G197" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H197" s="2">
         <v>45141</v>
@@ -7275,22 +7287,22 @@
         <v>135</v>
       </c>
       <c r="B198" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C198" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D198" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E198">
         <v>3</v>
       </c>
       <c r="F198" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G198" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H198" s="2">
         <v>45141</v>
@@ -7307,22 +7319,22 @@
         <v>131</v>
       </c>
       <c r="B199" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C199" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D199" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E199">
         <v>1</v>
       </c>
       <c r="F199" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G199" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H199" s="2">
         <v>45141</v>
@@ -7339,22 +7351,22 @@
         <v>127</v>
       </c>
       <c r="B200" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C200" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D200" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E200">
         <v>2</v>
       </c>
       <c r="F200" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G200" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H200" s="2">
         <v>45141</v>
@@ -7371,22 +7383,22 @@
         <v>117</v>
       </c>
       <c r="B201" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C201" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D201" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E201">
         <v>3</v>
       </c>
       <c r="F201" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G201" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H201" s="2">
         <v>45141</v>
@@ -7403,22 +7415,22 @@
         <v>120</v>
       </c>
       <c r="B202" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C202" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D202" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E202">
         <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G202" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H202" s="2">
         <v>45141</v>
@@ -7435,22 +7447,22 @@
         <v>152</v>
       </c>
       <c r="B203" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C203" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D203" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E203">
         <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G203" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H203" s="2">
         <v>45141</v>
@@ -7467,22 +7479,22 @@
         <v>141</v>
       </c>
       <c r="B204" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C204" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D204" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E204">
         <v>3</v>
       </c>
       <c r="F204" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G204" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H204" s="2">
         <v>45141</v>
@@ -7499,22 +7511,22 @@
         <v>120</v>
       </c>
       <c r="B205" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C205" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D205" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E205">
         <v>1</v>
       </c>
       <c r="F205" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G205" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H205" s="2">
         <v>45141</v>
@@ -7531,22 +7543,22 @@
         <v>152</v>
       </c>
       <c r="B206" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C206" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D206" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E206">
         <v>2</v>
       </c>
       <c r="F206" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G206" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H206" s="2">
         <v>45141</v>
@@ -7563,22 +7575,22 @@
         <v>141</v>
       </c>
       <c r="B207" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C207" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D207" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E207">
         <v>3</v>
       </c>
       <c r="F207" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G207" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H207" s="2">
         <v>45141</v>
@@ -7595,22 +7607,22 @@
         <v>143</v>
       </c>
       <c r="B208" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C208" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D208" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E208">
         <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G208" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H208" s="2">
         <v>45141</v>
@@ -7627,22 +7639,22 @@
         <v>109</v>
       </c>
       <c r="B209" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C209" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D209" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E209">
         <v>2</v>
       </c>
       <c r="F209" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G209" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H209" s="2">
         <v>45141</v>
@@ -7659,22 +7671,22 @@
         <v>113</v>
       </c>
       <c r="B210" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C210" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D210" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E210">
         <v>3</v>
       </c>
       <c r="F210" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G210" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H210" s="2">
         <v>45141</v>
@@ -7691,22 +7703,22 @@
         <v>118</v>
       </c>
       <c r="B211" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C211" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D211" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E211">
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G211" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H211" s="2">
         <v>45141</v>
@@ -7723,22 +7735,22 @@
         <v>121</v>
       </c>
       <c r="B212" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C212" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D212" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E212">
         <v>2</v>
       </c>
       <c r="F212" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G212" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H212" s="2">
         <v>45141</v>
@@ -7755,22 +7767,22 @@
         <v>114</v>
       </c>
       <c r="B213" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C213" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D213" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E213">
         <v>3</v>
       </c>
       <c r="F213" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G213" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H213" s="2">
         <v>45141</v>
@@ -7787,22 +7799,22 @@
         <v>148</v>
       </c>
       <c r="B214" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C214" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D214" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E214">
         <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G214" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H214" s="2">
         <v>45141</v>
@@ -7819,22 +7831,22 @@
         <v>138</v>
       </c>
       <c r="B215" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C215" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D215" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E215">
         <v>2</v>
       </c>
       <c r="F215" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G215" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H215" s="2">
         <v>45141</v>
@@ -7851,22 +7863,22 @@
         <v>137</v>
       </c>
       <c r="B216" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C216" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D216" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E216">
         <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G216" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H216" s="2">
         <v>45141</v>
@@ -7883,22 +7895,22 @@
         <v>131</v>
       </c>
       <c r="B217" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C217" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D217" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E217">
         <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G217" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H217" s="2">
         <v>45141</v>
@@ -7915,22 +7927,22 @@
         <v>127</v>
       </c>
       <c r="B218" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C218" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D218" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E218">
         <v>2</v>
       </c>
       <c r="F218" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G218" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H218" s="2">
         <v>45141</v>
@@ -7947,22 +7959,22 @@
         <v>117</v>
       </c>
       <c r="B219" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C219" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D219" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E219">
         <v>3</v>
       </c>
       <c r="F219" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G219" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H219" s="2">
         <v>45141</v>
@@ -7979,22 +7991,22 @@
         <v>145</v>
       </c>
       <c r="B220" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C220" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D220" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E220">
         <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G220" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H220" s="2">
         <v>45141</v>
@@ -8011,22 +8023,22 @@
         <v>146</v>
       </c>
       <c r="B221" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C221" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D221" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E221">
         <v>2</v>
       </c>
       <c r="F221" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G221" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H221" s="2">
         <v>45141</v>
@@ -8043,22 +8055,22 @@
         <v>147</v>
       </c>
       <c r="B222" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C222" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D222" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E222">
         <v>3</v>
       </c>
       <c r="F222" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G222" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H222" s="2">
         <v>45141</v>
@@ -8075,22 +8087,22 @@
         <v>149</v>
       </c>
       <c r="B223" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C223" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D223" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E223">
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G223" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H223" s="2">
         <v>45141</v>
@@ -8107,22 +8119,22 @@
         <v>115</v>
       </c>
       <c r="B224" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C224" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D224" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E224">
         <v>2</v>
       </c>
       <c r="F224" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G224" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H224" s="2">
         <v>45141</v>
@@ -8139,22 +8151,22 @@
         <v>106</v>
       </c>
       <c r="B225" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C225" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D225" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E225">
         <v>3</v>
       </c>
       <c r="F225" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G225" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H225" s="2">
         <v>45141</v>
@@ -8171,22 +8183,22 @@
         <v>150</v>
       </c>
       <c r="B226" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C226" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D226" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E226">
         <v>1</v>
       </c>
       <c r="F226" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G226" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H226" s="2">
         <v>45141</v>
@@ -8203,22 +8215,22 @@
         <v>151</v>
       </c>
       <c r="B227" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C227" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D227" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E227">
         <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G227" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H227" s="2">
         <v>45141</v>
@@ -8235,22 +8247,22 @@
         <v>135</v>
       </c>
       <c r="B228" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C228" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D228" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E228">
         <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G228" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H228" s="2">
         <v>45141</v>
@@ -8267,22 +8279,22 @@
         <v>120</v>
       </c>
       <c r="B229" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C229" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D229" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E229">
         <v>1</v>
       </c>
       <c r="F229" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G229" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H229" s="2">
         <v>45141</v>
@@ -8299,22 +8311,22 @@
         <v>152</v>
       </c>
       <c r="B230" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C230" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D230" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E230">
         <v>2</v>
       </c>
       <c r="F230" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G230" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H230" s="2">
         <v>45141</v>
@@ -8331,22 +8343,22 @@
         <v>141</v>
       </c>
       <c r="B231" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C231" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D231" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E231">
         <v>3</v>
       </c>
       <c r="F231" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G231" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H231" s="2">
         <v>45141</v>
@@ -8363,22 +8375,22 @@
         <v>118</v>
       </c>
       <c r="B232" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C232" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D232" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E232">
         <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G232" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H232" s="2">
         <v>45141</v>
@@ -8395,22 +8407,22 @@
         <v>121</v>
       </c>
       <c r="B233" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C233" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D233" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E233">
         <v>2</v>
       </c>
       <c r="F233" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G233" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H233" s="2">
         <v>45141</v>
@@ -8427,22 +8439,22 @@
         <v>114</v>
       </c>
       <c r="B234" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C234" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D234" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E234">
         <v>3</v>
       </c>
       <c r="F234" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G234" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H234" s="2">
         <v>45141</v>
@@ -8459,22 +8471,22 @@
         <v>143</v>
       </c>
       <c r="B235" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C235" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D235" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E235">
         <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G235" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H235" s="2">
         <v>45141</v>
@@ -8491,22 +8503,22 @@
         <v>109</v>
       </c>
       <c r="B236" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C236" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D236" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E236">
         <v>2</v>
       </c>
       <c r="F236" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G236" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H236" s="2">
         <v>45141</v>
@@ -8523,22 +8535,22 @@
         <v>113</v>
       </c>
       <c r="B237" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C237" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D237" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E237">
         <v>3</v>
       </c>
       <c r="F237" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G237" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H237" s="2">
         <v>45141</v>
@@ -8555,22 +8567,22 @@
         <v>148</v>
       </c>
       <c r="B238" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C238" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D238" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E238">
         <v>1</v>
       </c>
       <c r="F238" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G238" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H238" s="2">
         <v>45141</v>
@@ -8587,22 +8599,22 @@
         <v>138</v>
       </c>
       <c r="B239" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C239" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D239" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E239">
         <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G239" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H239" s="2">
         <v>45141</v>
@@ -8619,22 +8631,22 @@
         <v>137</v>
       </c>
       <c r="B240" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C240" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D240" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E240">
         <v>3</v>
       </c>
       <c r="F240" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G240" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H240" s="2">
         <v>45141</v>
@@ -8644,6 +8656,1350 @@
       </c>
       <c r="J240">
         <v>112.5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241" t="s">
+        <v>137</v>
+      </c>
+      <c r="B241" t="s">
+        <v>166</v>
+      </c>
+      <c r="C241" t="s">
+        <v>187</v>
+      </c>
+      <c r="D241" t="s">
+        <v>190</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+      <c r="F241" t="s">
+        <v>193</v>
+      </c>
+      <c r="G241" t="s">
+        <v>196</v>
+      </c>
+      <c r="H241" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I241">
+        <v>111.43</v>
+      </c>
+      <c r="J241">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242" t="s">
+        <v>130</v>
+      </c>
+      <c r="B242" t="s">
+        <v>170</v>
+      </c>
+      <c r="C242" t="s">
+        <v>187</v>
+      </c>
+      <c r="D242" t="s">
+        <v>190</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="F242" t="s">
+        <v>193</v>
+      </c>
+      <c r="G242" t="s">
+        <v>196</v>
+      </c>
+      <c r="H242" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I242">
+        <v>118.33</v>
+      </c>
+      <c r="J242">
+        <v>118.38</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243" t="s">
+        <v>127</v>
+      </c>
+      <c r="B243" t="s">
+        <v>163</v>
+      </c>
+      <c r="C243" t="s">
+        <v>187</v>
+      </c>
+      <c r="D243" t="s">
+        <v>190</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+      <c r="F243" t="s">
+        <v>193</v>
+      </c>
+      <c r="G243" t="s">
+        <v>196</v>
+      </c>
+      <c r="H243" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I243">
+        <v>115.85</v>
+      </c>
+      <c r="J243">
+        <v>115.94</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244" t="s">
+        <v>153</v>
+      </c>
+      <c r="B244" t="s">
+        <v>164</v>
+      </c>
+      <c r="C244" t="s">
+        <v>187</v>
+      </c>
+      <c r="D244" t="s">
+        <v>190</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+      <c r="F244" t="s">
+        <v>193</v>
+      </c>
+      <c r="G244" t="s">
+        <v>196</v>
+      </c>
+      <c r="H244" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I244">
+        <v>110.71</v>
+      </c>
+      <c r="J244">
+        <v>110.84</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="A245" t="s">
+        <v>121</v>
+      </c>
+      <c r="B245" t="s">
+        <v>164</v>
+      </c>
+      <c r="C245" t="s">
+        <v>187</v>
+      </c>
+      <c r="D245" t="s">
+        <v>190</v>
+      </c>
+      <c r="E245">
+        <v>1</v>
+      </c>
+      <c r="F245" t="s">
+        <v>193</v>
+      </c>
+      <c r="G245" t="s">
+        <v>196</v>
+      </c>
+      <c r="H245" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I245">
+        <v>112.79</v>
+      </c>
+      <c r="J245">
+        <v>112.76</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="A246" t="s">
+        <v>119</v>
+      </c>
+      <c r="B246" t="s">
+        <v>165</v>
+      </c>
+      <c r="C246" t="s">
+        <v>187</v>
+      </c>
+      <c r="D246" t="s">
+        <v>190</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+      <c r="F246" t="s">
+        <v>193</v>
+      </c>
+      <c r="G246" t="s">
+        <v>197</v>
+      </c>
+      <c r="H246" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I246">
+        <v>118.25</v>
+      </c>
+      <c r="J246">
+        <v>118.13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10">
+      <c r="A247" t="s">
+        <v>112</v>
+      </c>
+      <c r="B247" t="s">
+        <v>181</v>
+      </c>
+      <c r="C247" t="s">
+        <v>187</v>
+      </c>
+      <c r="D247" t="s">
+        <v>190</v>
+      </c>
+      <c r="E247">
+        <v>1</v>
+      </c>
+      <c r="F247" t="s">
+        <v>193</v>
+      </c>
+      <c r="G247" t="s">
+        <v>197</v>
+      </c>
+      <c r="H247" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I247">
+        <v>116.07</v>
+      </c>
+      <c r="J247">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="A248" t="s">
+        <v>106</v>
+      </c>
+      <c r="B248" t="s">
+        <v>155</v>
+      </c>
+      <c r="C248" t="s">
+        <v>187</v>
+      </c>
+      <c r="D248" t="s">
+        <v>190</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+      <c r="F248" t="s">
+        <v>193</v>
+      </c>
+      <c r="G248" t="s">
+        <v>197</v>
+      </c>
+      <c r="H248" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I248">
+        <v>112.52</v>
+      </c>
+      <c r="J248">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="A249" t="s">
+        <v>107</v>
+      </c>
+      <c r="B249" t="s">
+        <v>169</v>
+      </c>
+      <c r="C249" t="s">
+        <v>187</v>
+      </c>
+      <c r="D249" t="s">
+        <v>190</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+      <c r="F249" t="s">
+        <v>193</v>
+      </c>
+      <c r="G249" t="s">
+        <v>197</v>
+      </c>
+      <c r="H249" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I249">
+        <v>116.32</v>
+      </c>
+      <c r="J249">
+        <v>116.31</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="A250" t="s">
+        <v>137</v>
+      </c>
+      <c r="B250" t="s">
+        <v>166</v>
+      </c>
+      <c r="C250" t="s">
+        <v>187</v>
+      </c>
+      <c r="D250" t="s">
+        <v>190</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
+      <c r="F250" t="s">
+        <v>193</v>
+      </c>
+      <c r="G250" t="s">
+        <v>198</v>
+      </c>
+      <c r="H250" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I250">
+        <v>111.32</v>
+      </c>
+      <c r="J250">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="A251" t="s">
+        <v>119</v>
+      </c>
+      <c r="B251" t="s">
+        <v>165</v>
+      </c>
+      <c r="C251" t="s">
+        <v>187</v>
+      </c>
+      <c r="D251" t="s">
+        <v>190</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+      <c r="F251" t="s">
+        <v>193</v>
+      </c>
+      <c r="G251" t="s">
+        <v>198</v>
+      </c>
+      <c r="H251" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I251">
+        <v>118.36</v>
+      </c>
+      <c r="J251">
+        <v>118.38</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="A252" t="s">
+        <v>134</v>
+      </c>
+      <c r="B252" t="s">
+        <v>170</v>
+      </c>
+      <c r="C252" t="s">
+        <v>187</v>
+      </c>
+      <c r="D252" t="s">
+        <v>190</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+      <c r="F252" t="s">
+        <v>193</v>
+      </c>
+      <c r="G252" t="s">
+        <v>198</v>
+      </c>
+      <c r="H252" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I252">
+        <v>116.74</v>
+      </c>
+      <c r="J252">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253" t="s">
+        <v>113</v>
+      </c>
+      <c r="B253" t="s">
+        <v>157</v>
+      </c>
+      <c r="C253" t="s">
+        <v>187</v>
+      </c>
+      <c r="D253" t="s">
+        <v>190</v>
+      </c>
+      <c r="E253">
+        <v>1</v>
+      </c>
+      <c r="F253" t="s">
+        <v>193</v>
+      </c>
+      <c r="G253" t="s">
+        <v>198</v>
+      </c>
+      <c r="H253" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I253">
+        <v>116.07</v>
+      </c>
+      <c r="J253">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" t="s">
+        <v>139</v>
+      </c>
+      <c r="B254" t="s">
+        <v>159</v>
+      </c>
+      <c r="C254" t="s">
+        <v>187</v>
+      </c>
+      <c r="D254" t="s">
+        <v>190</v>
+      </c>
+      <c r="E254">
+        <v>1</v>
+      </c>
+      <c r="F254" t="s">
+        <v>193</v>
+      </c>
+      <c r="G254" t="s">
+        <v>198</v>
+      </c>
+      <c r="H254" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I254">
+        <v>113.98</v>
+      </c>
+      <c r="J254">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255" t="s">
+        <v>106</v>
+      </c>
+      <c r="B255" t="s">
+        <v>155</v>
+      </c>
+      <c r="C255" t="s">
+        <v>187</v>
+      </c>
+      <c r="D255" t="s">
+        <v>190</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+      <c r="F255" t="s">
+        <v>193</v>
+      </c>
+      <c r="G255" t="s">
+        <v>198</v>
+      </c>
+      <c r="H255" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I255">
+        <v>113.62</v>
+      </c>
+      <c r="J255">
+        <v>113.68</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256" t="s">
+        <v>130</v>
+      </c>
+      <c r="B256" t="s">
+        <v>170</v>
+      </c>
+      <c r="C256" t="s">
+        <v>187</v>
+      </c>
+      <c r="D256" t="s">
+        <v>190</v>
+      </c>
+      <c r="E256">
+        <v>1</v>
+      </c>
+      <c r="F256" t="s">
+        <v>193</v>
+      </c>
+      <c r="G256" t="s">
+        <v>198</v>
+      </c>
+      <c r="H256" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I256">
+        <v>119.25</v>
+      </c>
+      <c r="J256">
+        <v>119.25</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" t="s">
+        <v>121</v>
+      </c>
+      <c r="B257" t="s">
+        <v>164</v>
+      </c>
+      <c r="C257" t="s">
+        <v>187</v>
+      </c>
+      <c r="D257" t="s">
+        <v>190</v>
+      </c>
+      <c r="E257">
+        <v>1</v>
+      </c>
+      <c r="F257" t="s">
+        <v>193</v>
+      </c>
+      <c r="G257" t="s">
+        <v>198</v>
+      </c>
+      <c r="H257" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I257">
+        <v>110.43</v>
+      </c>
+      <c r="J257">
+        <v>110.45</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258" t="s">
+        <v>117</v>
+      </c>
+      <c r="B258" t="s">
+        <v>163</v>
+      </c>
+      <c r="C258" t="s">
+        <v>187</v>
+      </c>
+      <c r="D258" t="s">
+        <v>190</v>
+      </c>
+      <c r="E258">
+        <v>1</v>
+      </c>
+      <c r="F258" t="s">
+        <v>193</v>
+      </c>
+      <c r="G258" t="s">
+        <v>198</v>
+      </c>
+      <c r="H258" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I258">
+        <v>116.93</v>
+      </c>
+      <c r="J258">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="A259" t="s">
+        <v>154</v>
+      </c>
+      <c r="B259" t="s">
+        <v>157</v>
+      </c>
+      <c r="C259" t="s">
+        <v>187</v>
+      </c>
+      <c r="D259" t="s">
+        <v>190</v>
+      </c>
+      <c r="E259">
+        <v>1</v>
+      </c>
+      <c r="F259" t="s">
+        <v>193</v>
+      </c>
+      <c r="G259" t="s">
+        <v>198</v>
+      </c>
+      <c r="H259" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I259">
+        <v>115.69</v>
+      </c>
+      <c r="J259">
+        <v>115.71</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="A260" t="s">
+        <v>153</v>
+      </c>
+      <c r="B260" t="s">
+        <v>164</v>
+      </c>
+      <c r="C260" t="s">
+        <v>187</v>
+      </c>
+      <c r="D260" t="s">
+        <v>190</v>
+      </c>
+      <c r="E260">
+        <v>1</v>
+      </c>
+      <c r="F260" t="s">
+        <v>193</v>
+      </c>
+      <c r="G260" t="s">
+        <v>198</v>
+      </c>
+      <c r="H260" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I260">
+        <v>110.92</v>
+      </c>
+      <c r="J260">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261" t="s">
+        <v>147</v>
+      </c>
+      <c r="B261" t="s">
+        <v>182</v>
+      </c>
+      <c r="C261" t="s">
+        <v>187</v>
+      </c>
+      <c r="D261" t="s">
+        <v>190</v>
+      </c>
+      <c r="E261">
+        <v>1</v>
+      </c>
+      <c r="F261" t="s">
+        <v>193</v>
+      </c>
+      <c r="G261" t="s">
+        <v>198</v>
+      </c>
+      <c r="H261" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I261">
+        <v>117.63</v>
+      </c>
+      <c r="J261">
+        <v>117.64</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262" t="s">
+        <v>107</v>
+      </c>
+      <c r="B262" t="s">
+        <v>169</v>
+      </c>
+      <c r="C262" t="s">
+        <v>187</v>
+      </c>
+      <c r="D262" t="s">
+        <v>190</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+      <c r="F262" t="s">
+        <v>193</v>
+      </c>
+      <c r="G262" t="s">
+        <v>198</v>
+      </c>
+      <c r="H262" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I262">
+        <v>116.07</v>
+      </c>
+      <c r="J262">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="A263" t="s">
+        <v>112</v>
+      </c>
+      <c r="B263" t="s">
+        <v>181</v>
+      </c>
+      <c r="C263" t="s">
+        <v>187</v>
+      </c>
+      <c r="D263" t="s">
+        <v>190</v>
+      </c>
+      <c r="E263">
+        <v>1</v>
+      </c>
+      <c r="F263" t="s">
+        <v>193</v>
+      </c>
+      <c r="G263" t="s">
+        <v>199</v>
+      </c>
+      <c r="H263" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I263">
+        <v>115.98</v>
+      </c>
+      <c r="J263">
+        <v>115.94</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="A264" t="s">
+        <v>114</v>
+      </c>
+      <c r="B264" t="s">
+        <v>164</v>
+      </c>
+      <c r="C264" t="s">
+        <v>187</v>
+      </c>
+      <c r="D264" t="s">
+        <v>190</v>
+      </c>
+      <c r="E264">
+        <v>1</v>
+      </c>
+      <c r="F264" t="s">
+        <v>193</v>
+      </c>
+      <c r="G264" t="s">
+        <v>199</v>
+      </c>
+      <c r="H264" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I264">
+        <v>112.5</v>
+      </c>
+      <c r="J264">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="A265" t="s">
+        <v>130</v>
+      </c>
+      <c r="B265" t="s">
+        <v>170</v>
+      </c>
+      <c r="C265" t="s">
+        <v>187</v>
+      </c>
+      <c r="D265" t="s">
+        <v>190</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+      <c r="F265" t="s">
+        <v>193</v>
+      </c>
+      <c r="G265" t="s">
+        <v>199</v>
+      </c>
+      <c r="H265" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I265">
+        <v>118.68</v>
+      </c>
+      <c r="J265">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266" t="s">
+        <v>106</v>
+      </c>
+      <c r="B266" t="s">
+        <v>155</v>
+      </c>
+      <c r="C266" t="s">
+        <v>187</v>
+      </c>
+      <c r="D266" t="s">
+        <v>190</v>
+      </c>
+      <c r="E266">
+        <v>1</v>
+      </c>
+      <c r="F266" t="s">
+        <v>193</v>
+      </c>
+      <c r="G266" t="s">
+        <v>199</v>
+      </c>
+      <c r="H266" s="2">
+        <v>45238</v>
+      </c>
+      <c r="I266">
+        <v>112.57</v>
+      </c>
+      <c r="J266">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267" t="s">
+        <v>138</v>
+      </c>
+      <c r="B267" t="s">
+        <v>166</v>
+      </c>
+      <c r="C267" t="s">
+        <v>187</v>
+      </c>
+      <c r="D267" t="s">
+        <v>190</v>
+      </c>
+      <c r="E267">
+        <v>1</v>
+      </c>
+      <c r="F267" t="s">
+        <v>193</v>
+      </c>
+      <c r="G267" t="s">
+        <v>199</v>
+      </c>
+      <c r="H267" s="2">
+        <v>45238</v>
+      </c>
+      <c r="I267">
+        <v>112.41</v>
+      </c>
+      <c r="J267">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="A268" t="s">
+        <v>119</v>
+      </c>
+      <c r="B268" t="s">
+        <v>165</v>
+      </c>
+      <c r="C268" t="s">
+        <v>187</v>
+      </c>
+      <c r="D268" t="s">
+        <v>190</v>
+      </c>
+      <c r="E268">
+        <v>1</v>
+      </c>
+      <c r="F268" t="s">
+        <v>193</v>
+      </c>
+      <c r="G268" t="s">
+        <v>199</v>
+      </c>
+      <c r="H268" s="2">
+        <v>45238</v>
+      </c>
+      <c r="I268">
+        <v>118.48</v>
+      </c>
+      <c r="J268">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="A269" t="s">
+        <v>121</v>
+      </c>
+      <c r="B269" t="s">
+        <v>164</v>
+      </c>
+      <c r="C269" t="s">
+        <v>187</v>
+      </c>
+      <c r="D269" t="s">
+        <v>190</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="F269" t="s">
+        <v>193</v>
+      </c>
+      <c r="G269" t="s">
+        <v>199</v>
+      </c>
+      <c r="H269" s="2">
+        <v>45238</v>
+      </c>
+      <c r="I269">
+        <v>110.07</v>
+      </c>
+      <c r="J269">
+        <v>110.08</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="A270" t="s">
+        <v>127</v>
+      </c>
+      <c r="B270" t="s">
+        <v>163</v>
+      </c>
+      <c r="C270" t="s">
+        <v>187</v>
+      </c>
+      <c r="D270" t="s">
+        <v>190</v>
+      </c>
+      <c r="E270">
+        <v>1</v>
+      </c>
+      <c r="F270" t="s">
+        <v>193</v>
+      </c>
+      <c r="G270" t="s">
+        <v>199</v>
+      </c>
+      <c r="H270" s="2">
+        <v>45238</v>
+      </c>
+      <c r="I270">
+        <v>116.31</v>
+      </c>
+      <c r="J270">
+        <v>116.31</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="A271" t="s">
+        <v>111</v>
+      </c>
+      <c r="B271" t="s">
+        <v>158</v>
+      </c>
+      <c r="C271" t="s">
+        <v>187</v>
+      </c>
+      <c r="D271" t="s">
+        <v>190</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+      <c r="F271" t="s">
+        <v>193</v>
+      </c>
+      <c r="G271" t="s">
+        <v>196</v>
+      </c>
+      <c r="H271" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I271">
+        <v>114.7</v>
+      </c>
+      <c r="J271">
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="A272" t="s">
+        <v>114</v>
+      </c>
+      <c r="B272" t="s">
+        <v>164</v>
+      </c>
+      <c r="C272" t="s">
+        <v>187</v>
+      </c>
+      <c r="D272" t="s">
+        <v>190</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+      <c r="F272" t="s">
+        <v>193</v>
+      </c>
+      <c r="G272" t="s">
+        <v>197</v>
+      </c>
+      <c r="H272" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I272">
+        <v>110.44</v>
+      </c>
+      <c r="J272">
+        <v>110.45</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="A273" t="s">
+        <v>138</v>
+      </c>
+      <c r="B273" t="s">
+        <v>166</v>
+      </c>
+      <c r="C273" t="s">
+        <v>187</v>
+      </c>
+      <c r="D273" t="s">
+        <v>190</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="F273" t="s">
+        <v>193</v>
+      </c>
+      <c r="G273" t="s">
+        <v>197</v>
+      </c>
+      <c r="H273" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I273">
+        <v>112.29</v>
+      </c>
+      <c r="J273">
+        <v>112.26</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="A274" t="s">
+        <v>127</v>
+      </c>
+      <c r="B274" t="s">
+        <v>163</v>
+      </c>
+      <c r="C274" t="s">
+        <v>187</v>
+      </c>
+      <c r="D274" t="s">
+        <v>190</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+      <c r="F274" t="s">
+        <v>193</v>
+      </c>
+      <c r="G274" t="s">
+        <v>198</v>
+      </c>
+      <c r="H274" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I274">
+        <v>116.07</v>
+      </c>
+      <c r="J274">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10">
+      <c r="A275" t="s">
+        <v>114</v>
+      </c>
+      <c r="B275" t="s">
+        <v>164</v>
+      </c>
+      <c r="C275" t="s">
+        <v>187</v>
+      </c>
+      <c r="D275" t="s">
+        <v>190</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="F275" t="s">
+        <v>193</v>
+      </c>
+      <c r="G275" t="s">
+        <v>198</v>
+      </c>
+      <c r="H275" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I275">
+        <v>109.6</v>
+      </c>
+      <c r="J275">
+        <v>109.59</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10">
+      <c r="A276" t="s">
+        <v>111</v>
+      </c>
+      <c r="B276" t="s">
+        <v>158</v>
+      </c>
+      <c r="C276" t="s">
+        <v>187</v>
+      </c>
+      <c r="D276" t="s">
+        <v>190</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+      <c r="F276" t="s">
+        <v>193</v>
+      </c>
+      <c r="G276" t="s">
+        <v>198</v>
+      </c>
+      <c r="H276" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I276">
+        <v>114.74</v>
+      </c>
+      <c r="J276">
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10">
+      <c r="A277" t="s">
+        <v>138</v>
+      </c>
+      <c r="B277" t="s">
+        <v>166</v>
+      </c>
+      <c r="C277" t="s">
+        <v>187</v>
+      </c>
+      <c r="D277" t="s">
+        <v>190</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+      <c r="F277" t="s">
+        <v>193</v>
+      </c>
+      <c r="G277" t="s">
+        <v>198</v>
+      </c>
+      <c r="H277" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I277">
+        <v>111.74</v>
+      </c>
+      <c r="J277">
+        <v>111.86</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="A278" t="s">
+        <v>112</v>
+      </c>
+      <c r="B278" t="s">
+        <v>181</v>
+      </c>
+      <c r="C278" t="s">
+        <v>187</v>
+      </c>
+      <c r="D278" t="s">
+        <v>190</v>
+      </c>
+      <c r="E278">
+        <v>1</v>
+      </c>
+      <c r="F278" t="s">
+        <v>193</v>
+      </c>
+      <c r="G278" t="s">
+        <v>198</v>
+      </c>
+      <c r="H278" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I278">
+        <v>116.07</v>
+      </c>
+      <c r="J278">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="A279" t="s">
+        <v>137</v>
+      </c>
+      <c r="B279" t="s">
+        <v>166</v>
+      </c>
+      <c r="C279" t="s">
+        <v>187</v>
+      </c>
+      <c r="D279" t="s">
+        <v>190</v>
+      </c>
+      <c r="E279">
+        <v>1</v>
+      </c>
+      <c r="F279" t="s">
+        <v>193</v>
+      </c>
+      <c r="G279" t="s">
+        <v>199</v>
+      </c>
+      <c r="H279" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I279">
+        <v>112.1</v>
+      </c>
+      <c r="J279">
+        <v>112.15</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10">
+      <c r="A280" t="s">
+        <v>153</v>
+      </c>
+      <c r="B280" t="s">
+        <v>164</v>
+      </c>
+      <c r="C280" t="s">
+        <v>187</v>
+      </c>
+      <c r="D280" t="s">
+        <v>190</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+      <c r="F280" t="s">
+        <v>193</v>
+      </c>
+      <c r="G280" t="s">
+        <v>199</v>
+      </c>
+      <c r="H280" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I280">
+        <v>112.89</v>
+      </c>
+      <c r="J280">
+        <v>112.91</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10">
+      <c r="A281" t="s">
+        <v>107</v>
+      </c>
+      <c r="B281" t="s">
+        <v>169</v>
+      </c>
+      <c r="C281" t="s">
+        <v>187</v>
+      </c>
+      <c r="D281" t="s">
+        <v>190</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="F281" t="s">
+        <v>193</v>
+      </c>
+      <c r="G281" t="s">
+        <v>199</v>
+      </c>
+      <c r="H281" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I281">
+        <v>116.46</v>
+      </c>
+      <c r="J281">
+        <v>116.44</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10">
+      <c r="A282" t="s">
+        <v>111</v>
+      </c>
+      <c r="B282" t="s">
+        <v>158</v>
+      </c>
+      <c r="C282" t="s">
+        <v>187</v>
+      </c>
+      <c r="D282" t="s">
+        <v>190</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+      <c r="F282" t="s">
+        <v>193</v>
+      </c>
+      <c r="G282" t="s">
+        <v>199</v>
+      </c>
+      <c r="H282" s="2">
+        <v>45144</v>
+      </c>
+      <c r="I282">
+        <v>114.83</v>
+      </c>
+      <c r="J282">
+        <v>114.75</v>
       </c>
     </row>
   </sheetData>
